--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_grocery_and_food.xlsx
@@ -650,10 +650,10 @@
         <v>0.1262610068322522</v>
       </c>
       <c r="X2">
-        <v>0.08139858226891813</v>
+        <v>0.08137569554560808</v>
       </c>
       <c r="Y2">
-        <v>0.04486242456333403</v>
+        <v>0.04488531128664408</v>
       </c>
       <c r="Z2">
         <v>4.147078085957543</v>
@@ -662,10 +662,10 @@
         <v>0.1177895367734489</v>
       </c>
       <c r="AB2">
-        <v>0.06515107562941759</v>
+        <v>0.0651375910359703</v>
       </c>
       <c r="AC2">
-        <v>0.05263846114403133</v>
+        <v>0.05265194573747861</v>
       </c>
       <c r="AD2">
         <v>20941.2</v>
@@ -787,10 +787,10 @@
         <v>0.1262610068322522</v>
       </c>
       <c r="X3">
-        <v>0.08139858226891813</v>
+        <v>0.08137569554560808</v>
       </c>
       <c r="Y3">
-        <v>0.04486242456333403</v>
+        <v>0.04488531128664408</v>
       </c>
       <c r="Z3">
         <v>4.147078085957543</v>
@@ -799,10 +799,10 @@
         <v>0.1177895367734489</v>
       </c>
       <c r="AB3">
-        <v>0.06515107562941759</v>
+        <v>0.0651375910359703</v>
       </c>
       <c r="AC3">
-        <v>0.05263846114403133</v>
+        <v>0.05265194573747861</v>
       </c>
       <c r="AD3">
         <v>20941.2</v>
@@ -1139,49 +1139,49 @@
         <v>4.19470787963939</v>
       </c>
       <c r="F2">
-        <v>3.05373411845075</v>
+        <v>3.04859725967881</v>
       </c>
       <c r="G2">
         <v>3.79465806545138</v>
       </c>
       <c r="H2">
-        <v>3.78716196136701</v>
+        <v>3.97190156923857</v>
       </c>
       <c r="I2">
         <v>0.41081153188217</v>
       </c>
       <c r="J2">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="K2">
         <v>30034</v>
       </c>
       <c r="L2">
-        <v>28987.4501373282</v>
+        <v>30396.5016810177</v>
       </c>
       <c r="M2">
         <v>46415.6</v>
       </c>
       <c r="N2">
-        <v>45327.6821373282</v>
+        <v>47756.2376810177</v>
       </c>
       <c r="O2">
         <v>20941.2</v>
       </c>
       <c r="P2">
-        <v>20899.832</v>
+        <v>21919.336</v>
       </c>
       <c r="Q2">
-        <v>0.0651510756294176</v>
+        <v>0.0651375910359703</v>
       </c>
       <c r="R2">
-        <v>0.0656155242808041</v>
+        <v>0.0645947362286864</v>
       </c>
       <c r="S2">
         <v>0.0418488</v>
       </c>
       <c r="T2">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.08139858226891809</v>
+        <v>0.0813756955456081</v>
       </c>
       <c r="X2">
-        <v>0.08135794284882041</v>
+        <v>0.0823696811029587</v>
       </c>
       <c r="Y2">
         <v>0.821609596896261</v>
       </c>
       <c r="Z2">
-        <v>0.820671645566841</v>
+        <v>0.844565383440154</v>
       </c>
       <c r="AA2">
         <v>20941.2</v>
@@ -1236,7 +1236,7 @@
         <v>30034</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04330000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06926087795039705</v>
+        <v>0.06924579469179407</v>
       </c>
       <c r="C2">
-        <v>42844.26214622604</v>
+        <v>42842.19618784974</v>
       </c>
       <c r="D2">
-        <v>38284.66214622604</v>
+        <v>38282.59618784974</v>
       </c>
       <c r="E2">
         <v>-20941.2</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06926087795039705</v>
+        <v>0.06924579469179407</v>
       </c>
       <c r="T2">
         <v>0.5414733185171841</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06912596288528504</v>
+        <v>0.06910053054148925</v>
       </c>
       <c r="C3">
-        <v>42555.94485019308</v>
+        <v>42571.11209271947</v>
       </c>
       <c r="D3">
-        <v>38506.09685019308</v>
+        <v>38521.26409271947</v>
       </c>
       <c r="E3">
         <v>-20431.448</v>
@@ -1539,37 +1539,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M3">
-        <v>26.3541784</v>
+        <v>25.6405256</v>
       </c>
       <c r="N3">
-        <v>3668.970311395919</v>
+        <v>3669.683964195919</v>
       </c>
       <c r="O3">
-        <v>946.594340340147</v>
+        <v>946.7784627625471</v>
       </c>
       <c r="P3">
-        <v>2722.375971055772</v>
+        <v>2722.905501433372</v>
       </c>
       <c r="Q3">
-        <v>4658.275971055772</v>
+        <v>4658.805501433372</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06943671604574246</v>
+        <v>0.06942151973887803</v>
       </c>
       <c r="T3">
         <v>0.545531633692333</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>140.2177838257298</v>
+        <v>144.1204656817144</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.068991047820173</v>
+        <v>0.06895526639118441</v>
       </c>
       <c r="C4">
-        <v>42270.20396879529</v>
+        <v>42303.02255526958</v>
       </c>
       <c r="D4">
-        <v>38730.1079687953</v>
+        <v>38762.92655526958</v>
       </c>
       <c r="E4">
         <v>-19921.696</v>
@@ -1621,37 +1621,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M4">
-        <v>52.7083568</v>
+        <v>51.2810512</v>
       </c>
       <c r="N4">
-        <v>3642.616132995919</v>
+        <v>3644.043438595918</v>
       </c>
       <c r="O4">
-        <v>939.7949623129471</v>
+        <v>940.1632071577469</v>
       </c>
       <c r="P4">
-        <v>2702.821170682972</v>
+        <v>2703.880231438171</v>
       </c>
       <c r="Q4">
-        <v>4638.721170682972</v>
+        <v>4639.780231438172</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.06961614267364592</v>
+        <v>0.06960083101141266</v>
       </c>
       <c r="T4">
         <v>0.5496727716261586</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.10889191286492</v>
+        <v>72.06023284085718</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06885613275506099</v>
+        <v>0.06881000224087959</v>
       </c>
       <c r="C5">
-        <v>41987.08473040872</v>
+        <v>42037.98429021114</v>
       </c>
       <c r="D5">
-        <v>38956.74073040872</v>
+        <v>39007.64029021114</v>
       </c>
       <c r="E5">
         <v>-19411.944</v>
@@ -1703,37 +1703,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M5">
-        <v>79.0625352</v>
+        <v>76.92157679999998</v>
       </c>
       <c r="N5">
-        <v>3616.261954595918</v>
+        <v>3618.402912995919</v>
       </c>
       <c r="O5">
-        <v>932.995584285747</v>
+        <v>933.547951552947</v>
       </c>
       <c r="P5">
-        <v>2683.266370310171</v>
+        <v>2684.854961442972</v>
       </c>
       <c r="Q5">
-        <v>4619.166370310171</v>
+        <v>4620.754961442972</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0697992688196505</v>
+        <v>0.06978383942358721</v>
       </c>
       <c r="T5">
         <v>0.5538992938472794</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.73926127524327</v>
+        <v>48.04015522723813</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06872121768994896</v>
+        <v>0.06866473809057476</v>
       </c>
       <c r="C6">
-        <v>41706.63342827261</v>
+        <v>41776.05545353395</v>
       </c>
       <c r="D6">
-        <v>39186.04142827261</v>
+        <v>39255.46345353396</v>
       </c>
       <c r="E6">
         <v>-18902.192</v>
@@ -1785,37 +1785,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M6">
-        <v>105.4167136</v>
+        <v>102.5621024</v>
       </c>
       <c r="N6">
-        <v>3589.907776195918</v>
+        <v>3592.762387395918</v>
       </c>
       <c r="O6">
-        <v>926.1962062585469</v>
+        <v>926.9326959481469</v>
       </c>
       <c r="P6">
-        <v>2663.711569937372</v>
+        <v>2665.829691447771</v>
       </c>
       <c r="Q6">
-        <v>4599.611569937372</v>
+        <v>4601.729691447772</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06998621009369684</v>
+        <v>0.06997066051101537</v>
       </c>
       <c r="T6">
         <v>0.5582138686146737</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.05444595643245</v>
+        <v>36.03011642042859</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06858630262483692</v>
+        <v>0.06851947394026991</v>
       </c>
       <c r="C7">
-        <v>41428.89745201382</v>
+        <v>41517.29568858272</v>
       </c>
       <c r="D7">
-        <v>39418.05745201383</v>
+        <v>39506.45568858272</v>
       </c>
       <c r="E7">
         <v>-18392.44</v>
@@ -1867,37 +1867,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M7">
-        <v>131.770892</v>
+        <v>128.202628</v>
       </c>
       <c r="N7">
-        <v>3563.553597795918</v>
+        <v>3567.121861795918</v>
       </c>
       <c r="O7">
-        <v>919.3968282313469</v>
+        <v>920.317440343347</v>
       </c>
       <c r="P7">
-        <v>2644.156769564572</v>
+        <v>2646.804421452572</v>
       </c>
       <c r="Q7">
-        <v>4580.056769564572</v>
+        <v>4582.704421452572</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07017708697351256</v>
+        <v>0.07016141467396834</v>
       </c>
       <c r="T7">
         <v>0.5626192765350657</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.04355676514596</v>
+        <v>28.82409313634287</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06845138755972491</v>
+        <v>0.0683742097899651</v>
       </c>
       <c r="C8">
-        <v>41153.92532029806</v>
+        <v>41261.76617391233</v>
       </c>
       <c r="D8">
-        <v>39652.83732029807</v>
+        <v>39760.67817391233</v>
       </c>
       <c r="E8">
         <v>-17882.688</v>
@@ -1949,37 +1949,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M8">
-        <v>158.1250704</v>
+        <v>153.8431536</v>
       </c>
       <c r="N8">
-        <v>3537.199419395919</v>
+        <v>3541.481336195919</v>
       </c>
       <c r="O8">
-        <v>912.597450204147</v>
+        <v>913.702184738547</v>
       </c>
       <c r="P8">
-        <v>2624.601969191772</v>
+        <v>2627.779151457372</v>
       </c>
       <c r="Q8">
-        <v>4560.501969191772</v>
+        <v>4563.679151457372</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07037202506353714</v>
+        <v>0.0703562274361331</v>
       </c>
       <c r="T8">
         <v>0.5671184165388703</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.36963063762164</v>
+        <v>24.02007761361907</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06831647249461288</v>
+        <v>0.06822894563966027</v>
       </c>
       <c r="C9">
-        <v>40881.76671465521</v>
+        <v>41009.5296730031</v>
       </c>
       <c r="D9">
-        <v>39890.43071465522</v>
+        <v>40018.19367300311</v>
       </c>
       <c r="E9">
         <v>-17372.936</v>
@@ -2031,37 +2031,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M9">
-        <v>184.4792488</v>
+        <v>179.4836792</v>
       </c>
       <c r="N9">
-        <v>3510.845240995919</v>
+        <v>3515.840810595918</v>
       </c>
       <c r="O9">
-        <v>905.798072176947</v>
+        <v>907.0869291337469</v>
       </c>
       <c r="P9">
-        <v>2605.047168818972</v>
+        <v>2608.753881462171</v>
       </c>
       <c r="Q9">
-        <v>4540.947168818972</v>
+        <v>4544.653881462172</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07057115537055149</v>
+        <v>0.07055522972006481</v>
       </c>
       <c r="T9">
         <v>0.5717143122416815</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.03111197510426</v>
+        <v>20.58863795453063</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06818155742950087</v>
+        <v>0.06808368148935545</v>
       </c>
       <c r="C10">
-        <v>40612.47251452754</v>
+        <v>40760.65058592009</v>
       </c>
       <c r="D10">
-        <v>40130.88851452754</v>
+        <v>40279.0665859201</v>
       </c>
       <c r="E10">
         <v>-16863.184</v>
@@ -2113,37 +2113,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M10">
-        <v>210.8334272</v>
+        <v>205.1242048</v>
       </c>
       <c r="N10">
-        <v>3484.491062595918</v>
+        <v>3490.200284995919</v>
       </c>
       <c r="O10">
-        <v>898.9986941497469</v>
+        <v>900.471673528947</v>
       </c>
       <c r="P10">
-        <v>2585.492368446171</v>
+        <v>2589.728611466971</v>
       </c>
       <c r="Q10">
-        <v>4521.392368446172</v>
+        <v>4525.628611466972</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07077461459728354</v>
+        <v>0.07075855814060374</v>
       </c>
       <c r="T10">
         <v>0.5764101187206405</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.52722297821623</v>
+        <v>18.0150582102143</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06804664236438883</v>
+        <v>0.06793841733905061</v>
       </c>
       <c r="C11">
-        <v>40346.09483359371</v>
+        <v>40515.19500300656</v>
       </c>
       <c r="D11">
-        <v>40374.2628335937</v>
+        <v>40543.36300300655</v>
       </c>
       <c r="E11">
         <v>-16353.432</v>
@@ -2195,37 +2195,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M11">
-        <v>237.1876056</v>
+        <v>230.7647303999999</v>
       </c>
       <c r="N11">
-        <v>3458.136884195918</v>
+        <v>3464.559759395919</v>
       </c>
       <c r="O11">
-        <v>892.199316122547</v>
+        <v>893.8564179241471</v>
       </c>
       <c r="P11">
-        <v>2565.937568073371</v>
+        <v>2570.703341471772</v>
       </c>
       <c r="Q11">
-        <v>4501.837568073372</v>
+        <v>4506.603341471772</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07098254545537235</v>
+        <v>0.07096635531763804</v>
       </c>
       <c r="T11">
         <v>0.581209129737599</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.57975375841443</v>
+        <v>16.01338507574604</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06791172729927682</v>
+        <v>0.06779315318874579</v>
       </c>
       <c r="C12">
-        <v>40082.68705742202</v>
+        <v>40273.23076070494</v>
       </c>
       <c r="D12">
-        <v>40620.60705742202</v>
+        <v>40811.15076070494</v>
       </c>
       <c r="E12">
         <v>-15843.68</v>
@@ -2277,37 +2277,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M12">
-        <v>263.5417840000001</v>
+        <v>256.405256</v>
       </c>
       <c r="N12">
-        <v>3431.782705795918</v>
+        <v>3438.919233795918</v>
       </c>
       <c r="O12">
-        <v>885.399938095347</v>
+        <v>887.2411623193469</v>
       </c>
       <c r="P12">
-        <v>2546.382767700572</v>
+        <v>2551.678071476571</v>
       </c>
       <c r="Q12">
-        <v>4482.282767700572</v>
+        <v>4487.578071476571</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07119509699919646</v>
+        <v>0.07117877020971754</v>
       </c>
       <c r="T12">
         <v>0.586114785443823</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.02177838257298</v>
+        <v>14.41204656817144</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06777681223416479</v>
+        <v>0.06764788903844096</v>
       </c>
       <c r="C13">
-        <v>39822.30388251134</v>
+        <v>40034.82749960532</v>
       </c>
       <c r="D13">
-        <v>40869.97588251134</v>
+        <v>41082.49949960531</v>
       </c>
       <c r="E13">
         <v>-15333.928</v>
@@ -2359,37 +2359,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M13">
-        <v>289.8959624</v>
+        <v>282.0457816</v>
       </c>
       <c r="N13">
-        <v>3405.428527395919</v>
+        <v>3413.278708195919</v>
       </c>
       <c r="O13">
-        <v>878.600560068147</v>
+        <v>880.625906714547</v>
       </c>
       <c r="P13">
-        <v>2526.827967327772</v>
+        <v>2532.652801481372</v>
       </c>
       <c r="Q13">
-        <v>4462.727967327772</v>
+        <v>4468.552801481372</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07141242498220762</v>
+        <v>0.07139595847015838</v>
       </c>
       <c r="T13">
         <v>0.5911306806041194</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.74707125688453</v>
+        <v>13.10186051651949</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06764189716905276</v>
+        <v>0.06750262488813612</v>
       </c>
       <c r="C14">
-        <v>39565.0013567781</v>
+        <v>39800.05672482438</v>
       </c>
       <c r="D14">
-        <v>41122.4253567781</v>
+        <v>41357.48072482437</v>
       </c>
       <c r="E14">
         <v>-14824.176</v>
@@ -2441,37 +2441,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M14">
-        <v>316.2501408</v>
+        <v>307.6863071999999</v>
       </c>
       <c r="N14">
-        <v>3379.074348995919</v>
+        <v>3387.638182595918</v>
       </c>
       <c r="O14">
-        <v>871.8011820409471</v>
+        <v>874.010651109747</v>
       </c>
       <c r="P14">
-        <v>2507.273166954972</v>
+        <v>2513.627531486171</v>
       </c>
       <c r="Q14">
-        <v>4443.173166954972</v>
+        <v>4449.527531486172</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07163469223755996</v>
+        <v>0.07161808282742742</v>
       </c>
       <c r="T14">
         <v>0.5962605733816956</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.68481531881082</v>
+        <v>12.01003880680953</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06750698210394074</v>
+        <v>0.0673573607378313</v>
       </c>
       <c r="C15">
-        <v>39310.83692155371</v>
+        <v>39568.99186882602</v>
       </c>
       <c r="D15">
-        <v>41378.01292155371</v>
+        <v>41636.16786882602</v>
       </c>
       <c r="E15">
         <v>-14314.424</v>
@@ -2523,37 +2523,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M15">
-        <v>342.6043192</v>
+        <v>333.3268328</v>
       </c>
       <c r="N15">
-        <v>3352.720170595918</v>
+        <v>3361.997656995919</v>
       </c>
       <c r="O15">
-        <v>865.0018040137469</v>
+        <v>867.395395504947</v>
       </c>
       <c r="P15">
-        <v>2487.718366582171</v>
+        <v>2494.602261490972</v>
       </c>
       <c r="Q15">
-        <v>4423.618366582172</v>
+        <v>4430.502261490972</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07186206908498935</v>
+        <v>0.07184531349176011</v>
       </c>
       <c r="T15">
         <v>0.601508394728871</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.78598337120999</v>
+        <v>11.08618966782418</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06737206703882871</v>
+        <v>0.06721209658752647</v>
       </c>
       <c r="C16">
-        <v>39059.86945515772</v>
+        <v>39341.7083567992</v>
       </c>
       <c r="D16">
-        <v>41636.79745515772</v>
+        <v>41918.6363567992</v>
       </c>
       <c r="E16">
         <v>-13804.672</v>
@@ -2605,37 +2605,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M16">
-        <v>368.9584976</v>
+        <v>358.9673584</v>
       </c>
       <c r="N16">
-        <v>3326.365992195918</v>
+        <v>3336.357131395918</v>
       </c>
       <c r="O16">
-        <v>858.2024259865469</v>
+        <v>860.7801399001469</v>
       </c>
       <c r="P16">
-        <v>2468.163566209371</v>
+        <v>2475.576991495771</v>
       </c>
       <c r="Q16">
-        <v>4404.063566209372</v>
+        <v>4411.476991495772</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.0720947337660799</v>
+        <v>0.07207782859014705</v>
       </c>
       <c r="T16">
         <v>0.6068782584329574</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.01555598755213</v>
+        <v>10.29431897726531</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06723715197371669</v>
+        <v>0.06706683243722164</v>
       </c>
       <c r="C17">
-        <v>38812.1593181163</v>
+        <v>39118.28367471468</v>
       </c>
       <c r="D17">
-        <v>41898.8393181163</v>
+        <v>42204.96367471468</v>
       </c>
       <c r="E17">
         <v>-13294.92</v>
@@ -2687,37 +2687,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M17">
-        <v>395.312676</v>
+        <v>384.6078839999999</v>
       </c>
       <c r="N17">
-        <v>3300.011813795918</v>
+        <v>3310.716605795918</v>
       </c>
       <c r="O17">
-        <v>851.403047959347</v>
+        <v>854.164884295347</v>
       </c>
       <c r="P17">
-        <v>2448.608765836571</v>
+        <v>2456.551721500572</v>
       </c>
       <c r="Q17">
-        <v>4384.508765836572</v>
+        <v>4392.451721500573</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07233287291025493</v>
+        <v>0.07231581463202547</v>
       </c>
       <c r="T17">
         <v>0.6123744718712577</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.347852255048656</v>
+        <v>9.608031045447627</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06710223690860467</v>
+        <v>0.06692156828691681</v>
       </c>
       <c r="C18">
-        <v>38567.76840009911</v>
+        <v>38898.79744019059</v>
       </c>
       <c r="D18">
-        <v>42164.20040009911</v>
+        <v>42495.22944019059</v>
       </c>
       <c r="E18">
         <v>-12785.168</v>
@@ -2769,37 +2769,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M18">
-        <v>421.6668544</v>
+        <v>410.2484096</v>
       </c>
       <c r="N18">
-        <v>3273.657635395919</v>
+        <v>3285.076080195919</v>
       </c>
       <c r="O18">
-        <v>844.603669932147</v>
+        <v>847.549628690547</v>
       </c>
       <c r="P18">
-        <v>2429.053965463771</v>
+        <v>2437.526451505371</v>
       </c>
       <c r="Q18">
-        <v>4364.953965463772</v>
+        <v>4373.426451505372</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07257668203405318</v>
+        <v>0.0725594670082343</v>
       </c>
       <c r="T18">
         <v>0.6180015475342794</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.763611489108115</v>
+        <v>9.007529105107148</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06710607584349264</v>
+        <v>0.06696551413661199</v>
       </c>
       <c r="C19">
-        <v>38050.41924231519</v>
+        <v>38300.81281074975</v>
       </c>
       <c r="D19">
-        <v>42156.60324231519</v>
+        <v>42406.99681074975</v>
       </c>
       <c r="E19">
         <v>-12275.416</v>
@@ -2851,37 +2851,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M19">
-        <v>457.5533952</v>
+        <v>448.8876112</v>
       </c>
       <c r="N19">
-        <v>3237.771094595918</v>
+        <v>3246.436878595919</v>
       </c>
       <c r="O19">
-        <v>835.344942405747</v>
+        <v>837.580714677747</v>
       </c>
       <c r="P19">
-        <v>2402.426152190171</v>
+        <v>2408.856163918172</v>
       </c>
       <c r="Q19">
-        <v>4338.326152190171</v>
+        <v>4344.756163918172</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07282636607649716</v>
+        <v>0.07280899052603854</v>
       </c>
       <c r="T19">
         <v>0.6237642153819523</v>
       </c>
       <c r="U19">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.076269411531008</v>
+        <v>8.232181948433151</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06697932277838062</v>
+        <v>0.06683137998630716</v>
       </c>
       <c r="C20">
-        <v>37792.96419871879</v>
+        <v>38061.5245885852</v>
       </c>
       <c r="D20">
-        <v>42408.90019871879</v>
+        <v>42677.4605885852</v>
       </c>
       <c r="E20">
         <v>-11765.664</v>
@@ -2933,37 +2933,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M20">
-        <v>484.4683007999999</v>
+        <v>475.2927647999999</v>
       </c>
       <c r="N20">
-        <v>3210.856188995919</v>
+        <v>3220.031724995918</v>
       </c>
       <c r="O20">
-        <v>828.400896760947</v>
+        <v>830.768185048947</v>
       </c>
       <c r="P20">
-        <v>2382.455292234972</v>
+        <v>2389.263539946971</v>
       </c>
       <c r="Q20">
-        <v>4318.355292234972</v>
+        <v>4325.163539946972</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0730821399736349</v>
+        <v>0.07306459998330141</v>
       </c>
       <c r="T20">
         <v>0.6296674361039585</v>
       </c>
       <c r="U20">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.627587777557064</v>
+        <v>7.774838506853532</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0668525697132686</v>
+        <v>0.06669724583600233</v>
       </c>
       <c r="C21">
-        <v>37538.54720824161</v>
+        <v>37825.70844396742</v>
       </c>
       <c r="D21">
-        <v>42664.23520824161</v>
+        <v>42951.39644396742</v>
       </c>
       <c r="E21">
         <v>-11255.912</v>
@@ -3015,37 +3015,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M21">
-        <v>511.3832064</v>
+        <v>501.6979184</v>
       </c>
       <c r="N21">
-        <v>3183.941283395919</v>
+        <v>3193.626571395918</v>
       </c>
       <c r="O21">
-        <v>821.456851116147</v>
+        <v>823.955655420147</v>
       </c>
       <c r="P21">
-        <v>2362.484432279772</v>
+        <v>2369.670915975771</v>
       </c>
       <c r="Q21">
-        <v>4298.384432279772</v>
+        <v>4305.570915975772</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07334422927564024</v>
+        <v>0.07332652078518806</v>
       </c>
       <c r="T21">
         <v>0.6357164153623107</v>
       </c>
       <c r="U21">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.226135789264585</v>
+        <v>7.365636480177029</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06672581664815658</v>
+        <v>0.06656311168569751</v>
       </c>
       <c r="C22">
-        <v>37287.22347769608</v>
+        <v>37593.43166799107</v>
       </c>
       <c r="D22">
-        <v>42922.66347769609</v>
+        <v>43228.87166799107</v>
       </c>
       <c r="E22">
         <v>-10746.16</v>
@@ -3097,37 +3097,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M22">
-        <v>538.2981120000001</v>
+        <v>528.103072</v>
       </c>
       <c r="N22">
-        <v>3157.026377795919</v>
+        <v>3167.221417795919</v>
       </c>
       <c r="O22">
-        <v>814.512805471347</v>
+        <v>817.143125791347</v>
       </c>
       <c r="P22">
-        <v>2342.513572324572</v>
+        <v>2350.078292004572</v>
       </c>
       <c r="Q22">
-        <v>4278.413572324573</v>
+        <v>4285.978292004573</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07361287081019571</v>
+        <v>0.07359498960712188</v>
       </c>
       <c r="T22">
         <v>0.6419166191021217</v>
       </c>
       <c r="U22">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.864828999801356</v>
+        <v>6.997354656168178</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06694186758304455</v>
+        <v>0.06669387153539268</v>
       </c>
       <c r="C23">
-        <v>36338.84033331813</v>
+        <v>36813.14097188474</v>
       </c>
       <c r="D23">
-        <v>42484.03233331814</v>
+        <v>42958.33297188474</v>
       </c>
       <c r="E23">
         <v>-10236.408</v>
@@ -3179,37 +3179,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M23">
-        <v>588.76356</v>
+        <v>572.706372</v>
       </c>
       <c r="N23">
-        <v>3106.560929795919</v>
+        <v>3122.618117795918</v>
       </c>
       <c r="O23">
-        <v>801.492719887347</v>
+        <v>805.635474391347</v>
       </c>
       <c r="P23">
-        <v>2305.068209908572</v>
+        <v>2316.982643404571</v>
       </c>
       <c r="Q23">
-        <v>4240.968209908572</v>
+        <v>4252.882643404571</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07388831339625891</v>
+        <v>0.07387025510809199</v>
       </c>
       <c r="T23">
         <v>0.648273790025219</v>
       </c>
       <c r="U23">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.276415085532669</v>
+        <v>6.45238934026723</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06683143851793252</v>
+        <v>0.06657235138508784</v>
       </c>
       <c r="C24">
-        <v>36052.15780946249</v>
+        <v>36554.69913811543</v>
       </c>
       <c r="D24">
-        <v>42707.10180946249</v>
+        <v>43209.64313811543</v>
       </c>
       <c r="E24">
         <v>-9726.656000000001</v>
@@ -3261,37 +3261,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M24">
-        <v>616.79992</v>
+        <v>599.978104</v>
       </c>
       <c r="N24">
-        <v>3078.524569795919</v>
+        <v>3095.346385795919</v>
       </c>
       <c r="O24">
-        <v>794.259339007347</v>
+        <v>798.599367535347</v>
       </c>
       <c r="P24">
-        <v>2284.265230788571</v>
+        <v>2296.747018260572</v>
       </c>
       <c r="Q24">
-        <v>4220.165230788572</v>
+        <v>4232.647018260572</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.074170818612734</v>
+        <v>0.07415257869883056</v>
       </c>
       <c r="T24">
         <v>0.6547939653309598</v>
       </c>
       <c r="U24">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.991123490735728</v>
+        <v>6.159098915709628</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.0667210094528205</v>
+        <v>0.06645083123478301</v>
       </c>
       <c r="C25">
-        <v>35767.83017711063</v>
+        <v>36299.21498181934</v>
       </c>
       <c r="D25">
-        <v>42932.52617711063</v>
+        <v>43463.91098181934</v>
       </c>
       <c r="E25">
         <v>-9216.904</v>
@@ -3343,37 +3343,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M25">
-        <v>644.83628</v>
+        <v>627.249836</v>
       </c>
       <c r="N25">
-        <v>3050.488209795918</v>
+        <v>3068.074653795918</v>
       </c>
       <c r="O25">
-        <v>787.0259581273469</v>
+        <v>791.563260679347</v>
       </c>
       <c r="P25">
-        <v>2263.462251668571</v>
+        <v>2276.511393116572</v>
       </c>
       <c r="Q25">
-        <v>4199.362251668572</v>
+        <v>4212.411393116572</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0744606616270396</v>
+        <v>0.07444223536984806</v>
       </c>
       <c r="T25">
         <v>0.6614834958394472</v>
       </c>
       <c r="U25">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.730639860703741</v>
+        <v>5.891312006330949</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06687770038770847</v>
+        <v>0.06632931108447818</v>
       </c>
       <c r="C26">
-        <v>34938.9191825309</v>
+        <v>36046.74102556919</v>
       </c>
       <c r="D26">
-        <v>42613.36718253089</v>
+        <v>43721.18902556919</v>
       </c>
       <c r="E26">
         <v>-8707.152000000002</v>
@@ -3425,45 +3425,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M26">
-        <v>691.223712</v>
+        <v>654.5215679999999</v>
       </c>
       <c r="N26">
-        <v>3004.100777795918</v>
+        <v>3040.802921795918</v>
       </c>
       <c r="O26">
-        <v>775.058000671347</v>
+        <v>784.5271538233469</v>
       </c>
       <c r="P26">
-        <v>2229.042777124571</v>
+        <v>2256.275767972571</v>
       </c>
       <c r="Q26">
-        <v>4164.942777124572</v>
+        <v>4192.175767972572</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07475813208909009</v>
+        <v>0.07473951458483971</v>
       </c>
       <c r="T26">
         <v>0.6683490666244737</v>
       </c>
       <c r="U26">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.346061521969198</v>
+        <v>5.645840672733827</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06677840132259644</v>
+        <v>0.06635619093417335</v>
       </c>
       <c r="C27">
-        <v>34630.87309221542</v>
+        <v>35479.81797703862</v>
       </c>
       <c r="D27">
-        <v>42815.07309221543</v>
+        <v>43664.01797703862</v>
       </c>
       <c r="E27">
         <v>-8197.400000000001</v>
@@ -3507,37 +3507,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M27">
-        <v>720.0246999999999</v>
+        <v>691.98834</v>
       </c>
       <c r="N27">
-        <v>2975.299789795919</v>
+        <v>3003.336149795919</v>
       </c>
       <c r="O27">
-        <v>767.627345767347</v>
+        <v>774.8607266473471</v>
       </c>
       <c r="P27">
-        <v>2207.672444028572</v>
+        <v>2228.475423148571</v>
       </c>
       <c r="Q27">
-        <v>4143.572444028572</v>
+        <v>4164.375423148572</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07506353509679525</v>
+        <v>0.07504472124556447</v>
       </c>
       <c r="T27">
         <v>0.6753977192971009</v>
       </c>
       <c r="U27">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.132219061090431</v>
+        <v>5.34015427166868</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06667910225748441</v>
+        <v>0.06624060678386853</v>
       </c>
       <c r="C28">
-        <v>34324.74559092852</v>
+        <v>35216.97001810421</v>
       </c>
       <c r="D28">
-        <v>43018.69759092852</v>
+        <v>43910.92201810422</v>
       </c>
       <c r="E28">
         <v>-7687.648000000001</v>
@@ -3589,37 +3589,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M28">
-        <v>748.825688</v>
+        <v>719.6678736</v>
       </c>
       <c r="N28">
-        <v>2946.498801795919</v>
+        <v>2975.656616195919</v>
       </c>
       <c r="O28">
-        <v>760.196690863347</v>
+        <v>767.719406978547</v>
       </c>
       <c r="P28">
-        <v>2186.302110932571</v>
+        <v>2207.937209217372</v>
       </c>
       <c r="Q28">
-        <v>4122.202110932572</v>
+        <v>4143.837209217372</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07537719223984381</v>
+        <v>0.07535817673495747</v>
       </c>
       <c r="T28">
         <v>0.6826368760960153</v>
       </c>
       <c r="U28">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.93482602027926</v>
+        <v>5.134763722758346</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06657980319237239</v>
+        <v>0.06612502263356371</v>
       </c>
       <c r="C29">
-        <v>34020.56418337206</v>
+        <v>34956.93024239384</v>
       </c>
       <c r="D29">
-        <v>43224.26818337206</v>
+        <v>44160.63424239384</v>
       </c>
       <c r="E29">
         <v>-7177.896000000001</v>
@@ -3671,37 +3671,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M29">
-        <v>777.626676</v>
+        <v>747.3474072</v>
       </c>
       <c r="N29">
-        <v>2917.697813795919</v>
+        <v>2947.977082595919</v>
       </c>
       <c r="O29">
-        <v>752.7660359593471</v>
+        <v>760.578087309747</v>
       </c>
       <c r="P29">
-        <v>2164.931777836572</v>
+        <v>2187.398995286172</v>
       </c>
       <c r="Q29">
-        <v>4100.831777836573</v>
+        <v>4123.298995286172</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07569944272927726</v>
+        <v>0.07568022004597767</v>
       </c>
       <c r="T29">
         <v>0.6900743659579138</v>
       </c>
       <c r="U29">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.752054686194843</v>
+        <v>4.94458728858211</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06648050412726038</v>
+        <v>0.06600943848325887</v>
       </c>
       <c r="C30">
-        <v>33718.35690251176</v>
+        <v>34699.74683256313</v>
       </c>
       <c r="D30">
-        <v>43431.81290251176</v>
+        <v>44413.20283256314</v>
       </c>
       <c r="E30">
         <v>-6668.144</v>
@@ -3753,37 +3753,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M30">
-        <v>806.427664</v>
+        <v>775.0269408</v>
       </c>
       <c r="N30">
-        <v>2888.896825795919</v>
+        <v>2920.297548995919</v>
       </c>
       <c r="O30">
-        <v>745.3353810553471</v>
+        <v>753.436767640947</v>
       </c>
       <c r="P30">
-        <v>2143.561444740571</v>
+        <v>2166.860781354972</v>
       </c>
       <c r="Q30">
-        <v>4079.461444740572</v>
+        <v>4102.760781354972</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07603064462119496</v>
+        <v>0.07601120900452621</v>
       </c>
       <c r="T30">
         <v>0.6977184527604204</v>
       </c>
       <c r="U30">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.58233844740217</v>
+        <v>4.767994885418464</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06638120506214834</v>
+        <v>0.06589385433295404</v>
       </c>
       <c r="C31">
-        <v>33418.15232232112</v>
+        <v>34445.46907989551</v>
       </c>
       <c r="D31">
-        <v>43641.36032232112</v>
+        <v>44668.67707989551</v>
       </c>
       <c r="E31">
         <v>-6158.392000000003</v>
@@ -3835,37 +3835,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M31">
-        <v>835.2286519999999</v>
+        <v>802.7064743999998</v>
       </c>
       <c r="N31">
-        <v>2860.095837795919</v>
+        <v>2892.618015395919</v>
       </c>
       <c r="O31">
-        <v>737.9047261513471</v>
+        <v>746.295447972147</v>
       </c>
       <c r="P31">
-        <v>2122.191111644572</v>
+        <v>2146.322567423771</v>
       </c>
       <c r="Q31">
-        <v>4058.091111644572</v>
+        <v>4082.222567423772</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07637117614387091</v>
+        <v>0.07635152159570992</v>
       </c>
       <c r="T31">
         <v>0.70557786595173</v>
       </c>
       <c r="U31">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.424326776802095</v>
+        <v>4.603581268679896</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06628190599703632</v>
+        <v>0.06577827018264921</v>
       </c>
       <c r="C32">
-        <v>33119.97957089547</v>
+        <v>34194.147416372</v>
       </c>
       <c r="D32">
-        <v>43852.93957089547</v>
+        <v>44927.107416372</v>
       </c>
       <c r="E32">
         <v>-5648.640000000003</v>
@@ -3917,37 +3917,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M32">
-        <v>864.0296399999999</v>
+        <v>830.3860079999998</v>
       </c>
       <c r="N32">
-        <v>2831.294849795919</v>
+        <v>2864.938481795919</v>
       </c>
       <c r="O32">
-        <v>730.4740712473471</v>
+        <v>739.154128303347</v>
       </c>
       <c r="P32">
-        <v>2100.820778548572</v>
+        <v>2125.784353492571</v>
       </c>
       <c r="Q32">
-        <v>4036.720778548572</v>
+        <v>4061.684353492572</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07672143713862332</v>
+        <v>0.07670155740378459</v>
       </c>
       <c r="T32">
         <v>0.7136618338056486</v>
       </c>
       <c r="U32">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.276849217575359</v>
+        <v>4.4501285597239</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06650463493192429</v>
+        <v>0.06566268603234438</v>
       </c>
       <c r="C33">
-        <v>32138.48206297191</v>
+        <v>33945.83344786078</v>
       </c>
       <c r="D33">
-        <v>43381.19406297191</v>
+        <v>45188.54544786078</v>
       </c>
       <c r="E33">
         <v>-5138.888000000003</v>
@@ -3999,45 +3999,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M33">
-        <v>914.9538647999999</v>
+        <v>858.0655416</v>
       </c>
       <c r="N33">
-        <v>2780.370624995919</v>
+        <v>2837.258948195918</v>
       </c>
       <c r="O33">
-        <v>717.3356212489471</v>
+        <v>732.012808634547</v>
       </c>
       <c r="P33">
-        <v>2063.035003746972</v>
+        <v>2105.246139561371</v>
       </c>
       <c r="Q33">
-        <v>3998.935003746972</v>
+        <v>4041.146139561372</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07708185062597725</v>
+        <v>0.0770617391773107</v>
       </c>
       <c r="T33">
         <v>0.7219801195683764</v>
       </c>
       <c r="U33">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0429618</v>
+        <v>0.0402906</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.038809640531635</v>
+        <v>4.306576025539258</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06641572386681227</v>
+        <v>0.06578454188203955</v>
       </c>
       <c r="C34">
-        <v>31815.82357445319</v>
+        <v>33160.54405328147</v>
       </c>
       <c r="D34">
-        <v>43568.28757445319</v>
+        <v>44913.00805328147</v>
       </c>
       <c r="E34">
         <v>-4629.136</v>
@@ -4081,37 +4081,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M34">
-        <v>944.4685056000001</v>
+        <v>902.0571392000001</v>
       </c>
       <c r="N34">
-        <v>2750.855984195919</v>
+        <v>2793.267350595918</v>
       </c>
       <c r="O34">
-        <v>709.720843922547</v>
+        <v>720.662976453747</v>
       </c>
       <c r="P34">
-        <v>2041.135140273372</v>
+        <v>2072.604374142171</v>
       </c>
       <c r="Q34">
-        <v>3977.035140273372</v>
+        <v>4008.504374142172</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07745286451001805</v>
+        <v>0.07743251453241111</v>
       </c>
       <c r="T34">
         <v>0.7305430607947138</v>
       </c>
       <c r="U34">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.912596839265022</v>
+        <v>4.096552567693395</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06632681280170025</v>
+        <v>0.06567637773173474</v>
       </c>
       <c r="C35">
-        <v>31494.78586199376</v>
+        <v>32895.2016443691</v>
       </c>
       <c r="D35">
-        <v>43757.00186199376</v>
+        <v>45157.4176443691</v>
       </c>
       <c r="E35">
         <v>-4119.384000000002</v>
@@ -4163,37 +4163,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M35">
-        <v>973.9831463999999</v>
+        <v>930.2464248</v>
       </c>
       <c r="N35">
-        <v>2721.341343395919</v>
+        <v>2765.078064995918</v>
       </c>
       <c r="O35">
-        <v>702.106066596147</v>
+        <v>713.3901407689469</v>
       </c>
       <c r="P35">
-        <v>2019.235276799772</v>
+        <v>2051.687924226972</v>
       </c>
       <c r="Q35">
-        <v>3955.135276799772</v>
+        <v>3987.587924226972</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07783495343537351</v>
+        <v>0.0778143578085593</v>
       </c>
       <c r="T35">
         <v>0.739361612206912</v>
       </c>
       <c r="U35">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.794033298681234</v>
+        <v>3.972414611096625</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06623790173658822</v>
+        <v>0.06556821358142989</v>
       </c>
       <c r="C36">
-        <v>31175.39007819446</v>
+        <v>32632.53386820876</v>
       </c>
       <c r="D36">
-        <v>43947.35807819446</v>
+        <v>45404.50186820876</v>
       </c>
       <c r="E36">
         <v>-3609.632000000001</v>
@@ -4245,37 +4245,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M36">
-        <v>1003.4977872</v>
+        <v>958.4357103999999</v>
       </c>
       <c r="N36">
-        <v>2691.826702595919</v>
+        <v>2736.888779395918</v>
       </c>
       <c r="O36">
-        <v>694.491289269747</v>
+        <v>706.117305084147</v>
       </c>
       <c r="P36">
-        <v>1997.335413326171</v>
+        <v>2030.771474311771</v>
       </c>
       <c r="Q36">
-        <v>3933.235413326172</v>
+        <v>3966.671474311772</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07822862081301246</v>
+        <v>0.07820777209307561</v>
       </c>
       <c r="T36">
         <v>0.7484473924497829</v>
       </c>
       <c r="U36">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.682444084014138</v>
+        <v>3.855578887240843</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0661489906714762</v>
+        <v>0.06546004943112506</v>
       </c>
       <c r="C37">
-        <v>30857.65774534527</v>
+        <v>32372.58487006764</v>
       </c>
       <c r="D37">
-        <v>44139.37774534527</v>
+        <v>45654.30487006764</v>
       </c>
       <c r="E37">
         <v>-3099.880000000001</v>
@@ -4327,37 +4327,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M37">
-        <v>1033.012428</v>
+        <v>986.624996</v>
       </c>
       <c r="N37">
-        <v>2662.312061795918</v>
+        <v>2708.699493795918</v>
       </c>
       <c r="O37">
-        <v>686.8765119433469</v>
+        <v>698.844469399347</v>
       </c>
       <c r="P37">
-        <v>1975.435549852572</v>
+        <v>2009.855024396571</v>
       </c>
       <c r="Q37">
-        <v>3911.335549852572</v>
+        <v>3945.755024396572</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07863440103304031</v>
+        <v>0.07861329143250011</v>
       </c>
       <c r="T37">
         <v>0.7578127351616651</v>
       </c>
       <c r="U37">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.577231395899449</v>
+        <v>3.745419490462533</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.06606007960636419</v>
+        <v>0.06535188528082024</v>
       </c>
       <c r="C38">
-        <v>30541.61076353717</v>
+        <v>32115.39977208768</v>
       </c>
       <c r="D38">
-        <v>44333.08276353717</v>
+        <v>45906.87177208767</v>
       </c>
       <c r="E38">
         <v>-2590.128000000004</v>
@@ -4409,37 +4409,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M38">
-        <v>1062.5270688</v>
+        <v>1014.8142816</v>
       </c>
       <c r="N38">
-        <v>2632.797420995918</v>
+        <v>2680.510208195918</v>
       </c>
       <c r="O38">
-        <v>679.2617346169469</v>
+        <v>691.571633714547</v>
       </c>
       <c r="P38">
-        <v>1953.535686378972</v>
+        <v>1988.938574481371</v>
       </c>
       <c r="Q38">
-        <v>3889.435686378972</v>
+        <v>3924.838574481372</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.07905286188494404</v>
+        <v>0.07903148325128162</v>
       </c>
       <c r="T38">
         <v>0.7674707448332938</v>
       </c>
       <c r="U38">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.477863857124464</v>
+        <v>3.641380060171907</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.06597116854125215</v>
+        <v>0.06524372113051541</v>
       </c>
       <c r="C39">
-        <v>30227.27141898869</v>
+        <v>31861.024700457</v>
       </c>
       <c r="D39">
-        <v>44528.49541898868</v>
+        <v>46162.248700457</v>
       </c>
       <c r="E39">
         <v>-2080.376000000004</v>
@@ -4491,37 +4491,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M39">
-        <v>1092.0417096</v>
+        <v>1043.0035672</v>
       </c>
       <c r="N39">
-        <v>2603.282780195918</v>
+        <v>2652.320922595919</v>
       </c>
       <c r="O39">
-        <v>671.646957290547</v>
+        <v>684.298798029747</v>
       </c>
       <c r="P39">
-        <v>1931.635822905371</v>
+        <v>1968.022124566171</v>
       </c>
       <c r="Q39">
-        <v>3867.535822905372</v>
+        <v>3903.922124566172</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.07948460720833675</v>
+        <v>0.07946295100081811</v>
       </c>
       <c r="T39">
         <v>0.7774353579865614</v>
       </c>
       <c r="U39">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.38386753666164</v>
+        <v>3.542964382869964</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06588225747614013</v>
+        <v>0.06513555698021059</v>
       </c>
       <c r="C40">
-        <v>29914.66239259321</v>
+        <v>31609.50681349314</v>
       </c>
       <c r="D40">
-        <v>44725.63839259322</v>
+        <v>46420.48281349314</v>
       </c>
       <c r="E40">
         <v>-1570.624</v>
@@ -4573,37 +4573,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M40">
-        <v>1121.5563504</v>
+        <v>1071.1928528</v>
       </c>
       <c r="N40">
-        <v>2573.768139395918</v>
+        <v>2624.131636995919</v>
       </c>
       <c r="O40">
-        <v>664.032179964147</v>
+        <v>677.0259623449471</v>
       </c>
       <c r="P40">
-        <v>1909.735959431771</v>
+        <v>1947.105674650972</v>
       </c>
       <c r="Q40">
-        <v>3845.635959431772</v>
+        <v>3883.005674650972</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.07993027980022602</v>
+        <v>0.07990833706485578</v>
       </c>
       <c r="T40">
         <v>0.7877214102738054</v>
       </c>
       <c r="U40">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.294818390960018</v>
+        <v>3.449728478057596</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.0657933464110281</v>
+        <v>0.06502739282990576</v>
       </c>
       <c r="C41">
-        <v>29603.80676869498</v>
+        <v>31360.8943306747</v>
       </c>
       <c r="D41">
-        <v>44924.53476869498</v>
+        <v>46681.6223306747</v>
       </c>
       <c r="E41">
         <v>-1060.871999999999</v>
@@ -4655,37 +4655,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M41">
-        <v>1151.0709912</v>
+        <v>1099.3821384</v>
       </c>
       <c r="N41">
-        <v>2544.253498595918</v>
+        <v>2595.942351395918</v>
       </c>
       <c r="O41">
-        <v>656.4174026377469</v>
+        <v>669.7531266601469</v>
       </c>
       <c r="P41">
-        <v>1887.836095958171</v>
+        <v>1926.189224735771</v>
       </c>
       <c r="Q41">
-        <v>3823.736095958172</v>
+        <v>3862.089224735772</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08039056460824279</v>
+        <v>0.08036832595066518</v>
       </c>
       <c r="T41">
         <v>0.7983447101770246</v>
       </c>
       <c r="U41">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.210335868114889</v>
+        <v>3.361273901697145</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06570443534591608</v>
+        <v>0.06491922867960093</v>
       </c>
       <c r="C42">
-        <v>29294.72804409972</v>
+        <v>31115.2365626578</v>
       </c>
       <c r="D42">
-        <v>45125.20804409972</v>
+        <v>46945.7165626578</v>
       </c>
       <c r="E42">
         <v>-551.119999999999</v>
@@ -4737,37 +4737,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M42">
-        <v>1180.585632</v>
+        <v>1127.571424</v>
       </c>
       <c r="N42">
-        <v>2514.738857795918</v>
+        <v>2567.753065795918</v>
       </c>
       <c r="O42">
-        <v>648.8026253113469</v>
+        <v>662.480290975347</v>
       </c>
       <c r="P42">
-        <v>1865.936232484571</v>
+        <v>1905.272774820571</v>
       </c>
       <c r="Q42">
-        <v>3801.836232484572</v>
+        <v>3841.172774820572</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08086619224319347</v>
+        <v>0.08084364779933488</v>
       </c>
       <c r="T42">
         <v>0.8093221200770179</v>
       </c>
       <c r="U42">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.130077471412017</v>
+        <v>3.277242054154716</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06561552428080406</v>
+        <v>0.06481106452929609</v>
       </c>
       <c r="C43">
-        <v>28987.45013732819</v>
+        <v>30872.58394231781</v>
       </c>
       <c r="D43">
-        <v>45327.68213732819</v>
+        <v>47212.81594231781</v>
       </c>
       <c r="E43">
         <v>-41.36799999999857</v>
@@ -4819,37 +4819,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M43">
-        <v>1210.1002728</v>
+        <v>1155.7607096</v>
       </c>
       <c r="N43">
-        <v>2485.224216995918</v>
+        <v>2539.563780195918</v>
       </c>
       <c r="O43">
-        <v>641.1878479849469</v>
+        <v>655.2074552905469</v>
       </c>
       <c r="P43">
-        <v>1844.036369010971</v>
+        <v>1884.356324905371</v>
       </c>
       <c r="Q43">
-        <v>3779.936369010972</v>
+        <v>3820.256324905372</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08135794284882043</v>
+        <v>0.08133508225304423</v>
       </c>
       <c r="T43">
         <v>0.8206716455668412</v>
       </c>
       <c r="U43">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.053734118450748</v>
+        <v>3.197309321126552</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06633687721569204</v>
+        <v>0.06470290037899126</v>
       </c>
       <c r="C44">
-        <v>26885.57406714835</v>
+        <v>30632.98805685644</v>
       </c>
       <c r="D44">
-        <v>43735.55806714835</v>
+        <v>47482.97205685644</v>
       </c>
       <c r="E44">
         <v>468.3839999999982</v>
@@ -4901,45 +4901,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M44">
-        <v>1295.279832</v>
+        <v>1183.9499952</v>
       </c>
       <c r="N44">
-        <v>2400.044657795918</v>
+        <v>2511.374494595919</v>
       </c>
       <c r="O44">
-        <v>619.2115217113469</v>
+        <v>647.9346196057471</v>
       </c>
       <c r="P44">
-        <v>1780.833136084571</v>
+        <v>1863.439874990172</v>
       </c>
       <c r="Q44">
-        <v>3716.733136084572</v>
+        <v>3799.339874990172</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08186665037188282</v>
+        <v>0.08184346272239873</v>
       </c>
       <c r="T44">
         <v>0.8324125340045897</v>
       </c>
       <c r="U44">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.852915947969395</v>
+        <v>3.121182908718778</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06626725815058002</v>
+        <v>0.06459473622868644</v>
       </c>
       <c r="C45">
-        <v>26524.58789803719</v>
+        <v>30396.50168101766</v>
       </c>
       <c r="D45">
-        <v>43884.32389803719</v>
+        <v>47756.23768101766</v>
       </c>
       <c r="E45">
         <v>978.1359999999986</v>
@@ -4983,45 +4983,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M45">
-        <v>1326.119828</v>
+        <v>1212.1392808</v>
       </c>
       <c r="N45">
-        <v>2369.204661795919</v>
+        <v>2483.185208995918</v>
       </c>
       <c r="O45">
-        <v>611.254802743347</v>
+        <v>640.661783920947</v>
       </c>
       <c r="P45">
-        <v>1757.949859052572</v>
+        <v>1842.523425074971</v>
       </c>
       <c r="Q45">
-        <v>3693.849859052572</v>
+        <v>3778.423425074972</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08239320728171931</v>
+        <v>0.08236968110295867</v>
       </c>
       <c r="T45">
         <v>0.8445653834401539</v>
       </c>
       <c r="U45">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.786569065458479</v>
+        <v>3.048597259678806</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06619763908546798</v>
+        <v>0.06530277207838162</v>
       </c>
       <c r="C46">
-        <v>26164.61723253642</v>
+        <v>28152.98956789994</v>
       </c>
       <c r="D46">
-        <v>44034.10523253642</v>
+        <v>46022.47756789994</v>
       </c>
       <c r="E46">
         <v>1487.887999999999</v>
@@ -5065,37 +5065,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M46">
-        <v>1356.959824</v>
+        <v>1296.4012864</v>
       </c>
       <c r="N46">
-        <v>2338.364665795918</v>
+        <v>2398.923203395918</v>
       </c>
       <c r="O46">
-        <v>603.298083775347</v>
+        <v>618.922186476147</v>
       </c>
       <c r="P46">
-        <v>1735.066582020571</v>
+        <v>1780.001016919771</v>
       </c>
       <c r="Q46">
-        <v>3670.966582020572</v>
+        <v>3715.901016919772</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08293856979547853</v>
+        <v>0.08291469299711002</v>
       </c>
       <c r="T46">
         <v>0.8571522632127023</v>
       </c>
       <c r="U46">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.723237950334422</v>
+        <v>2.850448027599179</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06612802002035598</v>
+        <v>0.06521315792807679</v>
       </c>
       <c r="C47">
-        <v>25805.67250428561</v>
+        <v>27855.68446795866</v>
       </c>
       <c r="D47">
-        <v>44184.91250428561</v>
+        <v>46234.92446795866</v>
       </c>
       <c r="E47">
         <v>1997.639999999999</v>
@@ -5147,37 +5147,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M47">
-        <v>1387.79982</v>
+        <v>1325.864952</v>
       </c>
       <c r="N47">
-        <v>2307.524669795918</v>
+        <v>2369.459537795919</v>
       </c>
       <c r="O47">
-        <v>595.341364807347</v>
+        <v>611.320560751347</v>
       </c>
       <c r="P47">
-        <v>1712.183304988571</v>
+        <v>1758.138977044572</v>
       </c>
       <c r="Q47">
-        <v>3648.083304988572</v>
+        <v>3694.038977044572</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08350376367337448</v>
+        <v>0.08347952350559415</v>
       </c>
       <c r="T47">
         <v>0.8701968477042528</v>
       </c>
       <c r="U47">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.662721551438102</v>
+        <v>2.787104738096975</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06605840095524394</v>
+        <v>0.06512354377777196</v>
       </c>
       <c r="C48">
-        <v>25447.76429034757</v>
+        <v>27560.34983975409</v>
       </c>
       <c r="D48">
-        <v>44336.75629034757</v>
+        <v>46449.3418397541</v>
       </c>
       <c r="E48">
         <v>2507.392</v>
@@ -5229,37 +5229,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M48">
-        <v>1418.639816</v>
+        <v>1355.3286176</v>
       </c>
       <c r="N48">
-        <v>2276.684673795919</v>
+        <v>2339.995872195918</v>
       </c>
       <c r="O48">
-        <v>587.3846458393471</v>
+        <v>603.7189350265469</v>
       </c>
       <c r="P48">
-        <v>1689.300027956572</v>
+        <v>1736.276937169371</v>
       </c>
       <c r="Q48">
-        <v>3625.200027956572</v>
+        <v>3672.176937169372</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08408989065785914</v>
+        <v>0.08406527366254066</v>
       </c>
       <c r="T48">
         <v>0.8837245649547495</v>
       </c>
       <c r="U48">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.604836300319882</v>
+        <v>2.726515504660084</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06598878189013191</v>
+        <v>0.06503392962746712</v>
       </c>
       <c r="C49">
-        <v>25090.90331368082</v>
+        <v>27267.01322557543</v>
       </c>
       <c r="D49">
-        <v>44489.64731368082</v>
+        <v>46665.75722557543</v>
       </c>
       <c r="E49">
         <v>3017.144</v>
@@ -5311,37 +5311,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M49">
-        <v>1449.479812</v>
+        <v>1384.7922832</v>
       </c>
       <c r="N49">
-        <v>2245.844677795918</v>
+        <v>2310.532206595918</v>
       </c>
       <c r="O49">
-        <v>579.4279268713469</v>
+        <v>596.1173093017469</v>
       </c>
       <c r="P49">
-        <v>1666.416750924571</v>
+        <v>1714.414897294171</v>
       </c>
       <c r="Q49">
-        <v>3602.316750924572</v>
+        <v>3650.314897294172</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08469813564175832</v>
+        <v>0.08467312759899456</v>
       </c>
       <c r="T49">
         <v>0.8977627621014911</v>
       </c>
       <c r="U49">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.044891</v>
+        <v>0.0428876</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.549414251376906</v>
+        <v>2.668504536475827</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06688079482501989</v>
+        <v>0.0649443154771623</v>
       </c>
       <c r="C50">
-        <v>22698.61599175326</v>
+        <v>26975.7026834113</v>
       </c>
       <c r="D50">
-        <v>42607.11199175326</v>
+        <v>46884.1986834113</v>
       </c>
       <c r="E50">
         <v>3526.895999999997</v>
@@ -5393,45 +5393,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M50">
-        <v>1546.3836672</v>
+        <v>1414.2559488</v>
       </c>
       <c r="N50">
-        <v>2148.940822595919</v>
+        <v>2281.068540995919</v>
       </c>
       <c r="O50">
-        <v>554.426732229747</v>
+        <v>588.515683576947</v>
       </c>
       <c r="P50">
-        <v>1594.514090366172</v>
+        <v>1692.552857418972</v>
       </c>
       <c r="Q50">
-        <v>3530.414090366172</v>
+        <v>3628.452857418972</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.08532977466349978</v>
+        <v>0.08530436053300441</v>
       </c>
       <c r="T50">
         <v>0.912340889907723</v>
       </c>
       <c r="U50">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.389655664487814</v>
+        <v>2.612910691965914</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06683120975990786</v>
+        <v>0.06485470132685747</v>
       </c>
       <c r="C51">
-        <v>22289.31833776877</v>
+        <v>26686.44679907671</v>
       </c>
       <c r="D51">
-        <v>42707.56633776877</v>
+        <v>47104.69479907671</v>
       </c>
       <c r="E51">
         <v>4036.647999999997</v>
@@ -5475,45 +5475,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M51">
-        <v>1578.5999936</v>
+        <v>1443.7196144</v>
       </c>
       <c r="N51">
-        <v>2116.724496195919</v>
+        <v>2251.604875395918</v>
       </c>
       <c r="O51">
-        <v>546.114920018547</v>
+        <v>580.914057852147</v>
       </c>
       <c r="P51">
-        <v>1570.609576177372</v>
+        <v>1670.690817543772</v>
       </c>
       <c r="Q51">
-        <v>3506.509576177372</v>
+        <v>3606.590817543772</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08598618384295659</v>
+        <v>0.08596034769972052</v>
       </c>
       <c r="T51">
         <v>0.9274907090004738</v>
       </c>
       <c r="U51">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.340887181539083</v>
+        <v>2.55958598396661</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06678162469479584</v>
+        <v>0.06476508717655263</v>
       </c>
       <c r="C52">
-        <v>21880.4954835541</v>
+        <v>26399.27469868334</v>
       </c>
       <c r="D52">
-        <v>42808.4954835541</v>
+        <v>47327.27469868334</v>
       </c>
       <c r="E52">
         <v>4546.399999999998</v>
@@ -5557,45 +5557,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M52">
-        <v>1610.81632</v>
+        <v>1473.18328</v>
       </c>
       <c r="N52">
-        <v>2084.508169795919</v>
+        <v>2222.141209795918</v>
       </c>
       <c r="O52">
-        <v>537.803107807347</v>
+        <v>573.3124321273469</v>
       </c>
       <c r="P52">
-        <v>1546.705061988572</v>
+        <v>1648.828777668571</v>
       </c>
       <c r="Q52">
-        <v>3482.605061988572</v>
+        <v>3584.728777668572</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08666884938959167</v>
+        <v>0.08664257435310527</v>
       </c>
       <c r="T52">
         <v>0.9432465208569346</v>
       </c>
       <c r="U52">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0468944</v>
+        <v>0.0428876</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.294069437908301</v>
+        <v>2.508394264287277</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06851061362968382</v>
+        <v>0.06599994302624781</v>
       </c>
       <c r="C53">
-        <v>18111.67632591794</v>
+        <v>22996.32830027044</v>
       </c>
       <c r="D53">
-        <v>39549.42832591794</v>
+        <v>44434.08030027044</v>
       </c>
       <c r="E53">
         <v>5056.151999999998</v>
@@ -5639,45 +5639,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M53">
-        <v>1765.2202008</v>
+        <v>1593.6376776</v>
       </c>
       <c r="N53">
-        <v>1930.104288995919</v>
+        <v>2101.686812195919</v>
       </c>
       <c r="O53">
-        <v>497.966906560947</v>
+        <v>542.2351975465471</v>
       </c>
       <c r="P53">
-        <v>1432.137382434972</v>
+        <v>1559.451614649372</v>
       </c>
       <c r="Q53">
-        <v>3368.037382434972</v>
+        <v>3495.351614649372</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08737937883608941</v>
+        <v>0.08735264699234246</v>
       </c>
       <c r="T53">
         <v>0.9596454270748837</v>
       </c>
       <c r="U53">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.093407093415991</v>
+        <v>2.318798395480354</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06849590256457179</v>
+        <v>0.06593629887594298</v>
       </c>
       <c r="C54">
-        <v>17627.55953533914</v>
+        <v>22627.01766453059</v>
       </c>
       <c r="D54">
-        <v>39575.06353533914</v>
+        <v>44574.52166453059</v>
       </c>
       <c r="E54">
         <v>5565.903999999999</v>
@@ -5721,45 +5721,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M54">
-        <v>1799.8323616</v>
+        <v>1624.8854752</v>
       </c>
       <c r="N54">
-        <v>1895.492128195918</v>
+        <v>2070.439014595919</v>
       </c>
       <c r="O54">
-        <v>489.036969074547</v>
+        <v>534.173265765747</v>
       </c>
       <c r="P54">
-        <v>1406.455159121371</v>
+        <v>1536.265748830172</v>
       </c>
       <c r="Q54">
-        <v>3342.355159121372</v>
+        <v>3472.165748830172</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.08811951367619122</v>
+        <v>0.08809230599154788</v>
       </c>
       <c r="T54">
         <v>0.9767276210519139</v>
       </c>
       <c r="U54">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.053149264696452</v>
+        <v>2.274206118644194</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06848119149945976</v>
+        <v>0.06697378272563816</v>
       </c>
       <c r="C55">
-        <v>17143.47599885416</v>
+        <v>19933.18042411474</v>
       </c>
       <c r="D55">
-        <v>39600.73199885416</v>
+        <v>42390.43642411474</v>
       </c>
       <c r="E55">
         <v>6075.655999999999</v>
@@ -5803,37 +5803,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M55">
-        <v>1834.4445224</v>
+        <v>1731.7804696</v>
       </c>
       <c r="N55">
-        <v>1860.879967395918</v>
+        <v>1963.544020195918</v>
       </c>
       <c r="O55">
-        <v>480.1070315881469</v>
+        <v>506.5943572105469</v>
       </c>
       <c r="P55">
-        <v>1380.772935807771</v>
+        <v>1456.949662985372</v>
       </c>
       <c r="Q55">
-        <v>3316.672935807772</v>
+        <v>3392.849662985372</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.08889114361587183</v>
+        <v>0.0888634398417833</v>
       </c>
       <c r="T55">
         <v>0.9945367169003071</v>
       </c>
       <c r="U55">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.0503818</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.014410599324821</v>
+        <v>2.133829636414279</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07407600043434773</v>
+        <v>0.06693091457533333</v>
       </c>
       <c r="C56">
-        <v>8798.155820472071</v>
+        <v>19509.42562947173</v>
       </c>
       <c r="D56">
-        <v>31765.16382047207</v>
+        <v>42476.43362947174</v>
       </c>
       <c r="E56">
         <v>6585.407999999999</v>
@@ -5885,45 +5885,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M56">
-        <v>2254.4291952</v>
+        <v>1764.4555728</v>
       </c>
       <c r="N56">
-        <v>1440.895294595919</v>
+        <v>1930.868916995918</v>
       </c>
       <c r="O56">
-        <v>371.750986005747</v>
+        <v>498.164180584947</v>
       </c>
       <c r="P56">
-        <v>1069.144308590171</v>
+        <v>1432.704736410971</v>
       </c>
       <c r="Q56">
-        <v>3005.044308590172</v>
+        <v>3368.604736410972</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.08969632268336465</v>
+        <v>0.08966810125072462</v>
       </c>
       <c r="T56">
         <v>1.013120121263848</v>
       </c>
       <c r="U56">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.639139742185645</v>
+        <v>2.094314272776978</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07416516936923571</v>
+        <v>0.06688804642502849</v>
       </c>
       <c r="C57">
-        <v>8188.54664043754</v>
+        <v>19086.02046808077</v>
       </c>
       <c r="D57">
-        <v>31665.30664043754</v>
+        <v>42562.78046808077</v>
       </c>
       <c r="E57">
         <v>7095.16</v>
@@ -5967,45 +5967,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M57">
-        <v>2296.177884</v>
+        <v>1797.130676</v>
       </c>
       <c r="N57">
-        <v>1399.146605795918</v>
+        <v>1898.193813795918</v>
       </c>
       <c r="O57">
-        <v>360.9798242953469</v>
+        <v>489.7340039593469</v>
       </c>
       <c r="P57">
-        <v>1038.166781500571</v>
+        <v>1408.459809836571</v>
       </c>
       <c r="Q57">
-        <v>2974.066781500572</v>
+        <v>3344.359809836572</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09053728748719048</v>
+        <v>0.09050852538895221</v>
       </c>
       <c r="T57">
         <v>1.032529454710213</v>
       </c>
       <c r="U57">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.609337201418633</v>
+        <v>2.05623583145376</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07425433830412367</v>
+        <v>0.06684517827472367</v>
       </c>
       <c r="C58">
-        <v>7579.563316347347</v>
+        <v>18662.96707650684</v>
       </c>
       <c r="D58">
-        <v>31566.07531634735</v>
+        <v>42649.47907650684</v>
       </c>
       <c r="E58">
         <v>7604.912</v>
@@ -6049,45 +6049,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M58">
-        <v>2337.9265728</v>
+        <v>1829.8057792</v>
       </c>
       <c r="N58">
-        <v>1357.397916995918</v>
+        <v>1865.518710595918</v>
       </c>
       <c r="O58">
-        <v>350.208662584947</v>
+        <v>481.3038273337469</v>
       </c>
       <c r="P58">
-        <v>1007.189254410971</v>
+        <v>1384.214883262171</v>
       </c>
       <c r="Q58">
-        <v>2943.089254410972</v>
+        <v>3320.114883262172</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09141647796391747</v>
+        <v>0.09138715062437197</v>
       </c>
       <c r="T58">
         <v>1.052821030585958</v>
       </c>
       <c r="U58">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0607698</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.580599037107586</v>
+        <v>2.019517334463514</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07434350723901166</v>
+        <v>0.07010124212441883</v>
       </c>
       <c r="C59">
-        <v>6971.199982744103</v>
+        <v>12438.71594439034</v>
       </c>
       <c r="D59">
-        <v>31467.46398274411</v>
+        <v>36934.97994439034</v>
       </c>
       <c r="E59">
         <v>8114.664000000001</v>
@@ -6131,45 +6131,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M59">
-        <v>2379.6752616</v>
+        <v>2089.1166216</v>
       </c>
       <c r="N59">
-        <v>1315.649228195918</v>
+        <v>1606.207868195918</v>
       </c>
       <c r="O59">
-        <v>339.4375008745469</v>
+        <v>414.4016299945469</v>
       </c>
       <c r="P59">
-        <v>976.2117273213712</v>
+        <v>1191.806238201371</v>
       </c>
       <c r="Q59">
-        <v>2912.111727321372</v>
+        <v>3127.706238201372</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09233656102095736</v>
+        <v>0.09230664214981124</v>
       </c>
       <c r="T59">
         <v>1.074056400688481</v>
       </c>
       <c r="U59">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0607698</v>
+        <v>0.0533498</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.552869229439032</v>
+        <v>1.768845478317896</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07443267617389965</v>
+        <v>0.07179465397411401</v>
       </c>
       <c r="C60">
-        <v>6363.450847236214</v>
+        <v>9522.848718991721</v>
       </c>
       <c r="D60">
-        <v>31369.46684723621</v>
+        <v>34528.86471899172</v>
       </c>
       <c r="E60">
         <v>8624.415999999994</v>
@@ -6213,37 +6213,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M60">
-        <v>2421.4239504</v>
+        <v>2241.0736928</v>
       </c>
       <c r="N60">
-        <v>1273.900539395919</v>
+        <v>1454.250796995919</v>
       </c>
       <c r="O60">
-        <v>328.666339164147</v>
+        <v>375.1967056249471</v>
       </c>
       <c r="P60">
-        <v>945.2342002317716</v>
+        <v>1079.054091370972</v>
       </c>
       <c r="Q60">
-        <v>2881.134200231772</v>
+        <v>3014.954091370972</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09330045755690392</v>
+        <v>0.09326991898598574</v>
       </c>
       <c r="T60">
         <v>1.096302978891125</v>
       </c>
       <c r="U60">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.526095622034911</v>
+        <v>1.648908066552232</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07452184510878762</v>
+        <v>0.07183859982380918</v>
       </c>
       <c r="C61">
-        <v>5756.310189363539</v>
+        <v>8954.821684644521</v>
       </c>
       <c r="D61">
-        <v>31272.07818936353</v>
+        <v>34470.58968464452</v>
       </c>
       <c r="E61">
         <v>9134.167999999994</v>
@@ -6295,37 +6295,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M61">
-        <v>2463.1726392</v>
+        <v>2279.7128944</v>
       </c>
       <c r="N61">
-        <v>1232.151850595919</v>
+        <v>1415.611595395919</v>
       </c>
       <c r="O61">
-        <v>317.8951774537471</v>
+        <v>365.2277916121471</v>
       </c>
       <c r="P61">
-        <v>914.2566731421718</v>
+        <v>1050.383803783772</v>
       </c>
       <c r="Q61">
-        <v>2850.156673142173</v>
+        <v>2986.283803783772</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.09431137343606735</v>
+        <v>0.09428018493611995</v>
       </c>
       <c r="T61">
         <v>1.119634756030484</v>
       </c>
       <c r="U61">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.0607698</v>
+        <v>0.0562436</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.500229594542794</v>
+        <v>1.620960472203889</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09826568095423324</v>
+        <v>0.07188254567350436</v>
       </c>
       <c r="C62">
-        <v>-8905.914009022694</v>
+        <v>8386.991022686139</v>
       </c>
       <c r="D62">
-        <v>17119.6059909773</v>
+        <v>34412.51102268614</v>
       </c>
       <c r="E62">
         <v>9643.919999999995</v>
@@ -6377,45 +6377,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M62">
-        <v>4003.592207999999</v>
+        <v>2318.352096</v>
       </c>
       <c r="N62">
-        <v>-308.2677182040807</v>
+        <v>1376.972393795919</v>
       </c>
       <c r="O62">
-        <v>-79.53307129665281</v>
+        <v>355.258877599347</v>
       </c>
       <c r="P62">
-        <v>-228.7346469074279</v>
+        <v>1021.713516196572</v>
       </c>
       <c r="Q62">
-        <v>1707.165353092573</v>
+        <v>2957.613516196572</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09607192566903014</v>
+        <v>0.09534096418376087</v>
       </c>
       <c r="T62">
-        <v>1.16026802056648</v>
+        <v>1.14413312202681</v>
       </c>
       <c r="U62">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
-        <v>0.2381345723628572</v>
+        <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.09972818447770199</v>
+        <v>0.0562436</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9230022184606868</v>
+        <v>1.593944464333824</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09911668095423326</v>
+        <v>0.07192649152319952</v>
       </c>
       <c r="C63">
-        <v>-9688.916039549309</v>
+        <v>7819.355742196938</v>
       </c>
       <c r="D63">
-        <v>16846.35596045068</v>
+        <v>34354.62774219694</v>
       </c>
       <c r="E63">
         <v>10153.672</v>
@@ -6459,45 +6459,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M63">
-        <v>4070.318744799999</v>
+        <v>2356.9912976</v>
       </c>
       <c r="N63">
-        <v>-374.9942550040805</v>
+        <v>1338.333192195918</v>
       </c>
       <c r="O63">
-        <v>-96.74851779105278</v>
+        <v>345.2899635865469</v>
       </c>
       <c r="P63">
-        <v>-278.2457372130277</v>
+        <v>993.0432286093715</v>
       </c>
       <c r="Q63">
-        <v>1657.654262786973</v>
+        <v>2928.943228609372</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09736094940413349</v>
+        <v>0.09645614236717825</v>
       </c>
       <c r="T63">
-        <v>1.190018482632287</v>
+        <v>1.169887814484486</v>
       </c>
       <c r="U63">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
-        <v>0.2342307269142858</v>
+        <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.10023919784692</v>
+        <v>0.0562436</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.9078710345514952</v>
+        <v>1.567814227213598</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09996768095423325</v>
+        <v>0.07197043737289469</v>
       </c>
       <c r="C64">
-        <v>-10463.33229450341</v>
+        <v>7251.914858913093</v>
       </c>
       <c r="D64">
-        <v>16581.69170549659</v>
+        <v>34296.93885891309</v>
       </c>
       <c r="E64">
         <v>10663.424</v>
@@ -6541,45 +6541,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M64">
-        <v>4137.045281599999</v>
+        <v>2395.6304992</v>
       </c>
       <c r="N64">
-        <v>-441.7207918040804</v>
+        <v>1299.693990595918</v>
       </c>
       <c r="O64">
-        <v>-113.9639642854527</v>
+        <v>335.321049573747</v>
       </c>
       <c r="P64">
-        <v>-327.7568275186276</v>
+        <v>964.3729410221715</v>
       </c>
       <c r="Q64">
-        <v>1608.143172481373</v>
+        <v>2900.272941022172</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.09871781649371594</v>
+        <v>0.09763001413919656</v>
       </c>
       <c r="T64">
-        <v>1.221334758491031</v>
+        <v>1.196998017071514</v>
       </c>
       <c r="U64">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
-        <v>0.2304528119640554</v>
+        <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.1007337269139051</v>
+        <v>0.0562436</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8932279533490518</v>
+        <v>1.542526900968217</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1008186809542333</v>
+        <v>0.07201438322258988</v>
       </c>
       <c r="C65">
-        <v>-11229.56117465828</v>
+        <v>6684.667395170876</v>
       </c>
       <c r="D65">
-        <v>16325.21482534172</v>
+        <v>34239.44339517088</v>
       </c>
       <c r="E65">
         <v>11173.176</v>
@@ -6623,45 +6623,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M65">
-        <v>4203.7718184</v>
+        <v>2434.2697008</v>
       </c>
       <c r="N65">
-        <v>-508.4473286040811</v>
+        <v>1261.054788995918</v>
       </c>
       <c r="O65">
-        <v>-131.1794107798529</v>
+        <v>325.352135560947</v>
       </c>
       <c r="P65">
-        <v>-377.2679178242282</v>
+        <v>935.7026534349715</v>
       </c>
       <c r="Q65">
-        <v>1558.632082175772</v>
+        <v>2871.602653434972</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1001480277503029</v>
+        <v>0.09886733843943207</v>
       </c>
       <c r="T65">
-        <v>1.254343806017816</v>
+        <v>1.225573636014597</v>
       </c>
       <c r="U65">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
-        <v>0.2267948308217687</v>
+        <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.1012125566454305</v>
+        <v>0.0562436</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8790497318673206</v>
+        <v>1.518042346984594</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1016696809542333</v>
+        <v>0.07880162507228503</v>
       </c>
       <c r="C66">
-        <v>-11987.97680722397</v>
+        <v>-866.9009582042672</v>
       </c>
       <c r="D66">
-        <v>16076.55119277603</v>
+        <v>27197.62704179573</v>
       </c>
       <c r="E66">
         <v>11682.928</v>
@@ -6705,45 +6705,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M66">
-        <v>4270.498355199999</v>
+        <v>2936.17152</v>
       </c>
       <c r="N66">
-        <v>-575.173865404081</v>
+        <v>759.1529697959186</v>
       </c>
       <c r="O66">
-        <v>-148.3948572742529</v>
+        <v>195.861466207347</v>
       </c>
       <c r="P66">
-        <v>-426.7790081298281</v>
+        <v>563.2915035885716</v>
       </c>
       <c r="Q66">
-        <v>1509.120991870172</v>
+        <v>2499.191503588572</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1016576951878113</v>
+        <v>0.1001734029785695</v>
       </c>
       <c r="T66">
-        <v>1.289186689518311</v>
+        <v>1.255736789343407</v>
       </c>
       <c r="U66">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
-        <v>0.2232511615901786</v>
+        <v>0.258</v>
       </c>
       <c r="W66">
-        <v>0.1016764229478456</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8653145798068937</v>
+        <v>1.258551983296915</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1025206809542333</v>
+        <v>0.0941653293906938</v>
       </c>
       <c r="C67">
-        <v>-12738.93086677066</v>
+        <v>-10016.23642215789</v>
       </c>
       <c r="D67">
-        <v>15835.34913322934</v>
+        <v>18558.04357784211</v>
       </c>
       <c r="E67">
         <v>12192.68</v>
@@ -6787,37 +6787,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M67">
-        <v>4337.224891999999</v>
+        <v>3929.678168</v>
       </c>
       <c r="N67">
-        <v>-641.9004022040808</v>
+        <v>-234.3536782040815</v>
       </c>
       <c r="O67">
-        <v>-165.6103037686529</v>
+        <v>-60.46324897665302</v>
       </c>
       <c r="P67">
-        <v>-476.2900984354279</v>
+        <v>-173.8904292274285</v>
       </c>
       <c r="Q67">
-        <v>1459.609901564573</v>
+        <v>1762.009570772572</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1032536293360345</v>
+        <v>0.1022240534402074</v>
       </c>
       <c r="T67">
-        <v>1.32602059493312</v>
+        <v>1.303095922406638</v>
       </c>
       <c r="U67">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.2198165283349451</v>
+        <v>0.2426136893679958</v>
       </c>
       <c r="W67">
-        <v>0.1021260164409557</v>
+        <v>0.0898260164409557</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8520020478098647</v>
+        <v>0.9403631370852552</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1033716809542333</v>
+        <v>0.0948933293906938</v>
       </c>
       <c r="C68">
-        <v>-13482.75423465535</v>
+        <v>-10801.183767276</v>
       </c>
       <c r="D68">
-        <v>15601.27776534465</v>
+        <v>18282.848232724</v>
       </c>
       <c r="E68">
         <v>12702.432</v>
@@ -6869,37 +6869,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M68">
-        <v>4403.951428799999</v>
+        <v>3990.1347552</v>
       </c>
       <c r="N68">
-        <v>-708.6269390040807</v>
+        <v>-294.8102654040817</v>
       </c>
       <c r="O68">
-        <v>-182.8257502630528</v>
+        <v>-76.0610484742531</v>
       </c>
       <c r="P68">
-        <v>-525.8011887410279</v>
+        <v>-218.7492169298287</v>
       </c>
       <c r="Q68">
-        <v>1410.098811258973</v>
+        <v>1717.150783070172</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1049434419635649</v>
+        <v>0.1038835844237429</v>
       </c>
       <c r="T68">
-        <v>1.365021200666447</v>
+        <v>1.341422273065656</v>
       </c>
       <c r="U68">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2164859748753247</v>
+        <v>0.2389377243775717</v>
       </c>
       <c r="W68">
-        <v>0.10256198588882</v>
+        <v>0.09026198588882001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8390929258733516</v>
+        <v>0.9261152107657815</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1042226809542332</v>
+        <v>0.09562132939069379</v>
       </c>
       <c r="C69">
-        <v>-14219.75851341861</v>
+        <v>-11578.08868503634</v>
       </c>
       <c r="D69">
-        <v>15374.02548658139</v>
+        <v>18015.69531496366</v>
       </c>
       <c r="E69">
         <v>13212.184</v>
@@ -6951,37 +6951,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M69">
-        <v>4470.677965599999</v>
+        <v>4050.5913424</v>
       </c>
       <c r="N69">
-        <v>-775.3534758040805</v>
+        <v>-355.2668526040816</v>
       </c>
       <c r="O69">
-        <v>-200.0411967574528</v>
+        <v>-91.65884797185305</v>
       </c>
       <c r="P69">
-        <v>-575.3122790466277</v>
+        <v>-263.6080046322285</v>
       </c>
       <c r="Q69">
-        <v>1360.587720953373</v>
+        <v>1672.291995367772</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1067356674776123</v>
+        <v>0.1056436930426442</v>
       </c>
       <c r="T69">
-        <v>1.406385479474521</v>
+        <v>1.382071432855525</v>
       </c>
       <c r="U69">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2132548409219616</v>
+        <v>0.2353714896853691</v>
       </c>
       <c r="W69">
-        <v>0.1029849413233152</v>
+        <v>0.09068494132331523</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8265691508603166</v>
+        <v>0.9122925956797252</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1050736809542333</v>
+        <v>0.09634932939069379</v>
       </c>
       <c r="C70">
-        <v>-14950.2374107271</v>
+        <v>-12347.29865109411</v>
       </c>
       <c r="D70">
-        <v>15153.2985892729</v>
+        <v>17756.23734890589</v>
       </c>
       <c r="E70">
         <v>13721.936</v>
@@ -7033,37 +7033,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M70">
-        <v>4537.4045024</v>
+        <v>4111.0479296</v>
       </c>
       <c r="N70">
-        <v>-842.0800126040813</v>
+        <v>-415.7234398040819</v>
       </c>
       <c r="O70">
-        <v>-217.256643251853</v>
+        <v>-107.2566474694531</v>
       </c>
       <c r="P70">
-        <v>-624.8233693522283</v>
+        <v>-308.4667923346287</v>
       </c>
       <c r="Q70">
-        <v>1311.076630647772</v>
+        <v>1627.433207665372</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1086399070862877</v>
+        <v>0.1075138084502269</v>
       </c>
       <c r="T70">
-        <v>1.4503350257081</v>
+        <v>1.42526116513226</v>
       </c>
       <c r="U70">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2101187403201681</v>
+        <v>0.2319101442488196</v>
       </c>
       <c r="W70">
-        <v>0.10339545689209</v>
+        <v>0.09109545689209</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.814413722171194</v>
+        <v>0.8988765280961998</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1059246809542333</v>
+        <v>0.0970773293906938</v>
       </c>
       <c r="C71">
-        <v>-15674.4680057867</v>
+        <v>-13109.14140822995</v>
       </c>
       <c r="D71">
-        <v>14938.8199942133</v>
+        <v>17504.14659177005</v>
       </c>
       <c r="E71">
         <v>14231.688</v>
@@ -7115,37 +7115,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M71">
-        <v>4604.1310392</v>
+        <v>4171.504516800001</v>
       </c>
       <c r="N71">
-        <v>-908.8065494040811</v>
+        <v>-476.1800270040821</v>
       </c>
       <c r="O71">
-        <v>-234.4720897462529</v>
+        <v>-122.8544469670532</v>
       </c>
       <c r="P71">
-        <v>-674.3344596578281</v>
+        <v>-353.3255800370289</v>
       </c>
       <c r="Q71">
-        <v>1261.565540342172</v>
+        <v>1582.574419962972</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1106670008632647</v>
+        <v>0.1095045764647503</v>
       </c>
       <c r="T71">
-        <v>1.497120026537394</v>
+        <v>1.47123733174943</v>
       </c>
       <c r="U71">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2070735411850932</v>
+        <v>0.2285491276655033</v>
       </c>
       <c r="W71">
-        <v>0.1037940734588713</v>
+        <v>0.09149407345887133</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8026106247484232</v>
+        <v>0.8858493320368345</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1675244665995922</v>
+        <v>0.09780532939069381</v>
       </c>
       <c r="C72">
-        <v>-23744.14723442838</v>
+        <v>-13863.92634750961</v>
       </c>
       <c r="D72">
-        <v>7378.892765571617</v>
+        <v>17259.11365249039</v>
       </c>
       <c r="E72">
         <v>14741.44</v>
@@ -7197,45 +7197,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M72">
-        <v>7700.313712</v>
+        <v>4231.961104</v>
       </c>
       <c r="N72">
-        <v>-4004.989222204082</v>
+        <v>-536.6366142040815</v>
       </c>
       <c r="O72">
-        <v>-1033.287219328653</v>
+        <v>-138.452246464653</v>
       </c>
       <c r="P72">
-        <v>-2971.702002875429</v>
+        <v>-398.1843677394285</v>
       </c>
       <c r="Q72">
-        <v>-1035.802002875428</v>
+        <v>1537.715632260572</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1172251863765698</v>
+        <v>0.1116280623469087</v>
       </c>
       <c r="T72">
-        <v>1.648481901436049</v>
+        <v>1.520278576141078</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.1238123216826347</v>
+        <v>0.2252841401274247</v>
       </c>
       <c r="W72">
-        <v>0.1890813009808875</v>
+        <v>0.09188130098088744</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.4798927197001345</v>
+        <v>0.8731943415791655</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1692244665995922</v>
+        <v>0.09853332939069381</v>
       </c>
       <c r="C73">
-        <v>-24355.53319766977</v>
+        <v>-14611.9457750396</v>
       </c>
       <c r="D73">
-        <v>7277.258802330222</v>
+        <v>17020.84622496039</v>
       </c>
       <c r="E73">
         <v>15251.19199999999</v>
@@ -7279,45 +7279,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M73">
-        <v>7810.318193599999</v>
+        <v>4292.417691199999</v>
       </c>
       <c r="N73">
-        <v>-4114.993703804081</v>
+        <v>-597.0932014040809</v>
       </c>
       <c r="O73">
-        <v>-1061.668375581453</v>
+        <v>-154.0500459622529</v>
       </c>
       <c r="P73">
-        <v>-3053.325328222628</v>
+        <v>-443.043155441828</v>
       </c>
       <c r="Q73">
-        <v>-1117.425328222627</v>
+        <v>1492.856844558172</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1196881238378308</v>
+        <v>0.1138979955312848</v>
       </c>
       <c r="T73">
-        <v>1.705326104933844</v>
+        <v>1.572701975318356</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.1220684861659779</v>
+        <v>0.222111124069292</v>
       </c>
       <c r="W73">
-        <v>0.189457620685382</v>
+        <v>0.09225762068538197</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4731336673099918</v>
+        <v>0.8608958297259379</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1709244665995922</v>
+        <v>0.09926132939069379</v>
       </c>
       <c r="C74">
-        <v>-24964.15746702018</v>
+        <v>-15353.47607522397</v>
       </c>
       <c r="D74">
-        <v>7178.386532979816</v>
+        <v>16789.06792477603</v>
       </c>
       <c r="E74">
         <v>15760.94399999999</v>
@@ -7361,45 +7361,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M74">
-        <v>7920.322675199999</v>
+        <v>4352.8742784</v>
       </c>
       <c r="N74">
-        <v>-4224.998185404081</v>
+        <v>-657.5497886040812</v>
       </c>
       <c r="O74">
-        <v>-1090.049531834253</v>
+        <v>-169.647845459853</v>
       </c>
       <c r="P74">
-        <v>-3134.948653569828</v>
+        <v>-487.9019431442282</v>
       </c>
       <c r="Q74">
-        <v>-1199.048653569827</v>
+        <v>1447.998056855772</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1223269854034676</v>
+        <v>0.1163300668002593</v>
       </c>
       <c r="T74">
-        <v>1.766230608681481</v>
+        <v>1.628869903008297</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.1203730905247838</v>
+        <v>0.2190262473461074</v>
       </c>
       <c r="W74">
-        <v>0.1898234870647517</v>
+        <v>0.09262348706475167</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4665623663751308</v>
+        <v>0.8489389432019665</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1726244665995921</v>
+        <v>0.0999893293906938</v>
       </c>
       <c r="C75">
-        <v>-25570.13109864425</v>
+        <v>-16088.77878025512</v>
       </c>
       <c r="D75">
-        <v>7082.164901355739</v>
+        <v>16563.51721974487</v>
       </c>
       <c r="E75">
         <v>16270.69599999999</v>
@@ -7443,45 +7443,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M75">
-        <v>8030.327156799999</v>
+        <v>4413.3308656</v>
       </c>
       <c r="N75">
-        <v>-4335.002667004081</v>
+        <v>-718.0063758040815</v>
       </c>
       <c r="O75">
-        <v>-1118.430688087053</v>
+        <v>-185.245644957453</v>
       </c>
       <c r="P75">
-        <v>-3216.571978917028</v>
+        <v>-532.7607308466285</v>
       </c>
       <c r="Q75">
-        <v>-1280.671978917027</v>
+        <v>1403.139269153372</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1251613181961887</v>
+        <v>0.1189422914965652</v>
       </c>
       <c r="T75">
-        <v>1.831646557151165</v>
+        <v>1.68919841793453</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.1187241440792388</v>
+        <v>0.216025887793421</v>
       </c>
       <c r="W75">
-        <v>0.1901793297077003</v>
+        <v>0.09297932970770029</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4601711010823208</v>
+        <v>0.8373096426101587</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1743244665995921</v>
+        <v>0.1007173293906938</v>
       </c>
       <c r="C76">
-        <v>-26173.5592729233</v>
+        <v>-16818.10155454004</v>
       </c>
       <c r="D76">
-        <v>6988.488727076696</v>
+        <v>16343.94644545995</v>
       </c>
       <c r="E76">
         <v>16780.44799999999</v>
@@ -7525,45 +7525,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M76">
-        <v>8140.331638399999</v>
+        <v>4473.787452799999</v>
       </c>
       <c r="N76">
-        <v>-4445.007148604081</v>
+        <v>-778.4629630040808</v>
       </c>
       <c r="O76">
-        <v>-1146.811844339853</v>
+        <v>-200.8434444550529</v>
       </c>
       <c r="P76">
-        <v>-3298.195304264228</v>
+        <v>-577.619518549028</v>
       </c>
       <c r="Q76">
-        <v>-1362.295304264228</v>
+        <v>1358.280481450973</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1282136765883498</v>
+        <v>0.1217554565541254</v>
       </c>
       <c r="T76">
-        <v>1.902094501656979</v>
+        <v>1.754167587855089</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.1171197637538437</v>
+        <v>0.2131066190394558</v>
       </c>
       <c r="W76">
-        <v>0.1905255549819206</v>
+        <v>0.09332555498192055</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4539525726893165</v>
+        <v>0.8259946474397513</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1760244665995921</v>
+        <v>0.1014453293906938</v>
       </c>
       <c r="C77">
-        <v>-26774.5416779789</v>
+        <v>-17541.67910185156</v>
       </c>
       <c r="D77">
-        <v>6897.258322021095</v>
+        <v>16130.12089814843</v>
       </c>
       <c r="E77">
         <v>17290.19999999999</v>
@@ -7607,45 +7607,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M77">
-        <v>8250.33612</v>
+        <v>4534.24404</v>
       </c>
       <c r="N77">
-        <v>-4555.011630204081</v>
+        <v>-838.9195502040811</v>
       </c>
       <c r="O77">
-        <v>-1175.193000592653</v>
+        <v>-216.4412439526529</v>
       </c>
       <c r="P77">
-        <v>-3379.818629611428</v>
+        <v>-622.4783062514282</v>
       </c>
       <c r="Q77">
-        <v>-1443.918629611428</v>
+        <v>1313.421693748572</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1315102236518838</v>
+        <v>0.1247936748162904</v>
       </c>
       <c r="T77">
-        <v>1.978178281723259</v>
+        <v>1.824334291369293</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.1155581669037924</v>
+        <v>0.2102651974522631</v>
       </c>
       <c r="W77">
-        <v>0.1908625475821616</v>
+        <v>0.0936625475821616</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4478998717201256</v>
+        <v>0.8149813854738879</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1777244665995922</v>
+        <v>0.1021733293906938</v>
       </c>
       <c r="C78">
-        <v>-27373.17286354366</v>
+        <v>-18259.73400219065</v>
       </c>
       <c r="D78">
-        <v>6808.37913645634</v>
+        <v>15921.81799780935</v>
       </c>
       <c r="E78">
         <v>17799.952</v>
@@ -7689,45 +7689,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M78">
-        <v>8360.340601600001</v>
+        <v>4594.700627200001</v>
       </c>
       <c r="N78">
-        <v>-4665.016111804082</v>
+        <v>-899.3761374040823</v>
       </c>
       <c r="O78">
-        <v>-1203.574156845453</v>
+        <v>-232.0390434502532</v>
       </c>
       <c r="P78">
-        <v>-3461.441954958629</v>
+        <v>-667.337093953829</v>
       </c>
       <c r="Q78">
-        <v>-1525.541954958629</v>
+        <v>1268.562906046172</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1350814829707123</v>
+        <v>0.1280850779336358</v>
       </c>
       <c r="T78">
-        <v>2.060602376795062</v>
+        <v>1.900348220176347</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.1140376647076899</v>
+        <v>0.2074985501173648</v>
       </c>
       <c r="W78">
-        <v>0.1911906719560806</v>
+        <v>0.09399067195608053</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.442006452355387</v>
+        <v>0.8042579461913365</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1794244665995922</v>
+        <v>0.1677088966525997</v>
       </c>
       <c r="C79">
-        <v>-27969.54256781976</v>
+        <v>-27328.70852801447</v>
       </c>
       <c r="D79">
-        <v>6721.761432180236</v>
+        <v>7362.595471985532</v>
       </c>
       <c r="E79">
         <v>18309.704</v>
@@ -7771,37 +7771,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M79">
-        <v>8470.345083200002</v>
+        <v>7881.5815232</v>
       </c>
       <c r="N79">
-        <v>-4775.020593404083</v>
+        <v>-4186.257033404082</v>
       </c>
       <c r="O79">
-        <v>-1231.955313098254</v>
+        <v>-1080.054314618253</v>
       </c>
       <c r="P79">
-        <v>-3543.06528030583</v>
+        <v>-3106.202718785829</v>
       </c>
       <c r="Q79">
-        <v>-1607.165280305829</v>
+        <v>-1170.302718785828</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1389632865781345</v>
+        <v>0.1382434172433848</v>
       </c>
       <c r="T79">
-        <v>2.150193784481803</v>
+        <v>2.13495189938533</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1125566560751224</v>
+        <v>0.1209647728138019</v>
       </c>
       <c r="W79">
-        <v>0.1915102736189886</v>
+        <v>0.1765102736189886</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4362661088183041</v>
+        <v>0.4688557085806276</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1811244665995921</v>
+        <v>0.1692588966525997</v>
       </c>
       <c r="C80">
-        <v>-28563.73601970087</v>
+        <v>-27930.89633694357</v>
       </c>
       <c r="D80">
-        <v>6637.319980299128</v>
+        <v>7270.159663056429</v>
       </c>
       <c r="E80">
         <v>18819.456</v>
@@ -7853,37 +7853,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M80">
-        <v>8580.349564800001</v>
+        <v>7983.9397248</v>
       </c>
       <c r="N80">
-        <v>-4885.025075004082</v>
+        <v>-4288.615235004082</v>
       </c>
       <c r="O80">
-        <v>-1260.336469351053</v>
+        <v>-1106.462730631053</v>
       </c>
       <c r="P80">
-        <v>-3624.688605653029</v>
+        <v>-3182.152504373029</v>
       </c>
       <c r="Q80">
-        <v>-1688.788605653029</v>
+        <v>-1246.252504373028</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1431979814225952</v>
+        <v>0.1424453907544477</v>
       </c>
       <c r="T80">
-        <v>2.247929865594612</v>
+        <v>2.231995167539208</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1111136220228773</v>
+        <v>0.1194139423931122</v>
       </c>
       <c r="W80">
-        <v>0.1918216803674631</v>
+        <v>0.1768216803674631</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4306729535770438</v>
+        <v>0.462844737957799</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1828244665995922</v>
+        <v>0.1708088966525997</v>
       </c>
       <c r="C81">
-        <v>-29155.83421849675</v>
+        <v>-28530.79190095769</v>
       </c>
       <c r="D81">
-        <v>6554.973781503251</v>
+        <v>7180.016099042316</v>
       </c>
       <c r="E81">
         <v>19329.208</v>
@@ -7935,37 +7935,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M81">
-        <v>8690.354046400002</v>
+        <v>8086.297926400001</v>
       </c>
       <c r="N81">
-        <v>-4995.029556604083</v>
+        <v>-4390.973436604082</v>
       </c>
       <c r="O81">
-        <v>-1288.717625603854</v>
+        <v>-1132.871146643853</v>
       </c>
       <c r="P81">
-        <v>-3706.311931000229</v>
+        <v>-3258.102289960229</v>
       </c>
       <c r="Q81">
-        <v>-1770.411931000229</v>
+        <v>-1322.202289960228</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1478359805379569</v>
+        <v>0.1470475522189452</v>
       </c>
       <c r="T81">
-        <v>2.354974144908642</v>
+        <v>2.338280651707742</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1097071204782839</v>
+        <v>0.1179023735020601</v>
       </c>
       <c r="W81">
-        <v>0.1921252034007863</v>
+        <v>0.1771252034007863</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4252213972026507</v>
+        <v>0.4569859438064345</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1845244665995922</v>
+        <v>0.1723588966525997</v>
       </c>
       <c r="C82">
-        <v>-29745.91419309058</v>
+        <v>-29128.4794412308</v>
       </c>
       <c r="D82">
-        <v>6474.645806909419</v>
+        <v>7092.080558769201</v>
       </c>
       <c r="E82">
         <v>19838.96</v>
@@ -8017,37 +8017,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M82">
-        <v>8800.358528000001</v>
+        <v>8188.656128000001</v>
       </c>
       <c r="N82">
-        <v>-5105.034038204082</v>
+        <v>-4493.331638204082</v>
       </c>
       <c r="O82">
-        <v>-1317.098781856653</v>
+        <v>-1159.279562656653</v>
       </c>
       <c r="P82">
-        <v>-3787.935256347429</v>
+        <v>-3334.052075547429</v>
       </c>
       <c r="Q82">
-        <v>-1852.035256347428</v>
+        <v>-1398.152075547428</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1529377795648547</v>
+        <v>0.1521099298298925</v>
       </c>
       <c r="T82">
-        <v>2.472722852154074</v>
+        <v>2.455194684293129</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1083357814723054</v>
+        <v>0.1164285938332844</v>
       </c>
       <c r="W82">
-        <v>0.1924211383582765</v>
+        <v>0.1774211383582765</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4199061297376177</v>
+        <v>0.451273619508854</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1862244665995921</v>
+        <v>0.1739088966525997</v>
       </c>
       <c r="C83">
-        <v>-30334.04924227198</v>
+        <v>-29724.03910294146</v>
       </c>
       <c r="D83">
-        <v>6396.262757728029</v>
+        <v>7006.272897058539</v>
       </c>
       <c r="E83">
         <v>20348.712</v>
@@ -8099,37 +8099,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M83">
-        <v>8910.363009600002</v>
+        <v>8291.014329600001</v>
       </c>
       <c r="N83">
-        <v>-5215.038519804083</v>
+        <v>-4595.689839804082</v>
       </c>
       <c r="O83">
-        <v>-1345.479938109454</v>
+        <v>-1185.687978669453</v>
       </c>
       <c r="P83">
-        <v>-3869.55858169463</v>
+        <v>-3410.001861134629</v>
       </c>
       <c r="Q83">
-        <v>-1933.658581694629</v>
+        <v>-1474.101861134628</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1585766100682681</v>
+        <v>0.1577051892946237</v>
       </c>
       <c r="T83">
-        <v>2.602866160162183</v>
+        <v>2.584415457150663</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1069983026886966</v>
+        <v>0.1149912037859599</v>
       </c>
       <c r="W83">
-        <v>0.1927097662797793</v>
+        <v>0.1777097662797793</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4147221034445606</v>
+        <v>0.4457023402556584</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1879244665995922</v>
+        <v>0.1754588966525997</v>
       </c>
       <c r="C84">
-        <v>-30920.3091578216</v>
+        <v>-30317.54719890407</v>
       </c>
       <c r="D84">
-        <v>6319.754842178398</v>
+        <v>6922.516801095936</v>
       </c>
       <c r="E84">
         <v>20858.464</v>
@@ -8181,37 +8181,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M84">
-        <v>9020.367491200002</v>
+        <v>8393.372531200001</v>
       </c>
       <c r="N84">
-        <v>-5325.043001404084</v>
+        <v>-4698.048041404082</v>
       </c>
       <c r="O84">
-        <v>-1373.861094362254</v>
+        <v>-1212.096394682253</v>
       </c>
       <c r="P84">
-        <v>-3951.181907041831</v>
+        <v>-3485.951646721829</v>
       </c>
       <c r="Q84">
-        <v>-2015.28190704183</v>
+        <v>-1550.051646721829</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.164841977294283</v>
+        <v>0.1639221442554362</v>
       </c>
       <c r="T84">
-        <v>2.747469835726749</v>
+        <v>2.727994093659033</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1056934453388345</v>
+        <v>0.1135888720324725</v>
       </c>
       <c r="W84">
-        <v>0.1929913544958795</v>
+        <v>0.1779913544958795</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4096645168171879</v>
+        <v>0.4402669458622966</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1896244665995922</v>
+        <v>0.1770088966525997</v>
       </c>
       <c r="C85">
-        <v>-31504.76043177486</v>
+        <v>-30909.07643593174</v>
       </c>
       <c r="D85">
-        <v>6245.055568225144</v>
+        <v>6840.739564068265</v>
       </c>
       <c r="E85">
         <v>21368.216</v>
@@ -8263,37 +8263,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M85">
-        <v>9130.371972800001</v>
+        <v>8495.730732800001</v>
       </c>
       <c r="N85">
-        <v>-5435.047483004083</v>
+        <v>-4800.406243004082</v>
       </c>
       <c r="O85">
-        <v>-1402.242250615054</v>
+        <v>-1238.504810695053</v>
       </c>
       <c r="P85">
-        <v>-4032.80523238903</v>
+        <v>-3561.901432309029</v>
       </c>
       <c r="Q85">
-        <v>-2096.905232389029</v>
+        <v>-1626.001432309028</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.171844446546888</v>
+        <v>0.1708705056822265</v>
       </c>
       <c r="T85">
-        <v>2.909085708416558</v>
+        <v>2.888464334462506</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1044200303347522</v>
+        <v>0.1122203314055753</v>
       </c>
       <c r="W85">
-        <v>0.1932661574537605</v>
+        <v>0.1782661574537605</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4047287997471013</v>
+        <v>0.4349625248278112</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1913244665995922</v>
+        <v>0.1785588966525997</v>
       </c>
       <c r="C86">
-        <v>-32087.46644915801</v>
+        <v>-31498.69612534205</v>
       </c>
       <c r="D86">
-        <v>6172.101550841986</v>
+        <v>6760.871874657949</v>
       </c>
       <c r="E86">
         <v>21877.968</v>
@@ -8345,37 +8345,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M86">
-        <v>9240.376454400001</v>
+        <v>8598.088934400001</v>
       </c>
       <c r="N86">
-        <v>-5545.051964604082</v>
+        <v>-4902.764444604082</v>
       </c>
       <c r="O86">
-        <v>-1430.623406867853</v>
+        <v>-1264.913226707853</v>
       </c>
       <c r="P86">
-        <v>-4114.428557736229</v>
+        <v>-3637.851217896229</v>
       </c>
       <c r="Q86">
-        <v>-2178.528557736228</v>
+        <v>-1701.951217896229</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1797222244560684</v>
+        <v>0.1786874122873656</v>
       </c>
       <c r="T86">
-        <v>3.090903565192592</v>
+        <v>3.068993355366411</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1031769347355289</v>
+        <v>0.1108843750793184</v>
       </c>
       <c r="W86">
-        <v>0.1935344174840729</v>
+        <v>0.1785344174840729</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3999105997501121</v>
+        <v>0.429784399532242</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1930244665995922</v>
+        <v>0.1801088966525997</v>
       </c>
       <c r="C87">
-        <v>-32668.48766737138</v>
+        <v>-32086.47237888666</v>
       </c>
       <c r="D87">
-        <v>6100.832332628618</v>
+        <v>6682.847621113336</v>
       </c>
       <c r="E87">
         <v>22387.72</v>
@@ -8427,37 +8427,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M87">
-        <v>9350.380936</v>
+        <v>8700.447136000001</v>
       </c>
       <c r="N87">
-        <v>-5655.056446204081</v>
+        <v>-5005.122646204082</v>
       </c>
       <c r="O87">
-        <v>-1459.004563120653</v>
+        <v>-1291.321642720653</v>
       </c>
       <c r="P87">
-        <v>-4196.051883083428</v>
+        <v>-3713.801003483429</v>
       </c>
       <c r="Q87">
-        <v>-2260.151883083427</v>
+        <v>-1777.901003483428</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1886503727531396</v>
+        <v>0.1875465731065233</v>
       </c>
       <c r="T87">
-        <v>3.296963802872098</v>
+        <v>3.273592912390838</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1019630884445227</v>
+        <v>0.1095798530195617</v>
       </c>
       <c r="W87">
-        <v>0.193796365513672</v>
+        <v>0.178796365513672</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3952057691648166</v>
+        <v>0.4247281124789215</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1947244665995921</v>
+        <v>0.1816588966525997</v>
       </c>
       <c r="C88">
-        <v>-33247.88178328611</v>
+        <v>-32672.46829126888</v>
       </c>
       <c r="D88">
-        <v>6031.190216713886</v>
+        <v>6606.603708731118</v>
       </c>
       <c r="E88">
         <v>22897.472</v>
@@ -8509,37 +8509,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M88">
-        <v>9460.3854176</v>
+        <v>8802.805337600001</v>
       </c>
       <c r="N88">
-        <v>-5765.060927804082</v>
+        <v>-5107.480847804082</v>
       </c>
       <c r="O88">
-        <v>-1487.385719373453</v>
+        <v>-1317.730058733453</v>
       </c>
       <c r="P88">
-        <v>-4277.675208430629</v>
+        <v>-3789.750789070629</v>
       </c>
       <c r="Q88">
-        <v>-2341.775208430628</v>
+        <v>-1853.850789070629</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1988539708069353</v>
+        <v>0.1976713283284179</v>
       </c>
       <c r="T88">
-        <v>3.532461217362962</v>
+        <v>3.507420977561613</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1007774711370283</v>
+        <v>0.108305668682125</v>
       </c>
       <c r="W88">
-        <v>0.1940522217286293</v>
+        <v>0.1790522217286293</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3906103532442955</v>
+        <v>0.4197894134966085</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1964244665995922</v>
+        <v>0.1832088966525997</v>
       </c>
       <c r="C89">
-        <v>-33825.70388902577</v>
+        <v>-33256.74411030822</v>
       </c>
       <c r="D89">
-        <v>5963.120110974231</v>
+        <v>6532.079889691784</v>
       </c>
       <c r="E89">
         <v>23407.224</v>
@@ -8591,37 +8591,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M89">
-        <v>9570.389899200001</v>
+        <v>8905.163539200001</v>
       </c>
       <c r="N89">
-        <v>-5875.065409404083</v>
+        <v>-5209.839049404082</v>
       </c>
       <c r="O89">
-        <v>-1515.766875626254</v>
+        <v>-1344.138474746253</v>
       </c>
       <c r="P89">
-        <v>-4359.298533777829</v>
+        <v>-3865.700574657829</v>
       </c>
       <c r="Q89">
-        <v>-2423.398533777829</v>
+        <v>-1929.800574657828</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2106273531766996</v>
+        <v>0.2093537381998346</v>
       </c>
       <c r="T89">
-        <v>3.804189003313959</v>
+        <v>3.777222591220198</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09961910939982102</v>
+        <v>0.1070607759386523</v>
       </c>
       <c r="W89">
-        <v>0.1943021961915186</v>
+        <v>0.1793021961915186</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3861205790690737</v>
+        <v>0.4149642478242336</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1981244665995922</v>
+        <v>0.1847588966525997</v>
       </c>
       <c r="C90">
-        <v>-34402.00661731621</v>
+        <v>-33839.35739571648</v>
       </c>
       <c r="D90">
-        <v>5896.569382683787</v>
+        <v>6459.21860428352</v>
       </c>
       <c r="E90">
         <v>23916.976</v>
@@ -8673,37 +8673,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M90">
-        <v>9680.3943808</v>
+        <v>9007.521740800001</v>
       </c>
       <c r="N90">
-        <v>-5985.069891004082</v>
+        <v>-5312.197251004082</v>
       </c>
       <c r="O90">
-        <v>-1544.148031879053</v>
+        <v>-1370.546890759053</v>
       </c>
       <c r="P90">
-        <v>-4440.921859125028</v>
+        <v>-3941.650360245029</v>
       </c>
       <c r="Q90">
-        <v>-2505.021859125028</v>
+        <v>-2005.750360245029</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2243629659414245</v>
+        <v>0.2229832163831542</v>
       </c>
       <c r="T90">
-        <v>4.121204753590123</v>
+        <v>4.091991140488549</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09848707406573215</v>
+        <v>0.1058441762120767</v>
       </c>
       <c r="W90">
-        <v>0.194546489416615</v>
+        <v>0.179546489416615</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3817328452160161</v>
+        <v>0.4102487450080492</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1998244665995922</v>
+        <v>0.1863088966525998</v>
       </c>
       <c r="C91">
-        <v>-34976.84027721002</v>
+        <v>-34420.36316736478</v>
       </c>
       <c r="D91">
-        <v>5831.487722789971</v>
+        <v>6387.964832635215</v>
       </c>
       <c r="E91">
         <v>24426.728</v>
@@ -8755,37 +8755,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M91">
-        <v>9790.398862400001</v>
+        <v>9109.879942400001</v>
       </c>
       <c r="N91">
-        <v>-6095.074372604083</v>
+        <v>-5414.555452604082</v>
       </c>
       <c r="O91">
-        <v>-1572.529188131853</v>
+        <v>-1396.955306771853</v>
       </c>
       <c r="P91">
-        <v>-4522.545184472229</v>
+        <v>-4017.600145832229</v>
       </c>
       <c r="Q91">
-        <v>-2586.645184472229</v>
+        <v>-2081.700145832228</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2405959628451904</v>
+        <v>0.2390907815088955</v>
       </c>
       <c r="T91">
-        <v>4.495859731189226</v>
+        <v>4.463990335078417</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09738047772791493</v>
+        <v>0.1046549158051994</v>
       </c>
       <c r="W91">
-        <v>0.194785292906316</v>
+        <v>0.179785292906316</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3774437121237013</v>
+        <v>0.4056392085472845</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2015244665995921</v>
+        <v>0.1878588966525997</v>
       </c>
       <c r="C92">
-        <v>-35550.25298092098</v>
+        <v>-34999.81404384415</v>
       </c>
       <c r="D92">
-        <v>5767.827019079014</v>
+        <v>6318.265956155848</v>
       </c>
       <c r="E92">
         <v>24936.48</v>
@@ -8837,37 +8837,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M92">
-        <v>9900.403344</v>
+        <v>9212.238144000001</v>
       </c>
       <c r="N92">
-        <v>-6205.078854204082</v>
+        <v>-5516.913654204082</v>
       </c>
       <c r="O92">
-        <v>-1600.910344384653</v>
+        <v>-1423.363722784653</v>
       </c>
       <c r="P92">
-        <v>-4604.168509819428</v>
+        <v>-4093.549931419429</v>
       </c>
       <c r="Q92">
-        <v>-2668.268509819428</v>
+        <v>-2157.649931419429</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2600755591297094</v>
+        <v>0.258419859659785</v>
       </c>
       <c r="T92">
-        <v>4.945445704308148</v>
+        <v>4.910389368586259</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.096298472419827</v>
+        <v>0.1034920834073639</v>
       </c>
       <c r="W92">
-        <v>0.1950187896518013</v>
+        <v>0.1800187896518013</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3732498931001046</v>
+        <v>0.4011321062300925</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2032244665995922</v>
+        <v>0.1894088966525997</v>
       </c>
       <c r="C93">
-        <v>-36122.29076244042</v>
+        <v>-35577.76037205302</v>
       </c>
       <c r="D93">
-        <v>5705.54123755958</v>
+        <v>6250.071627946977</v>
       </c>
       <c r="E93">
         <v>25446.232</v>
@@ -8919,37 +8919,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M93">
-        <v>10010.4078256</v>
+        <v>9314.596345600001</v>
       </c>
       <c r="N93">
-        <v>-6315.083335804083</v>
+        <v>-5619.271855804082</v>
       </c>
       <c r="O93">
-        <v>-1629.291500637453</v>
+        <v>-1449.772138797453</v>
       </c>
       <c r="P93">
-        <v>-4685.791835166629</v>
+        <v>-4169.499717006629</v>
       </c>
       <c r="Q93">
-        <v>-2749.891835166629</v>
+        <v>-2233.599717006628</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2838839545885661</v>
+        <v>0.2820442885108723</v>
       </c>
       <c r="T93">
-        <v>5.494939671453499</v>
+        <v>5.455988187318066</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09524024744818053</v>
+        <v>0.1023548077655247</v>
       </c>
       <c r="W93">
-        <v>0.1952471546006827</v>
+        <v>0.1802471546006826</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3691482459231804</v>
+        <v>0.3967240611066849</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2049244665995922</v>
+        <v>0.1909588966525997</v>
       </c>
       <c r="C94">
-        <v>-36692.99768855029</v>
+        <v>-36154.25034848242</v>
       </c>
       <c r="D94">
-        <v>5644.586311449708</v>
+        <v>6183.333651517583</v>
       </c>
       <c r="E94">
         <v>25955.984</v>
@@ -9001,37 +9001,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M94">
-        <v>10120.4123072</v>
+        <v>9416.954547200001</v>
       </c>
       <c r="N94">
-        <v>-6425.087817404084</v>
+        <v>-5721.630057404082</v>
       </c>
       <c r="O94">
-        <v>-1657.672656890254</v>
+        <v>-1476.180554810253</v>
       </c>
       <c r="P94">
-        <v>-4767.41516051383</v>
+        <v>-4245.449502593829</v>
       </c>
       <c r="Q94">
-        <v>-2831.51516051383</v>
+        <v>-2309.549502593828</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3136444489121369</v>
+        <v>0.3115748245747314</v>
       </c>
       <c r="T94">
-        <v>6.181807130385187</v>
+        <v>6.137986710732826</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09420502736722204</v>
+        <v>0.1012422555072038</v>
       </c>
       <c r="W94">
-        <v>0.1954705550941535</v>
+        <v>0.1804705550941535</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3651357649892327</v>
+        <v>0.3924118430511775</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2066244665995922</v>
+        <v>0.1925088966525997</v>
       </c>
       <c r="C95">
-        <v>-37262.41596279547</v>
+        <v>-36729.33013281268</v>
       </c>
       <c r="D95">
-        <v>5584.920037204538</v>
+        <v>6118.005867187321</v>
       </c>
       <c r="E95">
         <v>26465.736</v>
@@ -9083,37 +9083,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M95">
-        <v>10230.4167888</v>
+        <v>9519.312748800001</v>
       </c>
       <c r="N95">
-        <v>-6535.092299004083</v>
+        <v>-5823.988259004082</v>
       </c>
       <c r="O95">
-        <v>-1686.053813143053</v>
+        <v>-1502.588970823053</v>
       </c>
       <c r="P95">
-        <v>-4849.03848586103</v>
+        <v>-4321.399288181029</v>
       </c>
       <c r="Q95">
-        <v>-2913.138485861029</v>
+        <v>-2385.499288181029</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3519079416138708</v>
+        <v>0.3495426566568359</v>
       </c>
       <c r="T95">
-        <v>7.064922434725929</v>
+        <v>7.014841955123231</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09319207008370353</v>
+        <v>0.1001536291039005</v>
       </c>
       <c r="W95">
-        <v>0.1956891512759368</v>
+        <v>0.1806891512759368</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3612095739678431</v>
+        <v>0.3881923608678315</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2083244665995922</v>
+        <v>0.1940588966525997</v>
       </c>
       <c r="C96">
-        <v>-37830.5860229306</v>
+        <v>-37303.04395438459</v>
       </c>
       <c r="D96">
-        <v>5526.501977069399</v>
+        <v>6054.044045615419</v>
       </c>
       <c r="E96">
         <v>26975.488</v>
@@ -9165,37 +9165,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M96">
-        <v>10340.4212704</v>
+        <v>9621.670950400001</v>
       </c>
       <c r="N96">
-        <v>-6645.096780604084</v>
+        <v>-5926.346460604082</v>
       </c>
       <c r="O96">
-        <v>-1714.434969395854</v>
+        <v>-1528.997386835853</v>
       </c>
       <c r="P96">
-        <v>-4930.66181120823</v>
+        <v>-4397.34907376823</v>
       </c>
       <c r="Q96">
-        <v>-2994.761811208229</v>
+        <v>-2461.449073768229</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.4029259318828493</v>
+        <v>0.4001664327663086</v>
       </c>
       <c r="T96">
-        <v>8.242409507180252</v>
+        <v>8.183982280977103</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09220066508281308</v>
+        <v>0.09908816496449732</v>
       </c>
       <c r="W96">
-        <v>0.195903096475129</v>
+        <v>0.1809030964751289</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.357366918925632</v>
+        <v>0.3840626549011524</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2100244665995922</v>
+        <v>0.1956088966525997</v>
       </c>
       <c r="C97">
-        <v>-38397.54663231477</v>
+        <v>-37875.43421206072</v>
       </c>
       <c r="D97">
-        <v>5469.293367685229</v>
+        <v>5991.405787939279</v>
       </c>
       <c r="E97">
         <v>27485.24</v>
@@ -9247,37 +9247,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M97">
-        <v>10450.425752</v>
+        <v>9724.029152000001</v>
       </c>
       <c r="N97">
-        <v>-6755.101262204083</v>
+        <v>-6028.704662204083</v>
       </c>
       <c r="O97">
-        <v>-1742.816125648653</v>
+        <v>-1555.405802848653</v>
       </c>
       <c r="P97">
-        <v>-5012.285136555429</v>
+        <v>-4473.298859355429</v>
       </c>
       <c r="Q97">
-        <v>-3076.385136555428</v>
+        <v>-2537.398859355429</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4743511182594194</v>
+        <v>0.4710397193195706</v>
       </c>
       <c r="T97">
-        <v>9.890891408616309</v>
+        <v>9.82077873717253</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09123013176615188</v>
+        <v>0.09804513164908156</v>
       </c>
       <c r="W97">
-        <v>0.1961125375648644</v>
+        <v>0.1811125375648644</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3536051618843096</v>
+        <v>0.3800198901127192</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2117244665995921</v>
+        <v>0.1971588966525997</v>
       </c>
       <c r="C98">
-        <v>-38963.33496568747</v>
+        <v>-38446.54156795116</v>
       </c>
       <c r="D98">
-        <v>5413.257034312523</v>
+        <v>5930.050432048829</v>
       </c>
       <c r="E98">
         <v>27994.99199999999</v>
@@ -9329,37 +9329,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M98">
-        <v>10560.4302336</v>
+        <v>9826.387353599999</v>
       </c>
       <c r="N98">
-        <v>-6865.105743804082</v>
+        <v>-6131.062863804081</v>
       </c>
       <c r="O98">
-        <v>-1771.197281901453</v>
+        <v>-1581.814218861453</v>
       </c>
       <c r="P98">
-        <v>-5093.908461902629</v>
+        <v>-4549.248644942628</v>
       </c>
       <c r="Q98">
-        <v>-3158.008461902628</v>
+        <v>-2613.348644942627</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.581488897824273</v>
+        <v>0.577349649149462</v>
       </c>
       <c r="T98">
-        <v>12.36361426077036</v>
+        <v>12.27597342146563</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09027981789358781</v>
+        <v>0.09702382819440365</v>
       </c>
       <c r="W98">
-        <v>0.1963176152985638</v>
+        <v>0.1813176152985637</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3499217747813481</v>
+        <v>0.3760613495907118</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2134244665995922</v>
+        <v>0.1987088966525997</v>
       </c>
       <c r="C99">
-        <v>-39527.98668972545</v>
+        <v>-39016.40503543863</v>
       </c>
       <c r="D99">
-        <v>5358.35731027454</v>
+        <v>5869.938964561372</v>
       </c>
       <c r="E99">
         <v>28504.744</v>
@@ -9411,37 +9411,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M99">
-        <v>10670.4347152</v>
+        <v>9928.745555199999</v>
       </c>
       <c r="N99">
-        <v>-6975.110225404082</v>
+        <v>-6233.421065404081</v>
       </c>
       <c r="O99">
-        <v>-1799.578438154253</v>
+        <v>-1608.222634874253</v>
       </c>
       <c r="P99">
-        <v>-5175.531787249829</v>
+        <v>-4625.198430529828</v>
       </c>
       <c r="Q99">
-        <v>-3239.631787249828</v>
+        <v>-2689.298430529828</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.7600518637656974</v>
+        <v>0.7545328655326159</v>
       </c>
       <c r="T99">
-        <v>16.48481901436048</v>
+        <v>16.36796456195418</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08934909812148896</v>
+        <v>0.09602358254291493</v>
       </c>
       <c r="W99">
-        <v>0.1965184646253827</v>
+        <v>0.1815184646253827</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3463143338042207</v>
+        <v>0.3721844284609106</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2151244665995921</v>
+        <v>0.2002588966525997</v>
       </c>
       <c r="C100">
-        <v>-40091.53603874653</v>
+        <v>-39585.06206190358</v>
       </c>
       <c r="D100">
-        <v>5304.559961253462</v>
+        <v>5811.033938096411</v>
       </c>
       <c r="E100">
         <v>29014.496</v>
@@ -9493,37 +9493,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M100">
-        <v>10780.4391968</v>
+        <v>10031.1037568</v>
       </c>
       <c r="N100">
-        <v>-7085.114707004082</v>
+        <v>-6335.779267004081</v>
       </c>
       <c r="O100">
-        <v>-1827.959594407053</v>
+        <v>-1634.631050887053</v>
       </c>
       <c r="P100">
-        <v>-5257.155112597028</v>
+        <v>-4701.148216117028</v>
       </c>
       <c r="Q100">
-        <v>-3321.255112597028</v>
+        <v>-2765.248216117027</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.117177795648546</v>
+        <v>1.108899298298924</v>
       </c>
       <c r="T100">
-        <v>24.72722852154072</v>
+        <v>24.55194684293127</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.08843737263045337</v>
+        <v>0.09504375006798724</v>
       </c>
       <c r="W100">
-        <v>0.1967152149863482</v>
+        <v>0.1817152149863482</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3427805140715247</v>
+        <v>0.3683866281704932</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2168244665995922</v>
+        <v>0.2018088966525997</v>
       </c>
       <c r="C101">
-        <v>-40654.01588589863</v>
+        <v>-40152.54860651809</v>
       </c>
       <c r="D101">
-        <v>5251.832114101368</v>
+        <v>5753.299393481905</v>
       </c>
       <c r="E101">
         <v>29524.248</v>
@@ -9575,37 +9575,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M101">
-        <v>10890.4436784</v>
+        <v>10133.4619584</v>
       </c>
       <c r="N101">
-        <v>-7195.119188604082</v>
+        <v>-6438.137468604081</v>
       </c>
       <c r="O101">
-        <v>-1856.340750659853</v>
+        <v>-1661.039466899853</v>
       </c>
       <c r="P101">
-        <v>-5338.778437944229</v>
+        <v>-4777.098001704227</v>
       </c>
       <c r="Q101">
-        <v>-3402.878437944229</v>
+        <v>-2841.198001704227</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.188555591297092</v>
+        <v>2.171998596597848</v>
       </c>
       <c r="T101">
-        <v>49.45445704308143</v>
+        <v>49.10389368586254</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.08754406583620636</v>
+        <v>0.09408371218851262</v>
       </c>
       <c r="W101">
-        <v>0.1969079905925467</v>
+        <v>0.1819079905925467</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3393180846364587</v>
+        <v>0.3646655511182659</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_grocery_and_food.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06924579469179407</v>
+        <v>0.06910053054148925</v>
       </c>
       <c r="C2">
-        <v>42842.19618784974</v>
+        <v>42571.11209271947</v>
       </c>
       <c r="D2">
-        <v>38282.59618784974</v>
+        <v>38521.26409271947</v>
       </c>
       <c r="E2">
-        <v>-20941.2</v>
+        <v>-20431.448</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>509.752</v>
       </c>
       <c r="G2">
         <v>4559.6</v>
@@ -1457,28 +1457,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>25.6405256</v>
       </c>
       <c r="N2">
-        <v>3695.324489795918</v>
+        <v>3669.683964195919</v>
       </c>
       <c r="O2">
-        <v>953.393718367347</v>
+        <v>946.7784627625471</v>
       </c>
       <c r="P2">
-        <v>2741.930771428571</v>
+        <v>2722.905501433372</v>
       </c>
       <c r="Q2">
-        <v>4677.830771428572</v>
+        <v>4658.805501433372</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06924579469179407</v>
+        <v>0.06942151973887803</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.545531633692333</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.1204656817144</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06910053054148925</v>
+        <v>0.06895526639118441</v>
       </c>
       <c r="C3">
-        <v>42571.11209271947</v>
+        <v>42303.02255526958</v>
       </c>
       <c r="D3">
-        <v>38521.26409271947</v>
+        <v>38762.92655526958</v>
       </c>
       <c r="E3">
-        <v>-20431.448</v>
+        <v>-19921.696</v>
       </c>
       <c r="F3">
-        <v>509.752</v>
+        <v>1019.504</v>
       </c>
       <c r="G3">
         <v>4559.6</v>
@@ -1539,28 +1539,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M3">
-        <v>25.6405256</v>
+        <v>51.2810512</v>
       </c>
       <c r="N3">
-        <v>3669.683964195919</v>
+        <v>3644.043438595918</v>
       </c>
       <c r="O3">
-        <v>946.7784627625471</v>
+        <v>940.1632071577469</v>
       </c>
       <c r="P3">
-        <v>2722.905501433372</v>
+        <v>2703.880231438171</v>
       </c>
       <c r="Q3">
-        <v>4658.805501433372</v>
+        <v>4639.780231438172</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06942151973887803</v>
+        <v>0.06960083101141266</v>
       </c>
       <c r="T3">
-        <v>0.545531633692333</v>
+        <v>0.5496727716261586</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.1204656817144</v>
+        <v>72.06023284085718</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06895526639118441</v>
+        <v>0.06881000224087959</v>
       </c>
       <c r="C4">
-        <v>42303.02255526958</v>
+        <v>42037.98429021114</v>
       </c>
       <c r="D4">
-        <v>38762.92655526958</v>
+        <v>39007.64029021114</v>
       </c>
       <c r="E4">
-        <v>-19921.696</v>
+        <v>-19411.944</v>
       </c>
       <c r="F4">
-        <v>1019.504</v>
+        <v>1529.256</v>
       </c>
       <c r="G4">
         <v>4559.6</v>
@@ -1621,28 +1621,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M4">
-        <v>51.2810512</v>
+        <v>76.92157679999998</v>
       </c>
       <c r="N4">
-        <v>3644.043438595918</v>
+        <v>3618.402912995919</v>
       </c>
       <c r="O4">
-        <v>940.1632071577469</v>
+        <v>933.547951552947</v>
       </c>
       <c r="P4">
-        <v>2703.880231438171</v>
+        <v>2684.854961442972</v>
       </c>
       <c r="Q4">
-        <v>4639.780231438172</v>
+        <v>4620.754961442972</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06960083101141266</v>
+        <v>0.06978383942358721</v>
       </c>
       <c r="T4">
-        <v>0.5496727716261586</v>
+        <v>0.5538992938472794</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.06023284085718</v>
+        <v>48.04015522723813</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06881000224087959</v>
+        <v>0.06866473809057476</v>
       </c>
       <c r="C5">
-        <v>42037.98429021114</v>
+        <v>41776.05545353395</v>
       </c>
       <c r="D5">
-        <v>39007.64029021114</v>
+        <v>39255.46345353396</v>
       </c>
       <c r="E5">
-        <v>-19411.944</v>
+        <v>-18902.192</v>
       </c>
       <c r="F5">
-        <v>1529.256</v>
+        <v>2039.008</v>
       </c>
       <c r="G5">
         <v>4559.6</v>
@@ -1703,28 +1703,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M5">
-        <v>76.92157679999998</v>
+        <v>102.5621024</v>
       </c>
       <c r="N5">
-        <v>3618.402912995919</v>
+        <v>3592.762387395918</v>
       </c>
       <c r="O5">
-        <v>933.547951552947</v>
+        <v>926.9326959481469</v>
       </c>
       <c r="P5">
-        <v>2684.854961442972</v>
+        <v>2665.829691447771</v>
       </c>
       <c r="Q5">
-        <v>4620.754961442972</v>
+        <v>4601.729691447772</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06978383942358721</v>
+        <v>0.06997066051101537</v>
       </c>
       <c r="T5">
-        <v>0.5538992938472794</v>
+        <v>0.5582138686146737</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.04015522723813</v>
+        <v>36.03011642042859</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06866473809057476</v>
+        <v>0.06851947394026991</v>
       </c>
       <c r="C6">
-        <v>41776.05545353395</v>
+        <v>41517.29568858272</v>
       </c>
       <c r="D6">
-        <v>39255.46345353396</v>
+        <v>39506.45568858272</v>
       </c>
       <c r="E6">
-        <v>-18902.192</v>
+        <v>-18392.44</v>
       </c>
       <c r="F6">
-        <v>2039.008</v>
+        <v>2548.76</v>
       </c>
       <c r="G6">
         <v>4559.6</v>
@@ -1785,28 +1785,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M6">
-        <v>102.5621024</v>
+        <v>128.202628</v>
       </c>
       <c r="N6">
-        <v>3592.762387395918</v>
+        <v>3567.121861795918</v>
       </c>
       <c r="O6">
-        <v>926.9326959481469</v>
+        <v>920.317440343347</v>
       </c>
       <c r="P6">
-        <v>2665.829691447771</v>
+        <v>2646.804421452572</v>
       </c>
       <c r="Q6">
-        <v>4601.729691447772</v>
+        <v>4582.704421452572</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06997066051101537</v>
+        <v>0.07016141467396834</v>
       </c>
       <c r="T6">
-        <v>0.5582138686146737</v>
+        <v>0.5626192765350657</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.03011642042859</v>
+        <v>28.82409313634287</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06851947394026991</v>
+        <v>0.0683742097899651</v>
       </c>
       <c r="C7">
-        <v>41517.29568858272</v>
+        <v>41261.76617391233</v>
       </c>
       <c r="D7">
-        <v>39506.45568858272</v>
+        <v>39760.67817391233</v>
       </c>
       <c r="E7">
-        <v>-18392.44</v>
+        <v>-17882.688</v>
       </c>
       <c r="F7">
-        <v>2548.76</v>
+        <v>3058.512</v>
       </c>
       <c r="G7">
         <v>4559.6</v>
@@ -1867,28 +1867,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M7">
-        <v>128.202628</v>
+        <v>153.8431536</v>
       </c>
       <c r="N7">
-        <v>3567.121861795918</v>
+        <v>3541.481336195919</v>
       </c>
       <c r="O7">
-        <v>920.317440343347</v>
+        <v>913.702184738547</v>
       </c>
       <c r="P7">
-        <v>2646.804421452572</v>
+        <v>2627.779151457372</v>
       </c>
       <c r="Q7">
-        <v>4582.704421452572</v>
+        <v>4563.679151457372</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07016141467396834</v>
+        <v>0.0703562274361331</v>
       </c>
       <c r="T7">
-        <v>0.5626192765350657</v>
+        <v>0.5671184165388703</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.82409313634287</v>
+        <v>24.02007761361906</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0683742097899651</v>
+        <v>0.06822894563966028</v>
       </c>
       <c r="C8">
-        <v>41261.76617391233</v>
+        <v>41009.52967300308</v>
       </c>
       <c r="D8">
-        <v>39760.67817391233</v>
+        <v>40018.19367300309</v>
       </c>
       <c r="E8">
-        <v>-17882.688</v>
+        <v>-17372.936</v>
       </c>
       <c r="F8">
-        <v>3058.512</v>
+        <v>3568.263999999999</v>
       </c>
       <c r="G8">
         <v>4559.6</v>
@@ -1949,28 +1949,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M8">
-        <v>153.8431536</v>
+        <v>179.4836792</v>
       </c>
       <c r="N8">
-        <v>3541.481336195919</v>
+        <v>3515.840810595918</v>
       </c>
       <c r="O8">
-        <v>913.702184738547</v>
+        <v>907.0869291337469</v>
       </c>
       <c r="P8">
-        <v>2627.779151457372</v>
+        <v>2608.753881462171</v>
       </c>
       <c r="Q8">
-        <v>4563.679151457372</v>
+        <v>4544.653881462172</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0703562274361331</v>
+        <v>0.07055522972006481</v>
       </c>
       <c r="T8">
-        <v>0.5671184165388703</v>
+        <v>0.5717143122416815</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.02007761361907</v>
+        <v>20.58863795453063</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06822894563966027</v>
+        <v>0.06808368148935545</v>
       </c>
       <c r="C9">
-        <v>41009.5296730031</v>
+        <v>40760.65058592009</v>
       </c>
       <c r="D9">
-        <v>40018.19367300311</v>
+        <v>40279.0665859201</v>
       </c>
       <c r="E9">
-        <v>-17372.936</v>
+        <v>-16863.184</v>
       </c>
       <c r="F9">
-        <v>3568.264</v>
+        <v>4078.016</v>
       </c>
       <c r="G9">
         <v>4559.6</v>
@@ -2031,28 +2031,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M9">
-        <v>179.4836792</v>
+        <v>205.1242048</v>
       </c>
       <c r="N9">
-        <v>3515.840810595918</v>
+        <v>3490.200284995919</v>
       </c>
       <c r="O9">
-        <v>907.0869291337469</v>
+        <v>900.471673528947</v>
       </c>
       <c r="P9">
-        <v>2608.753881462171</v>
+        <v>2589.728611466971</v>
       </c>
       <c r="Q9">
-        <v>4544.653881462172</v>
+        <v>4525.628611466972</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07055522972006481</v>
+        <v>0.07075855814060374</v>
       </c>
       <c r="T9">
-        <v>0.5717143122416815</v>
+        <v>0.5764101187206405</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.58863795453063</v>
+        <v>18.0150582102143</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06808368148935545</v>
+        <v>0.06793841733905061</v>
       </c>
       <c r="C10">
-        <v>40760.65058592009</v>
+        <v>40515.19500300656</v>
       </c>
       <c r="D10">
-        <v>40279.0665859201</v>
+        <v>40543.36300300655</v>
       </c>
       <c r="E10">
-        <v>-16863.184</v>
+        <v>-16353.432</v>
       </c>
       <c r="F10">
-        <v>4078.016</v>
+        <v>4587.767999999999</v>
       </c>
       <c r="G10">
         <v>4559.6</v>
@@ -2113,28 +2113,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M10">
-        <v>205.1242048</v>
+        <v>230.7647303999999</v>
       </c>
       <c r="N10">
-        <v>3490.200284995919</v>
+        <v>3464.559759395919</v>
       </c>
       <c r="O10">
-        <v>900.471673528947</v>
+        <v>893.8564179241471</v>
       </c>
       <c r="P10">
-        <v>2589.728611466971</v>
+        <v>2570.703341471772</v>
       </c>
       <c r="Q10">
-        <v>4525.628611466972</v>
+        <v>4506.603341471772</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07075855814060374</v>
+        <v>0.07096635531763804</v>
       </c>
       <c r="T10">
-        <v>0.5764101187206405</v>
+        <v>0.581209129737599</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.0150582102143</v>
+        <v>16.01338507574604</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06793841733905061</v>
+        <v>0.06779315318874579</v>
       </c>
       <c r="C11">
-        <v>40515.19500300656</v>
+        <v>40273.23076070494</v>
       </c>
       <c r="D11">
-        <v>40543.36300300655</v>
+        <v>40811.15076070494</v>
       </c>
       <c r="E11">
-        <v>-16353.432</v>
+        <v>-15843.68</v>
       </c>
       <c r="F11">
-        <v>4587.767999999999</v>
+        <v>5097.52</v>
       </c>
       <c r="G11">
         <v>4559.6</v>
@@ -2195,28 +2195,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M11">
-        <v>230.7647303999999</v>
+        <v>256.405256</v>
       </c>
       <c r="N11">
-        <v>3464.559759395919</v>
+        <v>3438.919233795918</v>
       </c>
       <c r="O11">
-        <v>893.8564179241471</v>
+        <v>887.2411623193469</v>
       </c>
       <c r="P11">
-        <v>2570.703341471772</v>
+        <v>2551.678071476571</v>
       </c>
       <c r="Q11">
-        <v>4506.603341471772</v>
+        <v>4487.578071476571</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07096635531763804</v>
+        <v>0.07117877020971754</v>
       </c>
       <c r="T11">
-        <v>0.581209129737599</v>
+        <v>0.586114785443823</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.01338507574604</v>
+        <v>14.41204656817144</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06779315318874579</v>
+        <v>0.06764788903844096</v>
       </c>
       <c r="C12">
-        <v>40273.23076070494</v>
+        <v>40034.82749960532</v>
       </c>
       <c r="D12">
-        <v>40811.15076070494</v>
+        <v>41082.49949960531</v>
       </c>
       <c r="E12">
-        <v>-15843.68</v>
+        <v>-15333.928</v>
       </c>
       <c r="F12">
-        <v>5097.52</v>
+        <v>5607.272</v>
       </c>
       <c r="G12">
         <v>4559.6</v>
@@ -2277,28 +2277,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M12">
-        <v>256.405256</v>
+        <v>282.0457816</v>
       </c>
       <c r="N12">
-        <v>3438.919233795918</v>
+        <v>3413.278708195919</v>
       </c>
       <c r="O12">
-        <v>887.2411623193469</v>
+        <v>880.625906714547</v>
       </c>
       <c r="P12">
-        <v>2551.678071476571</v>
+        <v>2532.652801481372</v>
       </c>
       <c r="Q12">
-        <v>4487.578071476571</v>
+        <v>4468.552801481372</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07117877020971754</v>
+        <v>0.07139595847015838</v>
       </c>
       <c r="T12">
-        <v>0.586114785443823</v>
+        <v>0.5911306806041194</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.41204656817144</v>
+        <v>13.10186051651949</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06764788903844096</v>
+        <v>0.06750262488813612</v>
       </c>
       <c r="C13">
-        <v>40034.82749960532</v>
+        <v>39800.05672482438</v>
       </c>
       <c r="D13">
-        <v>41082.49949960531</v>
+        <v>41357.48072482437</v>
       </c>
       <c r="E13">
-        <v>-15333.928</v>
+        <v>-14824.176</v>
       </c>
       <c r="F13">
-        <v>5607.272</v>
+        <v>6117.023999999999</v>
       </c>
       <c r="G13">
         <v>4559.6</v>
@@ -2359,28 +2359,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M13">
-        <v>282.0457816</v>
+        <v>307.6863071999999</v>
       </c>
       <c r="N13">
-        <v>3413.278708195919</v>
+        <v>3387.638182595918</v>
       </c>
       <c r="O13">
-        <v>880.625906714547</v>
+        <v>874.010651109747</v>
       </c>
       <c r="P13">
-        <v>2532.652801481372</v>
+        <v>2513.627531486171</v>
       </c>
       <c r="Q13">
-        <v>4468.552801481372</v>
+        <v>4449.527531486172</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07139595847015838</v>
+        <v>0.07161808282742742</v>
       </c>
       <c r="T13">
-        <v>0.5911306806041194</v>
+        <v>0.5962605733816956</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.10186051651949</v>
+        <v>12.01003880680953</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06750262488813612</v>
+        <v>0.0673573607378313</v>
       </c>
       <c r="C14">
-        <v>39800.05672482438</v>
+        <v>39568.99186882602</v>
       </c>
       <c r="D14">
-        <v>41357.48072482437</v>
+        <v>41636.16786882602</v>
       </c>
       <c r="E14">
-        <v>-14824.176</v>
+        <v>-14314.424</v>
       </c>
       <c r="F14">
-        <v>6117.023999999999</v>
+        <v>6626.776</v>
       </c>
       <c r="G14">
         <v>4559.6</v>
@@ -2441,28 +2441,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M14">
-        <v>307.6863071999999</v>
+        <v>333.3268328</v>
       </c>
       <c r="N14">
-        <v>3387.638182595918</v>
+        <v>3361.997656995919</v>
       </c>
       <c r="O14">
-        <v>874.010651109747</v>
+        <v>867.395395504947</v>
       </c>
       <c r="P14">
-        <v>2513.627531486171</v>
+        <v>2494.602261490972</v>
       </c>
       <c r="Q14">
-        <v>4449.527531486172</v>
+        <v>4430.502261490972</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07161808282742742</v>
+        <v>0.07184531349176011</v>
       </c>
       <c r="T14">
-        <v>0.5962605733816956</v>
+        <v>0.601508394728871</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.01003880680953</v>
+        <v>11.08618966782418</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0673573607378313</v>
+        <v>0.06721209658752647</v>
       </c>
       <c r="C15">
-        <v>39568.99186882602</v>
+        <v>39341.7083567992</v>
       </c>
       <c r="D15">
-        <v>41636.16786882602</v>
+        <v>41918.6363567992</v>
       </c>
       <c r="E15">
-        <v>-14314.424</v>
+        <v>-13804.672</v>
       </c>
       <c r="F15">
-        <v>6626.776</v>
+        <v>7136.528</v>
       </c>
       <c r="G15">
         <v>4559.6</v>
@@ -2523,28 +2523,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M15">
-        <v>333.3268328</v>
+        <v>358.9673584</v>
       </c>
       <c r="N15">
-        <v>3361.997656995919</v>
+        <v>3336.357131395918</v>
       </c>
       <c r="O15">
-        <v>867.395395504947</v>
+        <v>860.7801399001469</v>
       </c>
       <c r="P15">
-        <v>2494.602261490972</v>
+        <v>2475.576991495771</v>
       </c>
       <c r="Q15">
-        <v>4430.502261490972</v>
+        <v>4411.476991495772</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07184531349176011</v>
+        <v>0.07207782859014705</v>
       </c>
       <c r="T15">
-        <v>0.601508394728871</v>
+        <v>0.6068782584329574</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.08618966782418</v>
+        <v>10.29431897726531</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06721209658752647</v>
+        <v>0.06706683243722164</v>
       </c>
       <c r="C16">
-        <v>39341.7083567992</v>
+        <v>39118.28367471468</v>
       </c>
       <c r="D16">
-        <v>41918.6363567992</v>
+        <v>42204.96367471468</v>
       </c>
       <c r="E16">
-        <v>-13804.672</v>
+        <v>-13294.92</v>
       </c>
       <c r="F16">
-        <v>7136.528</v>
+        <v>7646.280000000001</v>
       </c>
       <c r="G16">
         <v>4559.6</v>
@@ -2605,28 +2605,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M16">
-        <v>358.9673584</v>
+        <v>384.607884</v>
       </c>
       <c r="N16">
-        <v>3336.357131395918</v>
+        <v>3310.716605795918</v>
       </c>
       <c r="O16">
-        <v>860.7801399001469</v>
+        <v>854.164884295347</v>
       </c>
       <c r="P16">
-        <v>2475.576991495771</v>
+        <v>2456.551721500572</v>
       </c>
       <c r="Q16">
-        <v>4411.476991495772</v>
+        <v>4392.451721500573</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07207782859014705</v>
+        <v>0.07231581463202547</v>
       </c>
       <c r="T16">
-        <v>0.6068782584329574</v>
+        <v>0.6123744718712577</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.29431897726531</v>
+        <v>9.608031045447623</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06706683243722164</v>
+        <v>0.06692156828691681</v>
       </c>
       <c r="C17">
-        <v>39118.28367471468</v>
+        <v>38898.79744019059</v>
       </c>
       <c r="D17">
-        <v>42204.96367471468</v>
+        <v>42495.22944019059</v>
       </c>
       <c r="E17">
-        <v>-13294.92</v>
+        <v>-12785.168</v>
       </c>
       <c r="F17">
-        <v>7646.279999999999</v>
+        <v>8156.032</v>
       </c>
       <c r="G17">
         <v>4559.6</v>
@@ -2687,28 +2687,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M17">
-        <v>384.6078839999999</v>
+        <v>410.2484096</v>
       </c>
       <c r="N17">
-        <v>3310.716605795918</v>
+        <v>3285.076080195919</v>
       </c>
       <c r="O17">
-        <v>854.164884295347</v>
+        <v>847.549628690547</v>
       </c>
       <c r="P17">
-        <v>2456.551721500572</v>
+        <v>2437.526451505371</v>
       </c>
       <c r="Q17">
-        <v>4392.451721500573</v>
+        <v>4373.426451505372</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07231581463202547</v>
+        <v>0.0725594670082343</v>
       </c>
       <c r="T17">
-        <v>0.6123744718712577</v>
+        <v>0.6180015475342794</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.608031045447627</v>
+        <v>9.007529105107148</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06692156828691681</v>
+        <v>0.06696551413661199</v>
       </c>
       <c r="C18">
-        <v>38898.79744019059</v>
+        <v>38300.81281074975</v>
       </c>
       <c r="D18">
-        <v>42495.22944019059</v>
+        <v>42406.99681074975</v>
       </c>
       <c r="E18">
-        <v>-12785.168</v>
+        <v>-12275.416</v>
       </c>
       <c r="F18">
-        <v>8156.032</v>
+        <v>8665.784</v>
       </c>
       <c r="G18">
         <v>4559.6</v>
@@ -2769,45 +2769,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M18">
-        <v>410.2484096</v>
+        <v>448.8876112</v>
       </c>
       <c r="N18">
-        <v>3285.076080195919</v>
+        <v>3246.436878595919</v>
       </c>
       <c r="O18">
-        <v>847.549628690547</v>
+        <v>837.580714677747</v>
       </c>
       <c r="P18">
-        <v>2437.526451505371</v>
+        <v>2408.856163918172</v>
       </c>
       <c r="Q18">
-        <v>4373.426451505372</v>
+        <v>4344.756163918172</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0725594670082343</v>
+        <v>0.07280899052603854</v>
       </c>
       <c r="T18">
-        <v>0.6180015475342794</v>
+        <v>0.6237642153819523</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.007529105107148</v>
+        <v>8.232181948433151</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06696551413661199</v>
+        <v>0.06683137998630714</v>
       </c>
       <c r="C19">
-        <v>38300.81281074975</v>
+        <v>38061.52458858523</v>
       </c>
       <c r="D19">
-        <v>42406.99681074975</v>
+        <v>42677.46058858523</v>
       </c>
       <c r="E19">
-        <v>-12275.416</v>
+        <v>-11765.664</v>
       </c>
       <c r="F19">
-        <v>8665.784</v>
+        <v>9175.536</v>
       </c>
       <c r="G19">
         <v>4559.6</v>
@@ -2851,28 +2851,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M19">
-        <v>448.8876112</v>
+        <v>475.2927648</v>
       </c>
       <c r="N19">
-        <v>3246.436878595919</v>
+        <v>3220.031724995918</v>
       </c>
       <c r="O19">
-        <v>837.580714677747</v>
+        <v>830.768185048947</v>
       </c>
       <c r="P19">
-        <v>2408.856163918172</v>
+        <v>2389.263539946971</v>
       </c>
       <c r="Q19">
-        <v>4344.756163918172</v>
+        <v>4325.163539946972</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07280899052603854</v>
+        <v>0.07306459998330141</v>
       </c>
       <c r="T19">
-        <v>0.6237642153819523</v>
+        <v>0.6296674361039585</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.232181948433151</v>
+        <v>7.774838506853532</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06683137998630716</v>
+        <v>0.06669724583600233</v>
       </c>
       <c r="C20">
-        <v>38061.5245885852</v>
+        <v>37825.70844396742</v>
       </c>
       <c r="D20">
-        <v>42677.4605885852</v>
+        <v>42951.39644396742</v>
       </c>
       <c r="E20">
-        <v>-11765.664</v>
+        <v>-11255.912</v>
       </c>
       <c r="F20">
-        <v>9175.535999999998</v>
+        <v>9685.288</v>
       </c>
       <c r="G20">
         <v>4559.6</v>
@@ -2933,28 +2933,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M20">
-        <v>475.2927647999999</v>
+        <v>501.6979184</v>
       </c>
       <c r="N20">
-        <v>3220.031724995918</v>
+        <v>3193.626571395918</v>
       </c>
       <c r="O20">
-        <v>830.768185048947</v>
+        <v>823.955655420147</v>
       </c>
       <c r="P20">
-        <v>2389.263539946971</v>
+        <v>2369.670915975771</v>
       </c>
       <c r="Q20">
-        <v>4325.163539946972</v>
+        <v>4305.570915975772</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07306459998330141</v>
+        <v>0.07332652078518806</v>
       </c>
       <c r="T20">
-        <v>0.6296674361039585</v>
+        <v>0.6357164153623107</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.774838506853532</v>
+        <v>7.365636480177029</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06669724583600233</v>
+        <v>0.06656311168569751</v>
       </c>
       <c r="C21">
-        <v>37825.70844396742</v>
+        <v>37593.43166799107</v>
       </c>
       <c r="D21">
-        <v>42951.39644396742</v>
+        <v>43228.87166799107</v>
       </c>
       <c r="E21">
-        <v>-11255.912</v>
+        <v>-10746.16</v>
       </c>
       <c r="F21">
-        <v>9685.288</v>
+        <v>10195.04</v>
       </c>
       <c r="G21">
         <v>4559.6</v>
@@ -3015,28 +3015,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M21">
-        <v>501.6979184</v>
+        <v>528.103072</v>
       </c>
       <c r="N21">
-        <v>3193.626571395918</v>
+        <v>3167.221417795919</v>
       </c>
       <c r="O21">
-        <v>823.955655420147</v>
+        <v>817.143125791347</v>
       </c>
       <c r="P21">
-        <v>2369.670915975771</v>
+        <v>2350.078292004572</v>
       </c>
       <c r="Q21">
-        <v>4305.570915975772</v>
+        <v>4285.978292004573</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07332652078518806</v>
+        <v>0.07359498960712188</v>
       </c>
       <c r="T21">
-        <v>0.6357164153623107</v>
+        <v>0.6419166191021217</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.365636480177029</v>
+        <v>6.997354656168178</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06656311168569751</v>
+        <v>0.06669387153539268</v>
       </c>
       <c r="C22">
-        <v>37593.43166799107</v>
+        <v>36813.14097188474</v>
       </c>
       <c r="D22">
-        <v>43228.87166799107</v>
+        <v>42958.33297188474</v>
       </c>
       <c r="E22">
-        <v>-10746.16</v>
+        <v>-10236.408</v>
       </c>
       <c r="F22">
-        <v>10195.04</v>
+        <v>10704.792</v>
       </c>
       <c r="G22">
         <v>4559.6</v>
@@ -3097,45 +3097,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M22">
-        <v>528.103072</v>
+        <v>572.7063720000001</v>
       </c>
       <c r="N22">
-        <v>3167.221417795919</v>
+        <v>3122.618117795918</v>
       </c>
       <c r="O22">
-        <v>817.143125791347</v>
+        <v>805.635474391347</v>
       </c>
       <c r="P22">
-        <v>2350.078292004572</v>
+        <v>2316.982643404571</v>
       </c>
       <c r="Q22">
-        <v>4285.978292004573</v>
+        <v>4252.882643404571</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07359498960712188</v>
+        <v>0.07387025510809199</v>
       </c>
       <c r="T22">
-        <v>0.6419166191021217</v>
+        <v>0.6482737900252191</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.997354656168178</v>
+        <v>6.452389340267228</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06669387153539268</v>
+        <v>0.06657235138508784</v>
       </c>
       <c r="C23">
-        <v>36813.14097188474</v>
+        <v>36554.69913811543</v>
       </c>
       <c r="D23">
-        <v>42958.33297188474</v>
+        <v>43209.64313811543</v>
       </c>
       <c r="E23">
-        <v>-10236.408</v>
+        <v>-9726.656000000001</v>
       </c>
       <c r="F23">
-        <v>10704.792</v>
+        <v>11214.544</v>
       </c>
       <c r="G23">
         <v>4559.6</v>
@@ -3179,28 +3179,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M23">
-        <v>572.706372</v>
+        <v>599.978104</v>
       </c>
       <c r="N23">
-        <v>3122.618117795918</v>
+        <v>3095.346385795919</v>
       </c>
       <c r="O23">
-        <v>805.635474391347</v>
+        <v>798.599367535347</v>
       </c>
       <c r="P23">
-        <v>2316.982643404571</v>
+        <v>2296.747018260572</v>
       </c>
       <c r="Q23">
-        <v>4252.882643404571</v>
+        <v>4232.647018260572</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07387025510809199</v>
+        <v>0.07415257869883056</v>
       </c>
       <c r="T23">
-        <v>0.648273790025219</v>
+        <v>0.6547939653309598</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.45238934026723</v>
+        <v>6.159098915709628</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06657235138508784</v>
+        <v>0.06645083123478301</v>
       </c>
       <c r="C24">
-        <v>36554.69913811543</v>
+        <v>36299.21498181934</v>
       </c>
       <c r="D24">
-        <v>43209.64313811543</v>
+        <v>43463.91098181934</v>
       </c>
       <c r="E24">
-        <v>-9726.656000000001</v>
+        <v>-9216.904</v>
       </c>
       <c r="F24">
-        <v>11214.544</v>
+        <v>11724.296</v>
       </c>
       <c r="G24">
         <v>4559.6</v>
@@ -3261,28 +3261,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M24">
-        <v>599.978104</v>
+        <v>627.249836</v>
       </c>
       <c r="N24">
-        <v>3095.346385795919</v>
+        <v>3068.074653795918</v>
       </c>
       <c r="O24">
-        <v>798.599367535347</v>
+        <v>791.563260679347</v>
       </c>
       <c r="P24">
-        <v>2296.747018260572</v>
+        <v>2276.511393116572</v>
       </c>
       <c r="Q24">
-        <v>4232.647018260572</v>
+        <v>4212.411393116572</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07415257869883056</v>
+        <v>0.07444223536984806</v>
       </c>
       <c r="T24">
-        <v>0.6547939653309598</v>
+        <v>0.6614834958394472</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.159098915709628</v>
+        <v>5.891312006330949</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06645083123478301</v>
+        <v>0.06632931108447818</v>
       </c>
       <c r="C25">
-        <v>36299.21498181934</v>
+        <v>36046.74102556919</v>
       </c>
       <c r="D25">
-        <v>43463.91098181934</v>
+        <v>43721.18902556919</v>
       </c>
       <c r="E25">
-        <v>-9216.904</v>
+        <v>-8707.152</v>
       </c>
       <c r="F25">
-        <v>11724.296</v>
+        <v>12234.048</v>
       </c>
       <c r="G25">
         <v>4559.6</v>
@@ -3343,28 +3343,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M25">
-        <v>627.249836</v>
+        <v>654.521568</v>
       </c>
       <c r="N25">
-        <v>3068.074653795918</v>
+        <v>3040.802921795918</v>
       </c>
       <c r="O25">
-        <v>791.563260679347</v>
+        <v>784.5271538233469</v>
       </c>
       <c r="P25">
-        <v>2276.511393116572</v>
+        <v>2256.275767972571</v>
       </c>
       <c r="Q25">
-        <v>4212.411393116572</v>
+        <v>4192.175767972572</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07444223536984806</v>
+        <v>0.07473951458483971</v>
       </c>
       <c r="T25">
-        <v>0.6614834958394472</v>
+        <v>0.6683490666244737</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.891312006330949</v>
+        <v>5.645840672733826</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06632931108447818</v>
+        <v>0.06635619093417335</v>
       </c>
       <c r="C26">
-        <v>36046.74102556919</v>
+        <v>35479.81797703862</v>
       </c>
       <c r="D26">
-        <v>43721.18902556919</v>
+        <v>43664.01797703862</v>
       </c>
       <c r="E26">
-        <v>-8707.152000000002</v>
+        <v>-8197.400000000001</v>
       </c>
       <c r="F26">
-        <v>12234.048</v>
+        <v>12743.8</v>
       </c>
       <c r="G26">
         <v>4559.6</v>
@@ -3425,45 +3425,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M26">
-        <v>654.5215679999999</v>
+        <v>691.98834</v>
       </c>
       <c r="N26">
-        <v>3040.802921795918</v>
+        <v>3003.336149795919</v>
       </c>
       <c r="O26">
-        <v>784.5271538233469</v>
+        <v>774.8607266473471</v>
       </c>
       <c r="P26">
-        <v>2256.275767972571</v>
+        <v>2228.475423148571</v>
       </c>
       <c r="Q26">
-        <v>4192.175767972572</v>
+        <v>4164.375423148572</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07473951458483971</v>
+        <v>0.07504472124556447</v>
       </c>
       <c r="T26">
-        <v>0.6683490666244737</v>
+        <v>0.6753977192971009</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.645840672733827</v>
+        <v>5.34015427166868</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06635619093417335</v>
+        <v>0.06624060678386853</v>
       </c>
       <c r="C27">
-        <v>35479.81797703862</v>
+        <v>35216.97001810421</v>
       </c>
       <c r="D27">
-        <v>43664.01797703862</v>
+        <v>43910.92201810422</v>
       </c>
       <c r="E27">
-        <v>-8197.400000000001</v>
+        <v>-7687.648000000001</v>
       </c>
       <c r="F27">
-        <v>12743.8</v>
+        <v>13253.552</v>
       </c>
       <c r="G27">
         <v>4559.6</v>
@@ -3507,28 +3507,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M27">
-        <v>691.98834</v>
+        <v>719.6678736</v>
       </c>
       <c r="N27">
-        <v>3003.336149795919</v>
+        <v>2975.656616195919</v>
       </c>
       <c r="O27">
-        <v>774.8607266473471</v>
+        <v>767.719406978547</v>
       </c>
       <c r="P27">
-        <v>2228.475423148571</v>
+        <v>2207.937209217372</v>
       </c>
       <c r="Q27">
-        <v>4164.375423148572</v>
+        <v>4143.837209217372</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07504472124556447</v>
+        <v>0.07535817673495747</v>
       </c>
       <c r="T27">
-        <v>0.6753977192971009</v>
+        <v>0.6826368760960153</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.34015427166868</v>
+        <v>5.134763722758346</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06624060678386853</v>
+        <v>0.06612502263356371</v>
       </c>
       <c r="C28">
-        <v>35216.97001810421</v>
+        <v>34956.93024239384</v>
       </c>
       <c r="D28">
-        <v>43910.92201810422</v>
+        <v>44160.63424239384</v>
       </c>
       <c r="E28">
-        <v>-7687.648000000001</v>
+        <v>-7177.896000000001</v>
       </c>
       <c r="F28">
-        <v>13253.552</v>
+        <v>13763.304</v>
       </c>
       <c r="G28">
         <v>4559.6</v>
@@ -3589,28 +3589,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M28">
-        <v>719.6678736</v>
+        <v>747.3474072</v>
       </c>
       <c r="N28">
-        <v>2975.656616195919</v>
+        <v>2947.977082595919</v>
       </c>
       <c r="O28">
-        <v>767.719406978547</v>
+        <v>760.578087309747</v>
       </c>
       <c r="P28">
-        <v>2207.937209217372</v>
+        <v>2187.398995286172</v>
       </c>
       <c r="Q28">
-        <v>4143.837209217372</v>
+        <v>4123.298995286172</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07535817673495747</v>
+        <v>0.07568022004597767</v>
       </c>
       <c r="T28">
-        <v>0.6826368760960153</v>
+        <v>0.6900743659579138</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.134763722758346</v>
+        <v>4.94458728858211</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06612502263356371</v>
+        <v>0.06600943848325887</v>
       </c>
       <c r="C29">
-        <v>34956.93024239384</v>
+        <v>34699.74683256313</v>
       </c>
       <c r="D29">
-        <v>44160.63424239384</v>
+        <v>44413.20283256314</v>
       </c>
       <c r="E29">
-        <v>-7177.896000000001</v>
+        <v>-6668.144</v>
       </c>
       <c r="F29">
-        <v>13763.304</v>
+        <v>14273.056</v>
       </c>
       <c r="G29">
         <v>4559.6</v>
@@ -3671,28 +3671,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M29">
-        <v>747.3474072</v>
+        <v>775.0269408</v>
       </c>
       <c r="N29">
-        <v>2947.977082595919</v>
+        <v>2920.297548995919</v>
       </c>
       <c r="O29">
-        <v>760.578087309747</v>
+        <v>753.436767640947</v>
       </c>
       <c r="P29">
-        <v>2187.398995286172</v>
+        <v>2166.860781354972</v>
       </c>
       <c r="Q29">
-        <v>4123.298995286172</v>
+        <v>4102.760781354972</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07568022004597767</v>
+        <v>0.07601120900452621</v>
       </c>
       <c r="T29">
-        <v>0.6900743659579138</v>
+        <v>0.6977184527604204</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.94458728858211</v>
+        <v>4.767994885418464</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06600943848325887</v>
+        <v>0.06589385433295404</v>
       </c>
       <c r="C30">
-        <v>34699.74683256313</v>
+        <v>34445.46907989551</v>
       </c>
       <c r="D30">
-        <v>44413.20283256314</v>
+        <v>44668.67707989551</v>
       </c>
       <c r="E30">
-        <v>-6668.144</v>
+        <v>-6158.392</v>
       </c>
       <c r="F30">
-        <v>14273.056</v>
+        <v>14782.808</v>
       </c>
       <c r="G30">
         <v>4559.6</v>
@@ -3753,28 +3753,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M30">
-        <v>775.0269408</v>
+        <v>802.7064744</v>
       </c>
       <c r="N30">
-        <v>2920.297548995919</v>
+        <v>2892.618015395919</v>
       </c>
       <c r="O30">
-        <v>753.436767640947</v>
+        <v>746.295447972147</v>
       </c>
       <c r="P30">
-        <v>2166.860781354972</v>
+        <v>2146.322567423771</v>
       </c>
       <c r="Q30">
-        <v>4102.760781354972</v>
+        <v>4082.222567423772</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07601120900452621</v>
+        <v>0.07635152159570992</v>
       </c>
       <c r="T30">
-        <v>0.6977184527604204</v>
+        <v>0.70557786595173</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.767994885418464</v>
+        <v>4.603581268679896</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06589385433295404</v>
+        <v>0.06577827018264921</v>
       </c>
       <c r="C31">
-        <v>34445.46907989551</v>
+        <v>34194.147416372</v>
       </c>
       <c r="D31">
-        <v>44668.67707989551</v>
+        <v>44927.107416372</v>
       </c>
       <c r="E31">
-        <v>-6158.392000000003</v>
+        <v>-5648.640000000003</v>
       </c>
       <c r="F31">
-        <v>14782.808</v>
+        <v>15292.56</v>
       </c>
       <c r="G31">
         <v>4559.6</v>
@@ -3835,28 +3835,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M31">
-        <v>802.7064743999998</v>
+        <v>830.3860079999998</v>
       </c>
       <c r="N31">
-        <v>2892.618015395919</v>
+        <v>2864.938481795919</v>
       </c>
       <c r="O31">
-        <v>746.295447972147</v>
+        <v>739.154128303347</v>
       </c>
       <c r="P31">
-        <v>2146.322567423771</v>
+        <v>2125.784353492571</v>
       </c>
       <c r="Q31">
-        <v>4082.222567423772</v>
+        <v>4061.684353492572</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07635152159570992</v>
+        <v>0.07670155740378459</v>
       </c>
       <c r="T31">
-        <v>0.70557786595173</v>
+        <v>0.7136618338056486</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.603581268679896</v>
+        <v>4.4501285597239</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06577827018264921</v>
+        <v>0.06566268603234438</v>
       </c>
       <c r="C32">
-        <v>34194.147416372</v>
+        <v>33945.83344786078</v>
       </c>
       <c r="D32">
-        <v>44927.107416372</v>
+        <v>45188.54544786078</v>
       </c>
       <c r="E32">
-        <v>-5648.640000000003</v>
+        <v>-5138.888000000003</v>
       </c>
       <c r="F32">
-        <v>15292.56</v>
+        <v>15802.312</v>
       </c>
       <c r="G32">
         <v>4559.6</v>
@@ -3917,28 +3917,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M32">
-        <v>830.3860079999998</v>
+        <v>858.0655416</v>
       </c>
       <c r="N32">
-        <v>2864.938481795919</v>
+        <v>2837.258948195918</v>
       </c>
       <c r="O32">
-        <v>739.154128303347</v>
+        <v>732.012808634547</v>
       </c>
       <c r="P32">
-        <v>2125.784353492571</v>
+        <v>2105.246139561371</v>
       </c>
       <c r="Q32">
-        <v>4061.684353492572</v>
+        <v>4041.146139561372</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07670155740378459</v>
+        <v>0.0770617391773107</v>
       </c>
       <c r="T32">
-        <v>0.7136618338056486</v>
+        <v>0.7219801195683764</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.4501285597239</v>
+        <v>4.306576025539258</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06566268603234438</v>
+        <v>0.06578454188203955</v>
       </c>
       <c r="C33">
-        <v>33945.83344786078</v>
+        <v>33160.54405328147</v>
       </c>
       <c r="D33">
-        <v>45188.54544786078</v>
+        <v>44913.00805328147</v>
       </c>
       <c r="E33">
-        <v>-5138.888000000003</v>
+        <v>-4629.136</v>
       </c>
       <c r="F33">
-        <v>15802.312</v>
+        <v>16312.064</v>
       </c>
       <c r="G33">
         <v>4559.6</v>
@@ -3999,45 +3999,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M33">
-        <v>858.0655416</v>
+        <v>902.0571392000001</v>
       </c>
       <c r="N33">
-        <v>2837.258948195918</v>
+        <v>2793.267350595918</v>
       </c>
       <c r="O33">
-        <v>732.012808634547</v>
+        <v>720.662976453747</v>
       </c>
       <c r="P33">
-        <v>2105.246139561371</v>
+        <v>2072.604374142171</v>
       </c>
       <c r="Q33">
-        <v>4041.146139561372</v>
+        <v>4008.504374142172</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0770617391773107</v>
+        <v>0.07743251453241111</v>
       </c>
       <c r="T33">
-        <v>0.7219801195683764</v>
+        <v>0.7305430607947138</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.306576025539258</v>
+        <v>4.096552567693395</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06578454188203955</v>
+        <v>0.06567637773173474</v>
       </c>
       <c r="C34">
-        <v>33160.54405328147</v>
+        <v>32895.2016443691</v>
       </c>
       <c r="D34">
-        <v>44913.00805328147</v>
+        <v>45157.4176443691</v>
       </c>
       <c r="E34">
-        <v>-4629.136</v>
+        <v>-4119.384000000002</v>
       </c>
       <c r="F34">
-        <v>16312.064</v>
+        <v>16821.816</v>
       </c>
       <c r="G34">
         <v>4559.6</v>
@@ -4081,28 +4081,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M34">
-        <v>902.0571392000001</v>
+        <v>930.2464248</v>
       </c>
       <c r="N34">
-        <v>2793.267350595918</v>
+        <v>2765.078064995918</v>
       </c>
       <c r="O34">
-        <v>720.662976453747</v>
+        <v>713.3901407689469</v>
       </c>
       <c r="P34">
-        <v>2072.604374142171</v>
+        <v>2051.687924226972</v>
       </c>
       <c r="Q34">
-        <v>4008.504374142172</v>
+        <v>3987.587924226972</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07743251453241111</v>
+        <v>0.0778143578085593</v>
       </c>
       <c r="T34">
-        <v>0.7305430607947138</v>
+        <v>0.739361612206912</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.096552567693395</v>
+        <v>3.972414611096625</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06567637773173474</v>
+        <v>0.06556821358142989</v>
       </c>
       <c r="C35">
-        <v>32895.2016443691</v>
+        <v>32632.53386820876</v>
       </c>
       <c r="D35">
-        <v>45157.4176443691</v>
+        <v>45404.50186820876</v>
       </c>
       <c r="E35">
-        <v>-4119.384000000002</v>
+        <v>-3609.632000000001</v>
       </c>
       <c r="F35">
-        <v>16821.816</v>
+        <v>17331.568</v>
       </c>
       <c r="G35">
         <v>4559.6</v>
@@ -4163,28 +4163,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M35">
-        <v>930.2464248</v>
+        <v>958.4357103999999</v>
       </c>
       <c r="N35">
-        <v>2765.078064995918</v>
+        <v>2736.888779395918</v>
       </c>
       <c r="O35">
-        <v>713.3901407689469</v>
+        <v>706.117305084147</v>
       </c>
       <c r="P35">
-        <v>2051.687924226972</v>
+        <v>2030.771474311771</v>
       </c>
       <c r="Q35">
-        <v>3987.587924226972</v>
+        <v>3966.671474311772</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0778143578085593</v>
+        <v>0.07820777209307561</v>
       </c>
       <c r="T35">
-        <v>0.739361612206912</v>
+        <v>0.7484473924497829</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.972414611096625</v>
+        <v>3.855578887240843</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06556821358142989</v>
+        <v>0.06546004943112506</v>
       </c>
       <c r="C36">
-        <v>32632.53386820876</v>
+        <v>32372.58487006764</v>
       </c>
       <c r="D36">
-        <v>45404.50186820876</v>
+        <v>45654.30487006764</v>
       </c>
       <c r="E36">
-        <v>-3609.632000000001</v>
+        <v>-3099.880000000001</v>
       </c>
       <c r="F36">
-        <v>17331.568</v>
+        <v>17841.32</v>
       </c>
       <c r="G36">
         <v>4559.6</v>
@@ -4245,28 +4245,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M36">
-        <v>958.4357103999999</v>
+        <v>986.624996</v>
       </c>
       <c r="N36">
-        <v>2736.888779395918</v>
+        <v>2708.699493795918</v>
       </c>
       <c r="O36">
-        <v>706.117305084147</v>
+        <v>698.844469399347</v>
       </c>
       <c r="P36">
-        <v>2030.771474311771</v>
+        <v>2009.855024396571</v>
       </c>
       <c r="Q36">
-        <v>3966.671474311772</v>
+        <v>3945.755024396572</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07820777209307561</v>
+        <v>0.07861329143250011</v>
       </c>
       <c r="T36">
-        <v>0.7484473924497829</v>
+        <v>0.7578127351616651</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.855578887240843</v>
+        <v>3.745419490462533</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06546004943112506</v>
+        <v>0.06535188528082023</v>
       </c>
       <c r="C37">
-        <v>32372.58487006764</v>
+        <v>32115.39977208771</v>
       </c>
       <c r="D37">
-        <v>45654.30487006764</v>
+        <v>45906.87177208771</v>
       </c>
       <c r="E37">
-        <v>-3099.880000000001</v>
+        <v>-2590.128000000001</v>
       </c>
       <c r="F37">
-        <v>17841.32</v>
+        <v>18351.072</v>
       </c>
       <c r="G37">
         <v>4559.6</v>
@@ -4327,28 +4327,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M37">
-        <v>986.624996</v>
+        <v>1014.8142816</v>
       </c>
       <c r="N37">
-        <v>2708.699493795918</v>
+        <v>2680.510208195918</v>
       </c>
       <c r="O37">
-        <v>698.844469399347</v>
+        <v>691.571633714547</v>
       </c>
       <c r="P37">
-        <v>2009.855024396571</v>
+        <v>1988.938574481371</v>
       </c>
       <c r="Q37">
-        <v>3945.755024396572</v>
+        <v>3924.838574481372</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07861329143250011</v>
+        <v>0.07903148325128162</v>
       </c>
       <c r="T37">
-        <v>0.7578127351616651</v>
+        <v>0.7674707448332938</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.745419490462533</v>
+        <v>3.641380060171907</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06535188528082024</v>
+        <v>0.06524372113051541</v>
       </c>
       <c r="C38">
-        <v>32115.39977208768</v>
+        <v>31861.024700457</v>
       </c>
       <c r="D38">
-        <v>45906.87177208767</v>
+        <v>46162.248700457</v>
       </c>
       <c r="E38">
-        <v>-2590.128000000004</v>
+        <v>-2080.376000000004</v>
       </c>
       <c r="F38">
-        <v>18351.072</v>
+        <v>18860.824</v>
       </c>
       <c r="G38">
         <v>4559.6</v>
@@ -4409,28 +4409,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M38">
-        <v>1014.8142816</v>
+        <v>1043.0035672</v>
       </c>
       <c r="N38">
-        <v>2680.510208195918</v>
+        <v>2652.320922595919</v>
       </c>
       <c r="O38">
-        <v>691.571633714547</v>
+        <v>684.298798029747</v>
       </c>
       <c r="P38">
-        <v>1988.938574481371</v>
+        <v>1968.022124566171</v>
       </c>
       <c r="Q38">
-        <v>3924.838574481372</v>
+        <v>3903.922124566172</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07903148325128162</v>
+        <v>0.07946295100081811</v>
       </c>
       <c r="T38">
-        <v>0.7674707448332938</v>
+        <v>0.7774353579865614</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.641380060171907</v>
+        <v>3.542964382869964</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06524372113051541</v>
+        <v>0.06513555698021059</v>
       </c>
       <c r="C39">
-        <v>31861.024700457</v>
+        <v>31609.50681349314</v>
       </c>
       <c r="D39">
-        <v>46162.248700457</v>
+        <v>46420.48281349314</v>
       </c>
       <c r="E39">
-        <v>-2080.376000000004</v>
+        <v>-1570.624</v>
       </c>
       <c r="F39">
-        <v>18860.824</v>
+        <v>19370.576</v>
       </c>
       <c r="G39">
         <v>4559.6</v>
@@ -4491,28 +4491,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M39">
-        <v>1043.0035672</v>
+        <v>1071.1928528</v>
       </c>
       <c r="N39">
-        <v>2652.320922595919</v>
+        <v>2624.131636995919</v>
       </c>
       <c r="O39">
-        <v>684.298798029747</v>
+        <v>677.0259623449471</v>
       </c>
       <c r="P39">
-        <v>1968.022124566171</v>
+        <v>1947.105674650972</v>
       </c>
       <c r="Q39">
-        <v>3903.922124566172</v>
+        <v>3883.005674650972</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07946295100081811</v>
+        <v>0.07990833706485578</v>
       </c>
       <c r="T39">
-        <v>0.7774353579865614</v>
+        <v>0.7877214102738054</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.542964382869964</v>
+        <v>3.449728478057596</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06513555698021059</v>
+        <v>0.06502739282990576</v>
       </c>
       <c r="C40">
-        <v>31609.50681349314</v>
+        <v>31360.8943306747</v>
       </c>
       <c r="D40">
-        <v>46420.48281349314</v>
+        <v>46681.6223306747</v>
       </c>
       <c r="E40">
-        <v>-1570.624</v>
+        <v>-1060.871999999999</v>
       </c>
       <c r="F40">
-        <v>19370.576</v>
+        <v>19880.328</v>
       </c>
       <c r="G40">
         <v>4559.6</v>
@@ -4573,28 +4573,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M40">
-        <v>1071.1928528</v>
+        <v>1099.3821384</v>
       </c>
       <c r="N40">
-        <v>2624.131636995919</v>
+        <v>2595.942351395918</v>
       </c>
       <c r="O40">
-        <v>677.0259623449471</v>
+        <v>669.7531266601469</v>
       </c>
       <c r="P40">
-        <v>1947.105674650972</v>
+        <v>1926.189224735771</v>
       </c>
       <c r="Q40">
-        <v>3883.005674650972</v>
+        <v>3862.089224735772</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07990833706485578</v>
+        <v>0.08036832595066518</v>
       </c>
       <c r="T40">
-        <v>0.7877214102738054</v>
+        <v>0.7983447101770246</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.449728478057596</v>
+        <v>3.361273901697145</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06502739282990576</v>
+        <v>0.06491922867960093</v>
       </c>
       <c r="C41">
-        <v>31360.8943306747</v>
+        <v>31115.2365626578</v>
       </c>
       <c r="D41">
-        <v>46681.6223306747</v>
+        <v>46945.7165626578</v>
       </c>
       <c r="E41">
-        <v>-1060.871999999999</v>
+        <v>-551.119999999999</v>
       </c>
       <c r="F41">
-        <v>19880.328</v>
+        <v>20390.08</v>
       </c>
       <c r="G41">
         <v>4559.6</v>
@@ -4655,28 +4655,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M41">
-        <v>1099.3821384</v>
+        <v>1127.571424</v>
       </c>
       <c r="N41">
-        <v>2595.942351395918</v>
+        <v>2567.753065795918</v>
       </c>
       <c r="O41">
-        <v>669.7531266601469</v>
+        <v>662.480290975347</v>
       </c>
       <c r="P41">
-        <v>1926.189224735771</v>
+        <v>1905.272774820571</v>
       </c>
       <c r="Q41">
-        <v>3862.089224735772</v>
+        <v>3841.172774820572</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08036832595066518</v>
+        <v>0.08084364779933488</v>
       </c>
       <c r="T41">
-        <v>0.7983447101770246</v>
+        <v>0.8093221200770179</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.361273901697145</v>
+        <v>3.277242054154716</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06491922867960093</v>
+        <v>0.06481106452929609</v>
       </c>
       <c r="C42">
-        <v>31115.2365626578</v>
+        <v>30872.58394231781</v>
       </c>
       <c r="D42">
-        <v>46945.7165626578</v>
+        <v>47212.81594231781</v>
       </c>
       <c r="E42">
-        <v>-551.119999999999</v>
+        <v>-41.36799999999857</v>
       </c>
       <c r="F42">
-        <v>20390.08</v>
+        <v>20899.832</v>
       </c>
       <c r="G42">
         <v>4559.6</v>
@@ -4737,28 +4737,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M42">
-        <v>1127.571424</v>
+        <v>1155.7607096</v>
       </c>
       <c r="N42">
-        <v>2567.753065795918</v>
+        <v>2539.563780195918</v>
       </c>
       <c r="O42">
-        <v>662.480290975347</v>
+        <v>655.2074552905469</v>
       </c>
       <c r="P42">
-        <v>1905.272774820571</v>
+        <v>1884.356324905371</v>
       </c>
       <c r="Q42">
-        <v>3841.172774820572</v>
+        <v>3820.256324905372</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08084364779933488</v>
+        <v>0.08133508225304423</v>
       </c>
       <c r="T42">
-        <v>0.8093221200770179</v>
+        <v>0.8206716455668412</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.277242054154716</v>
+        <v>3.197309321126552</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06481106452929609</v>
+        <v>0.06470290037899126</v>
       </c>
       <c r="C43">
-        <v>30872.58394231781</v>
+        <v>30632.98805685644</v>
       </c>
       <c r="D43">
-        <v>47212.81594231781</v>
+        <v>47482.97205685644</v>
       </c>
       <c r="E43">
-        <v>-41.36799999999857</v>
+        <v>468.3840000000018</v>
       </c>
       <c r="F43">
-        <v>20899.832</v>
+        <v>21409.584</v>
       </c>
       <c r="G43">
         <v>4559.6</v>
@@ -4819,28 +4819,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M43">
-        <v>1155.7607096</v>
+        <v>1183.9499952</v>
       </c>
       <c r="N43">
-        <v>2539.563780195918</v>
+        <v>2511.374494595918</v>
       </c>
       <c r="O43">
-        <v>655.2074552905469</v>
+        <v>647.934619605747</v>
       </c>
       <c r="P43">
-        <v>1884.356324905371</v>
+        <v>1863.439874990171</v>
       </c>
       <c r="Q43">
-        <v>3820.256324905372</v>
+        <v>3799.339874990172</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08133508225304423</v>
+        <v>0.08184346272239873</v>
       </c>
       <c r="T43">
-        <v>0.8206716455668412</v>
+        <v>0.8324125340045897</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.197309321126552</v>
+        <v>3.121182908718777</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06470290037899126</v>
+        <v>0.06459473622868644</v>
       </c>
       <c r="C44">
-        <v>30632.98805685644</v>
+        <v>30396.50168101766</v>
       </c>
       <c r="D44">
-        <v>47482.97205685644</v>
+        <v>47756.23768101766</v>
       </c>
       <c r="E44">
-        <v>468.3839999999982</v>
+        <v>978.1359999999986</v>
       </c>
       <c r="F44">
-        <v>21409.584</v>
+        <v>21919.336</v>
       </c>
       <c r="G44">
         <v>4559.6</v>
@@ -4901,28 +4901,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M44">
-        <v>1183.9499952</v>
+        <v>1212.1392808</v>
       </c>
       <c r="N44">
-        <v>2511.374494595919</v>
+        <v>2483.185208995918</v>
       </c>
       <c r="O44">
-        <v>647.9346196057471</v>
+        <v>640.661783920947</v>
       </c>
       <c r="P44">
-        <v>1863.439874990172</v>
+        <v>1842.523425074971</v>
       </c>
       <c r="Q44">
-        <v>3799.339874990172</v>
+        <v>3778.423425074972</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08184346272239873</v>
+        <v>0.08236968110295867</v>
       </c>
       <c r="T44">
-        <v>0.8324125340045897</v>
+        <v>0.8445653834401539</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.121182908718778</v>
+        <v>3.048597259678806</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06459473622868644</v>
+        <v>0.06530277207838162</v>
       </c>
       <c r="C45">
-        <v>30396.50168101766</v>
+        <v>28152.98956789994</v>
       </c>
       <c r="D45">
-        <v>47756.23768101766</v>
+        <v>46022.47756789994</v>
       </c>
       <c r="E45">
-        <v>978.1359999999986</v>
+        <v>1487.887999999999</v>
       </c>
       <c r="F45">
-        <v>21919.336</v>
+        <v>22429.088</v>
       </c>
       <c r="G45">
         <v>4559.6</v>
@@ -4983,45 +4983,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M45">
-        <v>1212.1392808</v>
+        <v>1296.4012864</v>
       </c>
       <c r="N45">
-        <v>2483.185208995918</v>
+        <v>2398.923203395918</v>
       </c>
       <c r="O45">
-        <v>640.661783920947</v>
+        <v>618.922186476147</v>
       </c>
       <c r="P45">
-        <v>1842.523425074971</v>
+        <v>1780.001016919771</v>
       </c>
       <c r="Q45">
-        <v>3778.423425074972</v>
+        <v>3715.901016919772</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08236968110295867</v>
+        <v>0.08291469299711002</v>
       </c>
       <c r="T45">
-        <v>0.8445653834401539</v>
+        <v>0.8571522632127023</v>
       </c>
       <c r="U45">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.048597259678806</v>
+        <v>2.850448027599179</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06530277207838162</v>
+        <v>0.06521315792807679</v>
       </c>
       <c r="C46">
-        <v>28152.98956789994</v>
+        <v>27855.68446795866</v>
       </c>
       <c r="D46">
-        <v>46022.47756789994</v>
+        <v>46234.92446795866</v>
       </c>
       <c r="E46">
-        <v>1487.887999999999</v>
+        <v>1997.639999999999</v>
       </c>
       <c r="F46">
-        <v>22429.088</v>
+        <v>22938.84</v>
       </c>
       <c r="G46">
         <v>4559.6</v>
@@ -5065,28 +5065,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M46">
-        <v>1296.4012864</v>
+        <v>1325.864952</v>
       </c>
       <c r="N46">
-        <v>2398.923203395918</v>
+        <v>2369.459537795919</v>
       </c>
       <c r="O46">
-        <v>618.922186476147</v>
+        <v>611.320560751347</v>
       </c>
       <c r="P46">
-        <v>1780.001016919771</v>
+        <v>1758.138977044572</v>
       </c>
       <c r="Q46">
-        <v>3715.901016919772</v>
+        <v>3694.038977044572</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08291469299711002</v>
+        <v>0.08347952350559415</v>
       </c>
       <c r="T46">
-        <v>0.8571522632127023</v>
+        <v>0.8701968477042528</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.850448027599179</v>
+        <v>2.787104738096975</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06521315792807679</v>
+        <v>0.06512354377777196</v>
       </c>
       <c r="C47">
-        <v>27855.68446795866</v>
+        <v>27560.34983975409</v>
       </c>
       <c r="D47">
-        <v>46234.92446795866</v>
+        <v>46449.3418397541</v>
       </c>
       <c r="E47">
-        <v>1997.639999999999</v>
+        <v>2507.392</v>
       </c>
       <c r="F47">
-        <v>22938.84</v>
+        <v>23448.592</v>
       </c>
       <c r="G47">
         <v>4559.6</v>
@@ -5147,28 +5147,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M47">
-        <v>1325.864952</v>
+        <v>1355.3286176</v>
       </c>
       <c r="N47">
-        <v>2369.459537795919</v>
+        <v>2339.995872195918</v>
       </c>
       <c r="O47">
-        <v>611.320560751347</v>
+        <v>603.7189350265469</v>
       </c>
       <c r="P47">
-        <v>1758.138977044572</v>
+        <v>1736.276937169371</v>
       </c>
       <c r="Q47">
-        <v>3694.038977044572</v>
+        <v>3672.176937169372</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08347952350559415</v>
+        <v>0.08406527366254066</v>
       </c>
       <c r="T47">
-        <v>0.8701968477042528</v>
+        <v>0.8837245649547495</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.787104738096975</v>
+        <v>2.726515504660084</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06512354377777196</v>
+        <v>0.06503392962746712</v>
       </c>
       <c r="C48">
-        <v>27560.34983975409</v>
+        <v>27267.01322557543</v>
       </c>
       <c r="D48">
-        <v>46449.3418397541</v>
+        <v>46665.75722557543</v>
       </c>
       <c r="E48">
-        <v>2507.392</v>
+        <v>3017.144</v>
       </c>
       <c r="F48">
-        <v>23448.592</v>
+        <v>23958.344</v>
       </c>
       <c r="G48">
         <v>4559.6</v>
@@ -5229,28 +5229,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M48">
-        <v>1355.3286176</v>
+        <v>1384.7922832</v>
       </c>
       <c r="N48">
-        <v>2339.995872195918</v>
+        <v>2310.532206595918</v>
       </c>
       <c r="O48">
-        <v>603.7189350265469</v>
+        <v>596.1173093017469</v>
       </c>
       <c r="P48">
-        <v>1736.276937169371</v>
+        <v>1714.414897294171</v>
       </c>
       <c r="Q48">
-        <v>3672.176937169372</v>
+        <v>3650.314897294172</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08406527366254066</v>
+        <v>0.08467312759899456</v>
       </c>
       <c r="T48">
-        <v>0.8837245649547495</v>
+        <v>0.8977627621014911</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.726515504660084</v>
+        <v>2.668504536475827</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06503392962746712</v>
+        <v>0.0649443154771623</v>
       </c>
       <c r="C49">
-        <v>27267.01322557543</v>
+        <v>26975.70268341129</v>
       </c>
       <c r="D49">
-        <v>46665.75722557543</v>
+        <v>46884.1986834113</v>
       </c>
       <c r="E49">
-        <v>3017.144</v>
+        <v>3526.896000000001</v>
       </c>
       <c r="F49">
-        <v>23958.344</v>
+        <v>24468.096</v>
       </c>
       <c r="G49">
         <v>4559.6</v>
@@ -5311,28 +5311,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M49">
-        <v>1384.7922832</v>
+        <v>1414.2559488</v>
       </c>
       <c r="N49">
-        <v>2310.532206595918</v>
+        <v>2281.068540995918</v>
       </c>
       <c r="O49">
-        <v>596.1173093017469</v>
+        <v>588.5156835769469</v>
       </c>
       <c r="P49">
-        <v>1714.414897294171</v>
+        <v>1692.552857418971</v>
       </c>
       <c r="Q49">
-        <v>3650.314897294172</v>
+        <v>3628.452857418972</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08467312759899456</v>
+        <v>0.08530436053300441</v>
       </c>
       <c r="T49">
-        <v>0.8977627621014911</v>
+        <v>0.9123408899077231</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.668504536475827</v>
+        <v>2.612910691965914</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0649443154771623</v>
+        <v>0.06485470132685747</v>
       </c>
       <c r="C50">
-        <v>26975.7026834113</v>
+        <v>26686.44679907671</v>
       </c>
       <c r="D50">
-        <v>46884.1986834113</v>
+        <v>47104.69479907671</v>
       </c>
       <c r="E50">
-        <v>3526.895999999997</v>
+        <v>4036.647999999997</v>
       </c>
       <c r="F50">
-        <v>24468.096</v>
+        <v>24977.848</v>
       </c>
       <c r="G50">
         <v>4559.6</v>
@@ -5393,28 +5393,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M50">
-        <v>1414.2559488</v>
+        <v>1443.7196144</v>
       </c>
       <c r="N50">
-        <v>2281.068540995919</v>
+        <v>2251.604875395918</v>
       </c>
       <c r="O50">
-        <v>588.515683576947</v>
+        <v>580.914057852147</v>
       </c>
       <c r="P50">
-        <v>1692.552857418972</v>
+        <v>1670.690817543772</v>
       </c>
       <c r="Q50">
-        <v>3628.452857418972</v>
+        <v>3606.590817543772</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08530436053300441</v>
+        <v>0.08596034769972052</v>
       </c>
       <c r="T50">
-        <v>0.912340889907723</v>
+        <v>0.9274907090004738</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.612910691965914</v>
+        <v>2.55958598396661</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06485470132685747</v>
+        <v>0.06476508717655263</v>
       </c>
       <c r="C51">
-        <v>26686.44679907671</v>
+        <v>26399.27469868334</v>
       </c>
       <c r="D51">
-        <v>47104.69479907671</v>
+        <v>47327.27469868334</v>
       </c>
       <c r="E51">
-        <v>4036.647999999997</v>
+        <v>4546.399999999998</v>
       </c>
       <c r="F51">
-        <v>24977.848</v>
+        <v>25487.6</v>
       </c>
       <c r="G51">
         <v>4559.6</v>
@@ -5475,28 +5475,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M51">
-        <v>1443.7196144</v>
+        <v>1473.18328</v>
       </c>
       <c r="N51">
-        <v>2251.604875395918</v>
+        <v>2222.141209795918</v>
       </c>
       <c r="O51">
-        <v>580.914057852147</v>
+        <v>573.3124321273469</v>
       </c>
       <c r="P51">
-        <v>1670.690817543772</v>
+        <v>1648.828777668571</v>
       </c>
       <c r="Q51">
-        <v>3606.590817543772</v>
+        <v>3584.728777668572</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08596034769972052</v>
+        <v>0.08664257435310527</v>
       </c>
       <c r="T51">
-        <v>0.9274907090004738</v>
+        <v>0.9432465208569346</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.55958598396661</v>
+        <v>2.508394264287277</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06476508717655263</v>
+        <v>0.06599994302624781</v>
       </c>
       <c r="C52">
-        <v>26399.27469868334</v>
+        <v>22996.32830027044</v>
       </c>
       <c r="D52">
-        <v>47327.27469868334</v>
+        <v>44434.08030027044</v>
       </c>
       <c r="E52">
-        <v>4546.399999999998</v>
+        <v>5056.151999999998</v>
       </c>
       <c r="F52">
-        <v>25487.6</v>
+        <v>25997.352</v>
       </c>
       <c r="G52">
         <v>4559.6</v>
@@ -5557,45 +5557,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M52">
-        <v>1473.18328</v>
+        <v>1593.6376776</v>
       </c>
       <c r="N52">
-        <v>2222.141209795918</v>
+        <v>2101.686812195919</v>
       </c>
       <c r="O52">
-        <v>573.3124321273469</v>
+        <v>542.2351975465471</v>
       </c>
       <c r="P52">
-        <v>1648.828777668571</v>
+        <v>1559.451614649372</v>
       </c>
       <c r="Q52">
-        <v>3584.728777668572</v>
+        <v>3495.351614649372</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08664257435310527</v>
+        <v>0.08735264699234246</v>
       </c>
       <c r="T52">
-        <v>0.9432465208569346</v>
+        <v>0.9596454270748837</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.508394264287277</v>
+        <v>2.318798395480354</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06599994302624781</v>
+        <v>0.06593629887594298</v>
       </c>
       <c r="C53">
-        <v>22996.32830027044</v>
+        <v>22627.01766453059</v>
       </c>
       <c r="D53">
-        <v>44434.08030027044</v>
+        <v>44574.52166453059</v>
       </c>
       <c r="E53">
-        <v>5056.151999999998</v>
+        <v>5565.903999999999</v>
       </c>
       <c r="F53">
-        <v>25997.352</v>
+        <v>26507.104</v>
       </c>
       <c r="G53">
         <v>4559.6</v>
@@ -5639,28 +5639,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M53">
-        <v>1593.6376776</v>
+        <v>1624.8854752</v>
       </c>
       <c r="N53">
-        <v>2101.686812195919</v>
+        <v>2070.439014595919</v>
       </c>
       <c r="O53">
-        <v>542.2351975465471</v>
+        <v>534.173265765747</v>
       </c>
       <c r="P53">
-        <v>1559.451614649372</v>
+        <v>1536.265748830172</v>
       </c>
       <c r="Q53">
-        <v>3495.351614649372</v>
+        <v>3472.165748830172</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08735264699234246</v>
+        <v>0.08809230599154788</v>
       </c>
       <c r="T53">
-        <v>0.9596454270748837</v>
+        <v>0.9767276210519139</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.318798395480354</v>
+        <v>2.274206118644194</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06593629887594298</v>
+        <v>0.06697378272563816</v>
       </c>
       <c r="C54">
-        <v>22627.01766453059</v>
+        <v>19933.18042411474</v>
       </c>
       <c r="D54">
-        <v>44574.52166453059</v>
+        <v>42390.43642411474</v>
       </c>
       <c r="E54">
-        <v>5565.903999999999</v>
+        <v>6075.655999999999</v>
       </c>
       <c r="F54">
-        <v>26507.104</v>
+        <v>27016.856</v>
       </c>
       <c r="G54">
         <v>4559.6</v>
@@ -5721,45 +5721,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M54">
-        <v>1624.8854752</v>
+        <v>1731.7804696</v>
       </c>
       <c r="N54">
-        <v>2070.439014595919</v>
+        <v>1963.544020195918</v>
       </c>
       <c r="O54">
-        <v>534.173265765747</v>
+        <v>506.5943572105469</v>
       </c>
       <c r="P54">
-        <v>1536.265748830172</v>
+        <v>1456.949662985372</v>
       </c>
       <c r="Q54">
-        <v>3472.165748830172</v>
+        <v>3392.849662985372</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08809230599154788</v>
+        <v>0.0888634398417833</v>
       </c>
       <c r="T54">
-        <v>0.9767276210519139</v>
+        <v>0.9945367169003071</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.274206118644194</v>
+        <v>2.133829636414279</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06697378272563816</v>
+        <v>0.06693091457533333</v>
       </c>
       <c r="C55">
-        <v>19933.18042411474</v>
+        <v>19509.42562947173</v>
       </c>
       <c r="D55">
-        <v>42390.43642411474</v>
+        <v>42476.43362947174</v>
       </c>
       <c r="E55">
-        <v>6075.655999999999</v>
+        <v>6585.407999999999</v>
       </c>
       <c r="F55">
-        <v>27016.856</v>
+        <v>27526.608</v>
       </c>
       <c r="G55">
         <v>4559.6</v>
@@ -5803,28 +5803,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M55">
-        <v>1731.7804696</v>
+        <v>1764.4555728</v>
       </c>
       <c r="N55">
-        <v>1963.544020195918</v>
+        <v>1930.868916995918</v>
       </c>
       <c r="O55">
-        <v>506.5943572105469</v>
+        <v>498.164180584947</v>
       </c>
       <c r="P55">
-        <v>1456.949662985372</v>
+        <v>1432.704736410971</v>
       </c>
       <c r="Q55">
-        <v>3392.849662985372</v>
+        <v>3368.604736410972</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0888634398417833</v>
+        <v>0.08966810125072462</v>
       </c>
       <c r="T55">
-        <v>0.9945367169003071</v>
+        <v>1.013120121263848</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.133829636414279</v>
+        <v>2.094314272776978</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06693091457533333</v>
+        <v>0.06688804642502849</v>
       </c>
       <c r="C56">
-        <v>19509.42562947173</v>
+        <v>19086.02046808077</v>
       </c>
       <c r="D56">
-        <v>42476.43362947174</v>
+        <v>42562.78046808077</v>
       </c>
       <c r="E56">
-        <v>6585.407999999999</v>
+        <v>7095.16</v>
       </c>
       <c r="F56">
-        <v>27526.608</v>
+        <v>28036.36</v>
       </c>
       <c r="G56">
         <v>4559.6</v>
@@ -5885,28 +5885,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M56">
-        <v>1764.4555728</v>
+        <v>1797.130676</v>
       </c>
       <c r="N56">
-        <v>1930.868916995918</v>
+        <v>1898.193813795918</v>
       </c>
       <c r="O56">
-        <v>498.164180584947</v>
+        <v>489.7340039593469</v>
       </c>
       <c r="P56">
-        <v>1432.704736410971</v>
+        <v>1408.459809836571</v>
       </c>
       <c r="Q56">
-        <v>3368.604736410972</v>
+        <v>3344.359809836572</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08966810125072462</v>
+        <v>0.09050852538895221</v>
       </c>
       <c r="T56">
-        <v>1.013120121263848</v>
+        <v>1.032529454710213</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.094314272776978</v>
+        <v>2.05623583145376</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06688804642502849</v>
+        <v>0.06684517827472367</v>
       </c>
       <c r="C57">
-        <v>19086.02046808077</v>
+        <v>18662.96707650684</v>
       </c>
       <c r="D57">
-        <v>42562.78046808077</v>
+        <v>42649.47907650684</v>
       </c>
       <c r="E57">
-        <v>7095.16</v>
+        <v>7604.912</v>
       </c>
       <c r="F57">
-        <v>28036.36</v>
+        <v>28546.112</v>
       </c>
       <c r="G57">
         <v>4559.6</v>
@@ -5967,28 +5967,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M57">
-        <v>1797.130676</v>
+        <v>1829.8057792</v>
       </c>
       <c r="N57">
-        <v>1898.193813795918</v>
+        <v>1865.518710595918</v>
       </c>
       <c r="O57">
-        <v>489.7340039593469</v>
+        <v>481.3038273337469</v>
       </c>
       <c r="P57">
-        <v>1408.459809836571</v>
+        <v>1384.214883262171</v>
       </c>
       <c r="Q57">
-        <v>3344.359809836572</v>
+        <v>3320.114883262172</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09050852538895221</v>
+        <v>0.09138715062437197</v>
       </c>
       <c r="T57">
-        <v>1.032529454710213</v>
+        <v>1.052821030585958</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.05623583145376</v>
+        <v>2.019517334463514</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06684517827472367</v>
+        <v>0.07010124212441883</v>
       </c>
       <c r="C58">
-        <v>18662.96707650684</v>
+        <v>12438.71594439034</v>
       </c>
       <c r="D58">
-        <v>42649.47907650684</v>
+        <v>36934.97994439034</v>
       </c>
       <c r="E58">
-        <v>7604.912</v>
+        <v>8114.664000000001</v>
       </c>
       <c r="F58">
-        <v>28546.112</v>
+        <v>29055.864</v>
       </c>
       <c r="G58">
         <v>4559.6</v>
@@ -6049,45 +6049,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M58">
-        <v>1829.8057792</v>
+        <v>2089.1166216</v>
       </c>
       <c r="N58">
-        <v>1865.518710595918</v>
+        <v>1606.207868195918</v>
       </c>
       <c r="O58">
-        <v>481.3038273337469</v>
+        <v>414.4016299945469</v>
       </c>
       <c r="P58">
-        <v>1384.214883262171</v>
+        <v>1191.806238201371</v>
       </c>
       <c r="Q58">
-        <v>3320.114883262172</v>
+        <v>3127.706238201372</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09138715062437197</v>
+        <v>0.09230664214981124</v>
       </c>
       <c r="T58">
-        <v>1.052821030585958</v>
+        <v>1.074056400688481</v>
       </c>
       <c r="U58">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.019517334463514</v>
+        <v>1.768845478317896</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07010124212441883</v>
+        <v>0.07179465397411401</v>
       </c>
       <c r="C59">
-        <v>12438.71594439034</v>
+        <v>9522.848718991714</v>
       </c>
       <c r="D59">
-        <v>36934.97994439034</v>
+        <v>34528.86471899172</v>
       </c>
       <c r="E59">
-        <v>8114.664000000001</v>
+        <v>8624.416000000001</v>
       </c>
       <c r="F59">
-        <v>29055.864</v>
+        <v>29565.616</v>
       </c>
       <c r="G59">
         <v>4559.6</v>
@@ -6131,45 +6131,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M59">
-        <v>2089.1166216</v>
+        <v>2241.0736928</v>
       </c>
       <c r="N59">
-        <v>1606.207868195918</v>
+        <v>1454.250796995918</v>
       </c>
       <c r="O59">
-        <v>414.4016299945469</v>
+        <v>375.196705624947</v>
       </c>
       <c r="P59">
-        <v>1191.806238201371</v>
+        <v>1079.054091370971</v>
       </c>
       <c r="Q59">
-        <v>3127.706238201372</v>
+        <v>3014.954091370972</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09230664214981124</v>
+        <v>0.09326991898598574</v>
       </c>
       <c r="T59">
-        <v>1.074056400688481</v>
+        <v>1.096302978891126</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.768845478317896</v>
+        <v>1.648908066552232</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07179465397411401</v>
+        <v>0.07183859982380918</v>
       </c>
       <c r="C60">
-        <v>9522.848718991721</v>
+        <v>8954.821684644521</v>
       </c>
       <c r="D60">
-        <v>34528.86471899172</v>
+        <v>34470.58968464452</v>
       </c>
       <c r="E60">
-        <v>8624.415999999994</v>
+        <v>9134.167999999994</v>
       </c>
       <c r="F60">
-        <v>29565.61599999999</v>
+        <v>30075.36799999999</v>
       </c>
       <c r="G60">
         <v>4559.6</v>
@@ -6213,28 +6213,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M60">
-        <v>2241.0736928</v>
+        <v>2279.7128944</v>
       </c>
       <c r="N60">
-        <v>1454.250796995919</v>
+        <v>1415.611595395919</v>
       </c>
       <c r="O60">
-        <v>375.1967056249471</v>
+        <v>365.2277916121471</v>
       </c>
       <c r="P60">
-        <v>1079.054091370972</v>
+        <v>1050.383803783772</v>
       </c>
       <c r="Q60">
-        <v>3014.954091370972</v>
+        <v>2986.283803783772</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09326991898598574</v>
+        <v>0.09428018493611995</v>
       </c>
       <c r="T60">
-        <v>1.096302978891125</v>
+        <v>1.119634756030484</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.648908066552232</v>
+        <v>1.620960472203889</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07183859982380918</v>
+        <v>0.07188254567350436</v>
       </c>
       <c r="C61">
-        <v>8954.821684644521</v>
+        <v>8386.991022686139</v>
       </c>
       <c r="D61">
-        <v>34470.58968464452</v>
+        <v>34412.51102268614</v>
       </c>
       <c r="E61">
-        <v>9134.167999999994</v>
+        <v>9643.919999999995</v>
       </c>
       <c r="F61">
-        <v>30075.36799999999</v>
+        <v>30585.12</v>
       </c>
       <c r="G61">
         <v>4559.6</v>
@@ -6295,28 +6295,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M61">
-        <v>2279.7128944</v>
+        <v>2318.352096</v>
       </c>
       <c r="N61">
-        <v>1415.611595395919</v>
+        <v>1376.972393795919</v>
       </c>
       <c r="O61">
-        <v>365.2277916121471</v>
+        <v>355.258877599347</v>
       </c>
       <c r="P61">
-        <v>1050.383803783772</v>
+        <v>1021.713516196572</v>
       </c>
       <c r="Q61">
-        <v>2986.283803783772</v>
+        <v>2957.613516196572</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09428018493611995</v>
+        <v>0.09534096418376087</v>
       </c>
       <c r="T61">
-        <v>1.119634756030484</v>
+        <v>1.14413312202681</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.620960472203889</v>
+        <v>1.593944464333824</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07188254567350436</v>
+        <v>0.07192649152319952</v>
       </c>
       <c r="C62">
-        <v>8386.991022686139</v>
+        <v>7819.355742196938</v>
       </c>
       <c r="D62">
-        <v>34412.51102268614</v>
+        <v>34354.62774219694</v>
       </c>
       <c r="E62">
-        <v>9643.919999999995</v>
+        <v>10153.672</v>
       </c>
       <c r="F62">
-        <v>30585.12</v>
+        <v>31094.872</v>
       </c>
       <c r="G62">
         <v>4559.6</v>
@@ -6377,28 +6377,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M62">
-        <v>2318.352096</v>
+        <v>2356.9912976</v>
       </c>
       <c r="N62">
-        <v>1376.972393795919</v>
+        <v>1338.333192195918</v>
       </c>
       <c r="O62">
-        <v>355.258877599347</v>
+        <v>345.2899635865469</v>
       </c>
       <c r="P62">
-        <v>1021.713516196572</v>
+        <v>993.0432286093715</v>
       </c>
       <c r="Q62">
-        <v>2957.613516196572</v>
+        <v>2928.943228609372</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09534096418376087</v>
+        <v>0.09645614236717825</v>
       </c>
       <c r="T62">
-        <v>1.14413312202681</v>
+        <v>1.169887814484486</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.593944464333824</v>
+        <v>1.567814227213598</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07192649152319952</v>
+        <v>0.07197043737289469</v>
       </c>
       <c r="C63">
-        <v>7819.355742196938</v>
+        <v>7251.914858913093</v>
       </c>
       <c r="D63">
-        <v>34354.62774219694</v>
+        <v>34296.93885891309</v>
       </c>
       <c r="E63">
-        <v>10153.672</v>
+        <v>10663.424</v>
       </c>
       <c r="F63">
-        <v>31094.872</v>
+        <v>31604.624</v>
       </c>
       <c r="G63">
         <v>4559.6</v>
@@ -6459,28 +6459,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M63">
-        <v>2356.9912976</v>
+        <v>2395.6304992</v>
       </c>
       <c r="N63">
-        <v>1338.333192195918</v>
+        <v>1299.693990595918</v>
       </c>
       <c r="O63">
-        <v>345.2899635865469</v>
+        <v>335.321049573747</v>
       </c>
       <c r="P63">
-        <v>993.0432286093715</v>
+        <v>964.3729410221715</v>
       </c>
       <c r="Q63">
-        <v>2928.943228609372</v>
+        <v>2900.272941022172</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09645614236717825</v>
+        <v>0.09763001413919656</v>
       </c>
       <c r="T63">
-        <v>1.169887814484486</v>
+        <v>1.196998017071514</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.567814227213598</v>
+        <v>1.542526900968217</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07197043737289469</v>
+        <v>0.07201438322258988</v>
       </c>
       <c r="C64">
-        <v>7251.914858913093</v>
+        <v>6684.667395170876</v>
       </c>
       <c r="D64">
-        <v>34296.93885891309</v>
+        <v>34239.44339517088</v>
       </c>
       <c r="E64">
-        <v>10663.424</v>
+        <v>11173.176</v>
       </c>
       <c r="F64">
-        <v>31604.624</v>
+        <v>32114.376</v>
       </c>
       <c r="G64">
         <v>4559.6</v>
@@ -6541,28 +6541,28 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M64">
-        <v>2395.6304992</v>
+        <v>2434.2697008</v>
       </c>
       <c r="N64">
-        <v>1299.693990595918</v>
+        <v>1261.054788995918</v>
       </c>
       <c r="O64">
-        <v>335.321049573747</v>
+        <v>325.352135560947</v>
       </c>
       <c r="P64">
-        <v>964.3729410221715</v>
+        <v>935.7026534349715</v>
       </c>
       <c r="Q64">
-        <v>2900.272941022172</v>
+        <v>2871.602653434972</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09763001413919656</v>
+        <v>0.09886733843943207</v>
       </c>
       <c r="T64">
-        <v>1.196998017071514</v>
+        <v>1.225573636014597</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.542526900968217</v>
+        <v>1.518042346984594</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07201438322258988</v>
+        <v>0.07880162507228503</v>
       </c>
       <c r="C65">
-        <v>6684.667395170876</v>
+        <v>-866.9009582042672</v>
       </c>
       <c r="D65">
-        <v>34239.44339517088</v>
+        <v>27197.62704179573</v>
       </c>
       <c r="E65">
-        <v>11173.176</v>
+        <v>11682.928</v>
       </c>
       <c r="F65">
-        <v>32114.376</v>
+        <v>32624.128</v>
       </c>
       <c r="G65">
         <v>4559.6</v>
@@ -6623,45 +6623,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M65">
-        <v>2434.2697008</v>
+        <v>2936.17152</v>
       </c>
       <c r="N65">
-        <v>1261.054788995918</v>
+        <v>759.1529697959186</v>
       </c>
       <c r="O65">
-        <v>325.352135560947</v>
+        <v>195.861466207347</v>
       </c>
       <c r="P65">
-        <v>935.7026534349715</v>
+        <v>563.2915035885716</v>
       </c>
       <c r="Q65">
-        <v>2871.602653434972</v>
+        <v>2499.191503588572</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09886733843943207</v>
+        <v>0.1001734029785695</v>
       </c>
       <c r="T65">
-        <v>1.225573636014597</v>
+        <v>1.255736789343407</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.518042346984594</v>
+        <v>1.258551983296915</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07880162507228503</v>
+        <v>0.0941653293906938</v>
       </c>
       <c r="C66">
-        <v>-866.9009582042672</v>
+        <v>-10016.23642215789</v>
       </c>
       <c r="D66">
-        <v>27197.62704179573</v>
+        <v>18558.04357784211</v>
       </c>
       <c r="E66">
-        <v>11682.928</v>
+        <v>12192.68</v>
       </c>
       <c r="F66">
-        <v>32624.128</v>
+        <v>33133.88</v>
       </c>
       <c r="G66">
         <v>4559.6</v>
@@ -6705,45 +6705,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M66">
-        <v>2936.17152</v>
+        <v>3929.678168</v>
       </c>
       <c r="N66">
-        <v>759.1529697959186</v>
+        <v>-234.3536782040815</v>
       </c>
       <c r="O66">
-        <v>195.861466207347</v>
+        <v>-60.46324897665302</v>
       </c>
       <c r="P66">
-        <v>563.2915035885716</v>
+        <v>-173.8904292274285</v>
       </c>
       <c r="Q66">
-        <v>2499.191503588572</v>
+        <v>1762.009570772572</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1001734029785695</v>
+        <v>0.1022240534402074</v>
       </c>
       <c r="T66">
-        <v>1.255736789343407</v>
+        <v>1.303095922406638</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.258</v>
+        <v>0.2426136893679958</v>
       </c>
       <c r="W66">
-        <v>0.06677999999999999</v>
+        <v>0.0898260164409557</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.258551983296915</v>
+        <v>0.9403631370852552</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0941653293906938</v>
+        <v>0.0948933293906938</v>
       </c>
       <c r="C67">
-        <v>-10016.23642215789</v>
+        <v>-10801.183767276</v>
       </c>
       <c r="D67">
-        <v>18558.04357784211</v>
+        <v>18282.848232724</v>
       </c>
       <c r="E67">
-        <v>12192.68</v>
+        <v>12702.432</v>
       </c>
       <c r="F67">
-        <v>33133.88</v>
+        <v>33643.632</v>
       </c>
       <c r="G67">
         <v>4559.6</v>
@@ -6787,37 +6787,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M67">
-        <v>3929.678168</v>
+        <v>3990.1347552</v>
       </c>
       <c r="N67">
-        <v>-234.3536782040815</v>
+        <v>-294.8102654040817</v>
       </c>
       <c r="O67">
-        <v>-60.46324897665302</v>
+        <v>-76.0610484742531</v>
       </c>
       <c r="P67">
-        <v>-173.8904292274285</v>
+        <v>-218.7492169298287</v>
       </c>
       <c r="Q67">
-        <v>1762.009570772572</v>
+        <v>1717.150783070172</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1022240534402074</v>
+        <v>0.1038835844237429</v>
       </c>
       <c r="T67">
-        <v>1.303095922406638</v>
+        <v>1.341422273065656</v>
       </c>
       <c r="U67">
         <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.2426136893679958</v>
+        <v>0.2389377243775717</v>
       </c>
       <c r="W67">
-        <v>0.0898260164409557</v>
+        <v>0.09026198588882001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9403631370852552</v>
+        <v>0.9261152107657815</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0948933293906938</v>
+        <v>0.09562132939069379</v>
       </c>
       <c r="C68">
-        <v>-10801.183767276</v>
+        <v>-11578.08868503634</v>
       </c>
       <c r="D68">
-        <v>18282.848232724</v>
+        <v>18015.69531496366</v>
       </c>
       <c r="E68">
-        <v>12702.432</v>
+        <v>13212.184</v>
       </c>
       <c r="F68">
-        <v>33643.632</v>
+        <v>34153.384</v>
       </c>
       <c r="G68">
         <v>4559.6</v>
@@ -6869,37 +6869,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M68">
-        <v>3990.1347552</v>
+        <v>4050.5913424</v>
       </c>
       <c r="N68">
-        <v>-294.8102654040817</v>
+        <v>-355.2668526040816</v>
       </c>
       <c r="O68">
-        <v>-76.0610484742531</v>
+        <v>-91.65884797185305</v>
       </c>
       <c r="P68">
-        <v>-218.7492169298287</v>
+        <v>-263.6080046322285</v>
       </c>
       <c r="Q68">
-        <v>1717.150783070172</v>
+        <v>1672.291995367772</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1038835844237429</v>
+        <v>0.1056436930426442</v>
       </c>
       <c r="T68">
-        <v>1.341422273065656</v>
+        <v>1.382071432855525</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2389377243775717</v>
+        <v>0.2353714896853691</v>
       </c>
       <c r="W68">
-        <v>0.09026198588882001</v>
+        <v>0.09068494132331523</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9261152107657815</v>
+        <v>0.9122925956797252</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09562132939069379</v>
+        <v>0.09634932939069379</v>
       </c>
       <c r="C69">
-        <v>-11578.08868503634</v>
+        <v>-12347.29865109411</v>
       </c>
       <c r="D69">
-        <v>18015.69531496366</v>
+        <v>17756.23734890589</v>
       </c>
       <c r="E69">
-        <v>13212.184</v>
+        <v>13721.936</v>
       </c>
       <c r="F69">
-        <v>34153.384</v>
+        <v>34663.136</v>
       </c>
       <c r="G69">
         <v>4559.6</v>
@@ -6951,37 +6951,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M69">
-        <v>4050.5913424</v>
+        <v>4111.0479296</v>
       </c>
       <c r="N69">
-        <v>-355.2668526040816</v>
+        <v>-415.7234398040819</v>
       </c>
       <c r="O69">
-        <v>-91.65884797185305</v>
+        <v>-107.2566474694531</v>
       </c>
       <c r="P69">
-        <v>-263.6080046322285</v>
+        <v>-308.4667923346287</v>
       </c>
       <c r="Q69">
-        <v>1672.291995367772</v>
+        <v>1627.433207665372</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1056436930426442</v>
+        <v>0.1075138084502269</v>
       </c>
       <c r="T69">
-        <v>1.382071432855525</v>
+        <v>1.42526116513226</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2353714896853691</v>
+        <v>0.2319101442488196</v>
       </c>
       <c r="W69">
-        <v>0.09068494132331523</v>
+        <v>0.09109545689209</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9122925956797252</v>
+        <v>0.8988765280961998</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09634932939069379</v>
+        <v>0.0970773293906938</v>
       </c>
       <c r="C70">
-        <v>-12347.29865109411</v>
+        <v>-13109.14140822995</v>
       </c>
       <c r="D70">
-        <v>17756.23734890589</v>
+        <v>17504.14659177005</v>
       </c>
       <c r="E70">
-        <v>13721.936</v>
+        <v>14231.688</v>
       </c>
       <c r="F70">
-        <v>34663.136</v>
+        <v>35172.888</v>
       </c>
       <c r="G70">
         <v>4559.6</v>
@@ -7033,37 +7033,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M70">
-        <v>4111.0479296</v>
+        <v>4171.504516800001</v>
       </c>
       <c r="N70">
-        <v>-415.7234398040819</v>
+        <v>-476.1800270040821</v>
       </c>
       <c r="O70">
-        <v>-107.2566474694531</v>
+        <v>-122.8544469670532</v>
       </c>
       <c r="P70">
-        <v>-308.4667923346287</v>
+        <v>-353.3255800370289</v>
       </c>
       <c r="Q70">
-        <v>1627.433207665372</v>
+        <v>1582.574419962972</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1075138084502269</v>
+        <v>0.1095045764647503</v>
       </c>
       <c r="T70">
-        <v>1.42526116513226</v>
+        <v>1.47123733174943</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2319101442488196</v>
+        <v>0.2285491276655033</v>
       </c>
       <c r="W70">
-        <v>0.09109545689209</v>
+        <v>0.09149407345887133</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8988765280961998</v>
+        <v>0.8858493320368345</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0970773293906938</v>
+        <v>0.09780532939069381</v>
       </c>
       <c r="C71">
-        <v>-13109.14140822995</v>
+        <v>-13863.92634750961</v>
       </c>
       <c r="D71">
-        <v>17504.14659177005</v>
+        <v>17259.11365249039</v>
       </c>
       <c r="E71">
-        <v>14231.688</v>
+        <v>14741.44</v>
       </c>
       <c r="F71">
-        <v>35172.888</v>
+        <v>35682.64</v>
       </c>
       <c r="G71">
         <v>4559.6</v>
@@ -7115,37 +7115,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M71">
-        <v>4171.504516800001</v>
+        <v>4231.961104</v>
       </c>
       <c r="N71">
-        <v>-476.1800270040821</v>
+        <v>-536.6366142040815</v>
       </c>
       <c r="O71">
-        <v>-122.8544469670532</v>
+        <v>-138.452246464653</v>
       </c>
       <c r="P71">
-        <v>-353.3255800370289</v>
+        <v>-398.1843677394285</v>
       </c>
       <c r="Q71">
-        <v>1582.574419962972</v>
+        <v>1537.715632260572</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1095045764647503</v>
+        <v>0.1116280623469087</v>
       </c>
       <c r="T71">
-        <v>1.47123733174943</v>
+        <v>1.520278576141078</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2285491276655033</v>
+        <v>0.2252841401274247</v>
       </c>
       <c r="W71">
-        <v>0.09149407345887133</v>
+        <v>0.09188130098088744</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8858493320368345</v>
+        <v>0.8731943415791655</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09780532939069381</v>
+        <v>0.09853332939069381</v>
       </c>
       <c r="C72">
-        <v>-13863.92634750961</v>
+        <v>-14611.94577503961</v>
       </c>
       <c r="D72">
-        <v>17259.11365249039</v>
+        <v>17020.84622496039</v>
       </c>
       <c r="E72">
-        <v>14741.44</v>
+        <v>15251.192</v>
       </c>
       <c r="F72">
-        <v>35682.64</v>
+        <v>36192.392</v>
       </c>
       <c r="G72">
         <v>4559.6</v>
@@ -7197,37 +7197,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M72">
-        <v>4231.961104</v>
+        <v>4292.4176912</v>
       </c>
       <c r="N72">
-        <v>-536.6366142040815</v>
+        <v>-597.0932014040818</v>
       </c>
       <c r="O72">
-        <v>-138.452246464653</v>
+        <v>-154.0500459622531</v>
       </c>
       <c r="P72">
-        <v>-398.1843677394285</v>
+        <v>-443.0431554418287</v>
       </c>
       <c r="Q72">
-        <v>1537.715632260572</v>
+        <v>1492.856844558172</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1116280623469087</v>
+        <v>0.1138979955312849</v>
       </c>
       <c r="T72">
-        <v>1.520278576141078</v>
+        <v>1.572701975318356</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.2252841401274247</v>
+        <v>0.222111124069292</v>
       </c>
       <c r="W72">
-        <v>0.09188130098088744</v>
+        <v>0.09225762068538199</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8731943415791655</v>
+        <v>0.8608958297259378</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09853332939069381</v>
+        <v>0.09926132939069379</v>
       </c>
       <c r="C73">
-        <v>-14611.9457750396</v>
+        <v>-15353.47607522397</v>
       </c>
       <c r="D73">
-        <v>17020.84622496039</v>
+        <v>16789.06792477603</v>
       </c>
       <c r="E73">
-        <v>15251.19199999999</v>
+        <v>15760.94399999999</v>
       </c>
       <c r="F73">
-        <v>36192.39199999999</v>
+        <v>36702.14399999999</v>
       </c>
       <c r="G73">
         <v>4559.6</v>
@@ -7279,37 +7279,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M73">
-        <v>4292.417691199999</v>
+        <v>4352.8742784</v>
       </c>
       <c r="N73">
-        <v>-597.0932014040809</v>
+        <v>-657.5497886040812</v>
       </c>
       <c r="O73">
-        <v>-154.0500459622529</v>
+        <v>-169.647845459853</v>
       </c>
       <c r="P73">
-        <v>-443.043155441828</v>
+        <v>-487.9019431442282</v>
       </c>
       <c r="Q73">
-        <v>1492.856844558172</v>
+        <v>1447.998056855772</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1138979955312848</v>
+        <v>0.1163300668002593</v>
       </c>
       <c r="T73">
-        <v>1.572701975318356</v>
+        <v>1.628869903008297</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.222111124069292</v>
+        <v>0.2190262473461074</v>
       </c>
       <c r="W73">
-        <v>0.09225762068538197</v>
+        <v>0.09262348706475167</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8608958297259379</v>
+        <v>0.8489389432019665</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09926132939069379</v>
+        <v>0.0999893293906938</v>
       </c>
       <c r="C74">
-        <v>-15353.47607522397</v>
+        <v>-16088.77878025512</v>
       </c>
       <c r="D74">
-        <v>16789.06792477603</v>
+        <v>16563.51721974487</v>
       </c>
       <c r="E74">
-        <v>15760.94399999999</v>
+        <v>16270.69599999999</v>
       </c>
       <c r="F74">
-        <v>36702.14399999999</v>
+        <v>37211.89599999999</v>
       </c>
       <c r="G74">
         <v>4559.6</v>
@@ -7361,37 +7361,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M74">
-        <v>4352.8742784</v>
+        <v>4413.3308656</v>
       </c>
       <c r="N74">
-        <v>-657.5497886040812</v>
+        <v>-718.0063758040815</v>
       </c>
       <c r="O74">
-        <v>-169.647845459853</v>
+        <v>-185.245644957453</v>
       </c>
       <c r="P74">
-        <v>-487.9019431442282</v>
+        <v>-532.7607308466285</v>
       </c>
       <c r="Q74">
-        <v>1447.998056855772</v>
+        <v>1403.139269153372</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1163300668002593</v>
+        <v>0.1189422914965652</v>
       </c>
       <c r="T74">
-        <v>1.628869903008297</v>
+        <v>1.68919841793453</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2190262473461074</v>
+        <v>0.216025887793421</v>
       </c>
       <c r="W74">
-        <v>0.09262348706475167</v>
+        <v>0.09297932970770029</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8489389432019665</v>
+        <v>0.8373096426101587</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0999893293906938</v>
+        <v>0.1007173293906938</v>
       </c>
       <c r="C75">
-        <v>-16088.77878025512</v>
+        <v>-16818.10155454004</v>
       </c>
       <c r="D75">
-        <v>16563.51721974487</v>
+        <v>16343.94644545995</v>
       </c>
       <c r="E75">
-        <v>16270.69599999999</v>
+        <v>16780.44799999999</v>
       </c>
       <c r="F75">
-        <v>37211.89599999999</v>
+        <v>37721.64799999999</v>
       </c>
       <c r="G75">
         <v>4559.6</v>
@@ -7443,37 +7443,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M75">
-        <v>4413.3308656</v>
+        <v>4473.787452799999</v>
       </c>
       <c r="N75">
-        <v>-718.0063758040815</v>
+        <v>-778.4629630040808</v>
       </c>
       <c r="O75">
-        <v>-185.245644957453</v>
+        <v>-200.8434444550529</v>
       </c>
       <c r="P75">
-        <v>-532.7607308466285</v>
+        <v>-577.619518549028</v>
       </c>
       <c r="Q75">
-        <v>1403.139269153372</v>
+        <v>1358.280481450973</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1189422914965652</v>
+        <v>0.1217554565541254</v>
       </c>
       <c r="T75">
-        <v>1.68919841793453</v>
+        <v>1.754167587855089</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.216025887793421</v>
+        <v>0.2131066190394558</v>
       </c>
       <c r="W75">
-        <v>0.09297932970770029</v>
+        <v>0.09332555498192055</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8373096426101587</v>
+        <v>0.8259946474397513</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1007173293906938</v>
+        <v>0.1014453293906938</v>
       </c>
       <c r="C76">
-        <v>-16818.10155454004</v>
+        <v>-17541.67910185156</v>
       </c>
       <c r="D76">
-        <v>16343.94644545995</v>
+        <v>16130.12089814843</v>
       </c>
       <c r="E76">
-        <v>16780.44799999999</v>
+        <v>17290.19999999999</v>
       </c>
       <c r="F76">
-        <v>37721.64799999999</v>
+        <v>38231.39999999999</v>
       </c>
       <c r="G76">
         <v>4559.6</v>
@@ -7525,37 +7525,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M76">
-        <v>4473.787452799999</v>
+        <v>4534.24404</v>
       </c>
       <c r="N76">
-        <v>-778.4629630040808</v>
+        <v>-838.9195502040811</v>
       </c>
       <c r="O76">
-        <v>-200.8434444550529</v>
+        <v>-216.4412439526529</v>
       </c>
       <c r="P76">
-        <v>-577.619518549028</v>
+        <v>-622.4783062514282</v>
       </c>
       <c r="Q76">
-        <v>1358.280481450973</v>
+        <v>1313.421693748572</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1217554565541254</v>
+        <v>0.1247936748162904</v>
       </c>
       <c r="T76">
-        <v>1.754167587855089</v>
+        <v>1.824334291369293</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.2131066190394558</v>
+        <v>0.2102651974522631</v>
       </c>
       <c r="W76">
-        <v>0.09332555498192055</v>
+        <v>0.0936625475821616</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8259946474397513</v>
+        <v>0.8149813854738879</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1014453293906938</v>
+        <v>0.1021733293906938</v>
       </c>
       <c r="C77">
-        <v>-17541.67910185156</v>
+        <v>-18259.73400219065</v>
       </c>
       <c r="D77">
-        <v>16130.12089814843</v>
+        <v>15921.81799780935</v>
       </c>
       <c r="E77">
-        <v>17290.19999999999</v>
+        <v>17799.952</v>
       </c>
       <c r="F77">
-        <v>38231.39999999999</v>
+        <v>38741.152</v>
       </c>
       <c r="G77">
         <v>4559.6</v>
@@ -7607,37 +7607,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M77">
-        <v>4534.24404</v>
+        <v>4594.700627200001</v>
       </c>
       <c r="N77">
-        <v>-838.9195502040811</v>
+        <v>-899.3761374040823</v>
       </c>
       <c r="O77">
-        <v>-216.4412439526529</v>
+        <v>-232.0390434502532</v>
       </c>
       <c r="P77">
-        <v>-622.4783062514282</v>
+        <v>-667.337093953829</v>
       </c>
       <c r="Q77">
-        <v>1313.421693748572</v>
+        <v>1268.562906046172</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1247936748162904</v>
+        <v>0.1280850779336358</v>
       </c>
       <c r="T77">
-        <v>1.824334291369293</v>
+        <v>1.900348220176347</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.2102651974522631</v>
+        <v>0.2074985501173648</v>
       </c>
       <c r="W77">
-        <v>0.0936625475821616</v>
+        <v>0.09399067195608053</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8149813854738879</v>
+        <v>0.8042579461913365</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1021733293906938</v>
+        <v>0.1677088966525997</v>
       </c>
       <c r="C78">
-        <v>-18259.73400219065</v>
+        <v>-27328.70852801447</v>
       </c>
       <c r="D78">
-        <v>15921.81799780935</v>
+        <v>7362.595471985532</v>
       </c>
       <c r="E78">
-        <v>17799.952</v>
+        <v>18309.704</v>
       </c>
       <c r="F78">
-        <v>38741.152</v>
+        <v>39250.904</v>
       </c>
       <c r="G78">
         <v>4559.6</v>
@@ -7689,45 +7689,45 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M78">
-        <v>4594.700627200001</v>
+        <v>7881.5815232</v>
       </c>
       <c r="N78">
-        <v>-899.3761374040823</v>
+        <v>-4186.257033404082</v>
       </c>
       <c r="O78">
-        <v>-232.0390434502532</v>
+        <v>-1080.054314618253</v>
       </c>
       <c r="P78">
-        <v>-667.337093953829</v>
+        <v>-3106.202718785829</v>
       </c>
       <c r="Q78">
-        <v>1268.562906046172</v>
+        <v>-1170.302718785828</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1280850779336358</v>
+        <v>0.1382434172433848</v>
       </c>
       <c r="T78">
-        <v>1.900348220176347</v>
+        <v>2.13495189938533</v>
       </c>
       <c r="U78">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.2074985501173648</v>
+        <v>0.1209647728138019</v>
       </c>
       <c r="W78">
-        <v>0.09399067195608053</v>
+        <v>0.1765102736189886</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.8042579461913365</v>
+        <v>0.4688557085806276</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1677088966525997</v>
+        <v>0.1692588966525997</v>
       </c>
       <c r="C79">
-        <v>-27328.70852801447</v>
+        <v>-27930.89633694357</v>
       </c>
       <c r="D79">
-        <v>7362.595471985532</v>
+        <v>7270.159663056429</v>
       </c>
       <c r="E79">
-        <v>18309.704</v>
+        <v>18819.456</v>
       </c>
       <c r="F79">
-        <v>39250.904</v>
+        <v>39760.656</v>
       </c>
       <c r="G79">
         <v>4559.6</v>
@@ -7771,37 +7771,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M79">
-        <v>7881.5815232</v>
+        <v>7983.9397248</v>
       </c>
       <c r="N79">
-        <v>-4186.257033404082</v>
+        <v>-4288.615235004082</v>
       </c>
       <c r="O79">
-        <v>-1080.054314618253</v>
+        <v>-1106.462730631053</v>
       </c>
       <c r="P79">
-        <v>-3106.202718785829</v>
+        <v>-3182.152504373029</v>
       </c>
       <c r="Q79">
-        <v>-1170.302718785828</v>
+        <v>-1246.252504373028</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1382434172433848</v>
+        <v>0.1424453907544477</v>
       </c>
       <c r="T79">
-        <v>2.13495189938533</v>
+        <v>2.231995167539208</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1209647728138019</v>
+        <v>0.1194139423931122</v>
       </c>
       <c r="W79">
-        <v>0.1765102736189886</v>
+        <v>0.1768216803674631</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4688557085806276</v>
+        <v>0.462844737957799</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1692588966525997</v>
+        <v>0.1708088966525997</v>
       </c>
       <c r="C80">
-        <v>-27930.89633694357</v>
+        <v>-28530.79190095769</v>
       </c>
       <c r="D80">
-        <v>7270.159663056429</v>
+        <v>7180.016099042316</v>
       </c>
       <c r="E80">
-        <v>18819.456</v>
+        <v>19329.208</v>
       </c>
       <c r="F80">
-        <v>39760.656</v>
+        <v>40270.408</v>
       </c>
       <c r="G80">
         <v>4559.6</v>
@@ -7853,37 +7853,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M80">
-        <v>7983.9397248</v>
+        <v>8086.297926400001</v>
       </c>
       <c r="N80">
-        <v>-4288.615235004082</v>
+        <v>-4390.973436604082</v>
       </c>
       <c r="O80">
-        <v>-1106.462730631053</v>
+        <v>-1132.871146643853</v>
       </c>
       <c r="P80">
-        <v>-3182.152504373029</v>
+        <v>-3258.102289960229</v>
       </c>
       <c r="Q80">
-        <v>-1246.252504373028</v>
+        <v>-1322.202289960228</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1424453907544477</v>
+        <v>0.1470475522189452</v>
       </c>
       <c r="T80">
-        <v>2.231995167539208</v>
+        <v>2.338280651707742</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1194139423931122</v>
+        <v>0.1179023735020601</v>
       </c>
       <c r="W80">
-        <v>0.1768216803674631</v>
+        <v>0.1771252034007863</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.462844737957799</v>
+        <v>0.4569859438064345</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1708088966525997</v>
+        <v>0.1723588966525997</v>
       </c>
       <c r="C81">
-        <v>-28530.79190095769</v>
+        <v>-29128.4794412308</v>
       </c>
       <c r="D81">
-        <v>7180.016099042316</v>
+        <v>7092.080558769201</v>
       </c>
       <c r="E81">
-        <v>19329.208</v>
+        <v>19838.96</v>
       </c>
       <c r="F81">
-        <v>40270.408</v>
+        <v>40780.16</v>
       </c>
       <c r="G81">
         <v>4559.6</v>
@@ -7935,37 +7935,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M81">
-        <v>8086.297926400001</v>
+        <v>8188.656128000001</v>
       </c>
       <c r="N81">
-        <v>-4390.973436604082</v>
+        <v>-4493.331638204082</v>
       </c>
       <c r="O81">
-        <v>-1132.871146643853</v>
+        <v>-1159.279562656653</v>
       </c>
       <c r="P81">
-        <v>-3258.102289960229</v>
+        <v>-3334.052075547429</v>
       </c>
       <c r="Q81">
-        <v>-1322.202289960228</v>
+        <v>-1398.152075547428</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1470475522189452</v>
+        <v>0.1521099298298925</v>
       </c>
       <c r="T81">
-        <v>2.338280651707742</v>
+        <v>2.455194684293129</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1179023735020601</v>
+        <v>0.1164285938332844</v>
       </c>
       <c r="W81">
-        <v>0.1771252034007863</v>
+        <v>0.1774211383582765</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4569859438064345</v>
+        <v>0.451273619508854</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1723588966525997</v>
+        <v>0.1739088966525997</v>
       </c>
       <c r="C82">
-        <v>-29128.4794412308</v>
+        <v>-29724.03910294146</v>
       </c>
       <c r="D82">
-        <v>7092.080558769201</v>
+        <v>7006.272897058539</v>
       </c>
       <c r="E82">
-        <v>19838.96</v>
+        <v>20348.712</v>
       </c>
       <c r="F82">
-        <v>40780.16</v>
+        <v>41289.912</v>
       </c>
       <c r="G82">
         <v>4559.6</v>
@@ -8017,37 +8017,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M82">
-        <v>8188.656128000001</v>
+        <v>8291.014329600001</v>
       </c>
       <c r="N82">
-        <v>-4493.331638204082</v>
+        <v>-4595.689839804082</v>
       </c>
       <c r="O82">
-        <v>-1159.279562656653</v>
+        <v>-1185.687978669453</v>
       </c>
       <c r="P82">
-        <v>-3334.052075547429</v>
+        <v>-3410.001861134629</v>
       </c>
       <c r="Q82">
-        <v>-1398.152075547428</v>
+        <v>-1474.101861134628</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1521099298298925</v>
+        <v>0.1577051892946237</v>
       </c>
       <c r="T82">
-        <v>2.455194684293129</v>
+        <v>2.584415457150663</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1164285938332844</v>
+        <v>0.1149912037859599</v>
       </c>
       <c r="W82">
-        <v>0.1774211383582765</v>
+        <v>0.1777097662797793</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.451273619508854</v>
+        <v>0.4457023402556584</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1739088966525997</v>
+        <v>0.1754588966525997</v>
       </c>
       <c r="C83">
-        <v>-29724.03910294146</v>
+        <v>-30317.54719890407</v>
       </c>
       <c r="D83">
-        <v>7006.272897058539</v>
+        <v>6922.516801095936</v>
       </c>
       <c r="E83">
-        <v>20348.712</v>
+        <v>20858.464</v>
       </c>
       <c r="F83">
-        <v>41289.912</v>
+        <v>41799.664</v>
       </c>
       <c r="G83">
         <v>4559.6</v>
@@ -8099,37 +8099,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M83">
-        <v>8291.014329600001</v>
+        <v>8393.372531200001</v>
       </c>
       <c r="N83">
-        <v>-4595.689839804082</v>
+        <v>-4698.048041404082</v>
       </c>
       <c r="O83">
-        <v>-1185.687978669453</v>
+        <v>-1212.096394682253</v>
       </c>
       <c r="P83">
-        <v>-3410.001861134629</v>
+        <v>-3485.951646721829</v>
       </c>
       <c r="Q83">
-        <v>-1474.101861134628</v>
+        <v>-1550.051646721829</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1577051892946237</v>
+        <v>0.1639221442554362</v>
       </c>
       <c r="T83">
-        <v>2.584415457150663</v>
+        <v>2.727994093659033</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1149912037859599</v>
+        <v>0.1135888720324725</v>
       </c>
       <c r="W83">
-        <v>0.1777097662797793</v>
+        <v>0.1779913544958795</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4457023402556584</v>
+        <v>0.4402669458622966</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1754588966525997</v>
+        <v>0.1770088966525997</v>
       </c>
       <c r="C84">
-        <v>-30317.54719890407</v>
+        <v>-30909.07643593174</v>
       </c>
       <c r="D84">
-        <v>6922.516801095936</v>
+        <v>6840.739564068265</v>
       </c>
       <c r="E84">
-        <v>20858.464</v>
+        <v>21368.216</v>
       </c>
       <c r="F84">
-        <v>41799.664</v>
+        <v>42309.416</v>
       </c>
       <c r="G84">
         <v>4559.6</v>
@@ -8181,37 +8181,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M84">
-        <v>8393.372531200001</v>
+        <v>8495.730732800001</v>
       </c>
       <c r="N84">
-        <v>-4698.048041404082</v>
+        <v>-4800.406243004082</v>
       </c>
       <c r="O84">
-        <v>-1212.096394682253</v>
+        <v>-1238.504810695053</v>
       </c>
       <c r="P84">
-        <v>-3485.951646721829</v>
+        <v>-3561.901432309029</v>
       </c>
       <c r="Q84">
-        <v>-1550.051646721829</v>
+        <v>-1626.001432309028</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1639221442554362</v>
+        <v>0.1708705056822265</v>
       </c>
       <c r="T84">
-        <v>2.727994093659033</v>
+        <v>2.888464334462506</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1135888720324725</v>
+        <v>0.1122203314055753</v>
       </c>
       <c r="W84">
-        <v>0.1779913544958795</v>
+        <v>0.1782661574537605</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4402669458622966</v>
+        <v>0.4349625248278112</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1770088966525997</v>
+        <v>0.1785588966525997</v>
       </c>
       <c r="C85">
-        <v>-30909.07643593174</v>
+        <v>-31498.69612534206</v>
       </c>
       <c r="D85">
-        <v>6840.739564068265</v>
+        <v>6760.871874657949</v>
       </c>
       <c r="E85">
-        <v>21368.216</v>
+        <v>21877.968</v>
       </c>
       <c r="F85">
-        <v>42309.416</v>
+        <v>42819.16800000001</v>
       </c>
       <c r="G85">
         <v>4559.6</v>
@@ -8263,37 +8263,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M85">
-        <v>8495.730732800001</v>
+        <v>8598.088934400001</v>
       </c>
       <c r="N85">
-        <v>-4800.406243004082</v>
+        <v>-4902.764444604082</v>
       </c>
       <c r="O85">
-        <v>-1238.504810695053</v>
+        <v>-1264.913226707853</v>
       </c>
       <c r="P85">
-        <v>-3561.901432309029</v>
+        <v>-3637.851217896229</v>
       </c>
       <c r="Q85">
-        <v>-1626.001432309028</v>
+        <v>-1701.951217896229</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1708705056822265</v>
+        <v>0.1786874122873657</v>
       </c>
       <c r="T85">
-        <v>2.888464334462506</v>
+        <v>3.068993355366413</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1122203314055753</v>
+        <v>0.1108843750793184</v>
       </c>
       <c r="W85">
-        <v>0.1782661574537605</v>
+        <v>0.1785344174840729</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4349625248278112</v>
+        <v>0.429784399532242</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1785588966525997</v>
+        <v>0.1801088966525997</v>
       </c>
       <c r="C86">
-        <v>-31498.69612534205</v>
+        <v>-32086.47237888666</v>
       </c>
       <c r="D86">
-        <v>6760.871874657949</v>
+        <v>6682.847621113336</v>
       </c>
       <c r="E86">
-        <v>21877.968</v>
+        <v>22387.72</v>
       </c>
       <c r="F86">
-        <v>42819.168</v>
+        <v>43328.92</v>
       </c>
       <c r="G86">
         <v>4559.6</v>
@@ -8345,37 +8345,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M86">
-        <v>8598.088934400001</v>
+        <v>8700.447136000001</v>
       </c>
       <c r="N86">
-        <v>-4902.764444604082</v>
+        <v>-5005.122646204082</v>
       </c>
       <c r="O86">
-        <v>-1264.913226707853</v>
+        <v>-1291.321642720653</v>
       </c>
       <c r="P86">
-        <v>-3637.851217896229</v>
+        <v>-3713.801003483429</v>
       </c>
       <c r="Q86">
-        <v>-1701.951217896229</v>
+        <v>-1777.901003483428</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1786874122873656</v>
+        <v>0.1875465731065233</v>
       </c>
       <c r="T86">
-        <v>3.068993355366411</v>
+        <v>3.273592912390838</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1108843750793184</v>
+        <v>0.1095798530195617</v>
       </c>
       <c r="W86">
-        <v>0.1785344174840729</v>
+        <v>0.178796365513672</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.429784399532242</v>
+        <v>0.4247281124789215</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1801088966525997</v>
+        <v>0.1816588966525997</v>
       </c>
       <c r="C87">
-        <v>-32086.47237888666</v>
+        <v>-32672.46829126888</v>
       </c>
       <c r="D87">
-        <v>6682.847621113336</v>
+        <v>6606.603708731118</v>
       </c>
       <c r="E87">
-        <v>22387.72</v>
+        <v>22897.472</v>
       </c>
       <c r="F87">
-        <v>43328.92</v>
+        <v>43838.672</v>
       </c>
       <c r="G87">
         <v>4559.6</v>
@@ -8427,37 +8427,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M87">
-        <v>8700.447136000001</v>
+        <v>8802.805337600001</v>
       </c>
       <c r="N87">
-        <v>-5005.122646204082</v>
+        <v>-5107.480847804082</v>
       </c>
       <c r="O87">
-        <v>-1291.321642720653</v>
+        <v>-1317.730058733453</v>
       </c>
       <c r="P87">
-        <v>-3713.801003483429</v>
+        <v>-3789.750789070629</v>
       </c>
       <c r="Q87">
-        <v>-1777.901003483428</v>
+        <v>-1853.850789070629</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1875465731065233</v>
+        <v>0.1976713283284179</v>
       </c>
       <c r="T87">
-        <v>3.273592912390838</v>
+        <v>3.507420977561613</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1095798530195617</v>
+        <v>0.108305668682125</v>
       </c>
       <c r="W87">
-        <v>0.178796365513672</v>
+        <v>0.1790522217286293</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4247281124789215</v>
+        <v>0.4197894134966085</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1816588966525997</v>
+        <v>0.1832088966525997</v>
       </c>
       <c r="C88">
-        <v>-32672.46829126888</v>
+        <v>-33256.74411030822</v>
       </c>
       <c r="D88">
-        <v>6606.603708731118</v>
+        <v>6532.079889691784</v>
       </c>
       <c r="E88">
-        <v>22897.472</v>
+        <v>23407.224</v>
       </c>
       <c r="F88">
-        <v>43838.672</v>
+        <v>44348.424</v>
       </c>
       <c r="G88">
         <v>4559.6</v>
@@ -8509,37 +8509,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M88">
-        <v>8802.805337600001</v>
+        <v>8905.163539200001</v>
       </c>
       <c r="N88">
-        <v>-5107.480847804082</v>
+        <v>-5209.839049404082</v>
       </c>
       <c r="O88">
-        <v>-1317.730058733453</v>
+        <v>-1344.138474746253</v>
       </c>
       <c r="P88">
-        <v>-3789.750789070629</v>
+        <v>-3865.700574657829</v>
       </c>
       <c r="Q88">
-        <v>-1853.850789070629</v>
+        <v>-1929.800574657828</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1976713283284179</v>
+        <v>0.2093537381998346</v>
       </c>
       <c r="T88">
-        <v>3.507420977561613</v>
+        <v>3.777222591220198</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.108305668682125</v>
+        <v>0.1070607759386523</v>
       </c>
       <c r="W88">
-        <v>0.1790522217286293</v>
+        <v>0.1793021961915186</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4197894134966085</v>
+        <v>0.4149642478242336</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1832088966525997</v>
+        <v>0.1847588966525997</v>
       </c>
       <c r="C89">
-        <v>-33256.74411030822</v>
+        <v>-33839.35739571648</v>
       </c>
       <c r="D89">
-        <v>6532.079889691784</v>
+        <v>6459.21860428352</v>
       </c>
       <c r="E89">
-        <v>23407.224</v>
+        <v>23916.976</v>
       </c>
       <c r="F89">
-        <v>44348.424</v>
+        <v>44858.176</v>
       </c>
       <c r="G89">
         <v>4559.6</v>
@@ -8591,37 +8591,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M89">
-        <v>8905.163539200001</v>
+        <v>9007.521740800001</v>
       </c>
       <c r="N89">
-        <v>-5209.839049404082</v>
+        <v>-5312.197251004082</v>
       </c>
       <c r="O89">
-        <v>-1344.138474746253</v>
+        <v>-1370.546890759053</v>
       </c>
       <c r="P89">
-        <v>-3865.700574657829</v>
+        <v>-3941.650360245029</v>
       </c>
       <c r="Q89">
-        <v>-1929.800574657828</v>
+        <v>-2005.750360245029</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2093537381998346</v>
+        <v>0.2229832163831542</v>
       </c>
       <c r="T89">
-        <v>3.777222591220198</v>
+        <v>4.091991140488549</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1070607759386523</v>
+        <v>0.1058441762120767</v>
       </c>
       <c r="W89">
-        <v>0.1793021961915186</v>
+        <v>0.179546489416615</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4149642478242336</v>
+        <v>0.4102487450080492</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1847588966525997</v>
+        <v>0.1863088966525998</v>
       </c>
       <c r="C90">
-        <v>-33839.35739571648</v>
+        <v>-34420.36316736478</v>
       </c>
       <c r="D90">
-        <v>6459.21860428352</v>
+        <v>6387.964832635215</v>
       </c>
       <c r="E90">
-        <v>23916.976</v>
+        <v>24426.728</v>
       </c>
       <c r="F90">
-        <v>44858.176</v>
+        <v>45367.928</v>
       </c>
       <c r="G90">
         <v>4559.6</v>
@@ -8673,37 +8673,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M90">
-        <v>9007.521740800001</v>
+        <v>9109.879942400001</v>
       </c>
       <c r="N90">
-        <v>-5312.197251004082</v>
+        <v>-5414.555452604082</v>
       </c>
       <c r="O90">
-        <v>-1370.546890759053</v>
+        <v>-1396.955306771853</v>
       </c>
       <c r="P90">
-        <v>-3941.650360245029</v>
+        <v>-4017.600145832229</v>
       </c>
       <c r="Q90">
-        <v>-2005.750360245029</v>
+        <v>-2081.700145832228</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2229832163831542</v>
+        <v>0.2390907815088955</v>
       </c>
       <c r="T90">
-        <v>4.091991140488549</v>
+        <v>4.463990335078417</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1058441762120767</v>
+        <v>0.1046549158051994</v>
       </c>
       <c r="W90">
-        <v>0.179546489416615</v>
+        <v>0.179785292906316</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4102487450080492</v>
+        <v>0.4056392085472845</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1863088966525998</v>
+        <v>0.1878588966525997</v>
       </c>
       <c r="C91">
-        <v>-34420.36316736478</v>
+        <v>-34999.81404384415</v>
       </c>
       <c r="D91">
-        <v>6387.964832635215</v>
+        <v>6318.265956155848</v>
       </c>
       <c r="E91">
-        <v>24426.728</v>
+        <v>24936.48</v>
       </c>
       <c r="F91">
-        <v>45367.928</v>
+        <v>45877.68</v>
       </c>
       <c r="G91">
         <v>4559.6</v>
@@ -8755,37 +8755,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M91">
-        <v>9109.879942400001</v>
+        <v>9212.238144000001</v>
       </c>
       <c r="N91">
-        <v>-5414.555452604082</v>
+        <v>-5516.913654204082</v>
       </c>
       <c r="O91">
-        <v>-1396.955306771853</v>
+        <v>-1423.363722784653</v>
       </c>
       <c r="P91">
-        <v>-4017.600145832229</v>
+        <v>-4093.549931419429</v>
       </c>
       <c r="Q91">
-        <v>-2081.700145832228</v>
+        <v>-2157.649931419429</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2390907815088955</v>
+        <v>0.258419859659785</v>
       </c>
       <c r="T91">
-        <v>4.463990335078417</v>
+        <v>4.910389368586259</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1046549158051994</v>
+        <v>0.1034920834073639</v>
       </c>
       <c r="W91">
-        <v>0.179785292906316</v>
+        <v>0.1800187896518013</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4056392085472845</v>
+        <v>0.4011321062300925</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1878588966525997</v>
+        <v>0.1894088966525997</v>
       </c>
       <c r="C92">
-        <v>-34999.81404384415</v>
+        <v>-35577.76037205302</v>
       </c>
       <c r="D92">
-        <v>6318.265956155848</v>
+        <v>6250.071627946977</v>
       </c>
       <c r="E92">
-        <v>24936.48</v>
+        <v>25446.232</v>
       </c>
       <c r="F92">
-        <v>45877.68</v>
+        <v>46387.432</v>
       </c>
       <c r="G92">
         <v>4559.6</v>
@@ -8837,37 +8837,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M92">
-        <v>9212.238144000001</v>
+        <v>9314.596345600001</v>
       </c>
       <c r="N92">
-        <v>-5516.913654204082</v>
+        <v>-5619.271855804082</v>
       </c>
       <c r="O92">
-        <v>-1423.363722784653</v>
+        <v>-1449.772138797453</v>
       </c>
       <c r="P92">
-        <v>-4093.549931419429</v>
+        <v>-4169.499717006629</v>
       </c>
       <c r="Q92">
-        <v>-2157.649931419429</v>
+        <v>-2233.599717006628</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.258419859659785</v>
+        <v>0.2820442885108723</v>
       </c>
       <c r="T92">
-        <v>4.910389368586259</v>
+        <v>5.455988187318066</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1034920834073639</v>
+        <v>0.1023548077655247</v>
       </c>
       <c r="W92">
-        <v>0.1800187896518013</v>
+        <v>0.1802471546006826</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4011321062300925</v>
+        <v>0.3967240611066849</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1894088966525997</v>
+        <v>0.1909588966525997</v>
       </c>
       <c r="C93">
-        <v>-35577.76037205302</v>
+        <v>-36154.25034848242</v>
       </c>
       <c r="D93">
-        <v>6250.071627946977</v>
+        <v>6183.333651517583</v>
       </c>
       <c r="E93">
-        <v>25446.232</v>
+        <v>25955.984</v>
       </c>
       <c r="F93">
-        <v>46387.432</v>
+        <v>46897.184</v>
       </c>
       <c r="G93">
         <v>4559.6</v>
@@ -8919,37 +8919,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M93">
-        <v>9314.596345600001</v>
+        <v>9416.954547200001</v>
       </c>
       <c r="N93">
-        <v>-5619.271855804082</v>
+        <v>-5721.630057404082</v>
       </c>
       <c r="O93">
-        <v>-1449.772138797453</v>
+        <v>-1476.180554810253</v>
       </c>
       <c r="P93">
-        <v>-4169.499717006629</v>
+        <v>-4245.449502593829</v>
       </c>
       <c r="Q93">
-        <v>-2233.599717006628</v>
+        <v>-2309.549502593828</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2820442885108723</v>
+        <v>0.3115748245747314</v>
       </c>
       <c r="T93">
-        <v>5.455988187318066</v>
+        <v>6.137986710732826</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1023548077655247</v>
+        <v>0.1012422555072038</v>
       </c>
       <c r="W93">
-        <v>0.1802471546006826</v>
+        <v>0.1804705550941535</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3967240611066849</v>
+        <v>0.3924118430511775</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1909588966525997</v>
+        <v>0.1925088966525997</v>
       </c>
       <c r="C94">
-        <v>-36154.25034848242</v>
+        <v>-36729.33013281268</v>
       </c>
       <c r="D94">
-        <v>6183.333651517583</v>
+        <v>6118.005867187321</v>
       </c>
       <c r="E94">
-        <v>25955.984</v>
+        <v>26465.736</v>
       </c>
       <c r="F94">
-        <v>46897.184</v>
+        <v>47406.936</v>
       </c>
       <c r="G94">
         <v>4559.6</v>
@@ -9001,37 +9001,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M94">
-        <v>9416.954547200001</v>
+        <v>9519.312748800001</v>
       </c>
       <c r="N94">
-        <v>-5721.630057404082</v>
+        <v>-5823.988259004082</v>
       </c>
       <c r="O94">
-        <v>-1476.180554810253</v>
+        <v>-1502.588970823053</v>
       </c>
       <c r="P94">
-        <v>-4245.449502593829</v>
+        <v>-4321.399288181029</v>
       </c>
       <c r="Q94">
-        <v>-2309.549502593828</v>
+        <v>-2385.499288181029</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3115748245747314</v>
+        <v>0.3495426566568359</v>
       </c>
       <c r="T94">
-        <v>6.137986710732826</v>
+        <v>7.014841955123231</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1012422555072038</v>
+        <v>0.1001536291039005</v>
       </c>
       <c r="W94">
-        <v>0.1804705550941535</v>
+        <v>0.1806891512759368</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3924118430511775</v>
+        <v>0.3881923608678315</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1925088966525997</v>
+        <v>0.1940588966525997</v>
       </c>
       <c r="C95">
-        <v>-36729.33013281268</v>
+        <v>-37303.04395438459</v>
       </c>
       <c r="D95">
-        <v>6118.005867187321</v>
+        <v>6054.044045615419</v>
       </c>
       <c r="E95">
-        <v>26465.736</v>
+        <v>26975.488</v>
       </c>
       <c r="F95">
-        <v>47406.936</v>
+        <v>47916.688</v>
       </c>
       <c r="G95">
         <v>4559.6</v>
@@ -9083,37 +9083,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M95">
-        <v>9519.312748800001</v>
+        <v>9621.670950400001</v>
       </c>
       <c r="N95">
-        <v>-5823.988259004082</v>
+        <v>-5926.346460604082</v>
       </c>
       <c r="O95">
-        <v>-1502.588970823053</v>
+        <v>-1528.997386835853</v>
       </c>
       <c r="P95">
-        <v>-4321.399288181029</v>
+        <v>-4397.34907376823</v>
       </c>
       <c r="Q95">
-        <v>-2385.499288181029</v>
+        <v>-2461.449073768229</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3495426566568359</v>
+        <v>0.4001664327663086</v>
       </c>
       <c r="T95">
-        <v>7.014841955123231</v>
+        <v>8.183982280977103</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1001536291039005</v>
+        <v>0.09908816496449732</v>
       </c>
       <c r="W95">
-        <v>0.1806891512759368</v>
+        <v>0.1809030964751289</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3881923608678315</v>
+        <v>0.3840626549011524</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1940588966525997</v>
+        <v>0.1956088966525997</v>
       </c>
       <c r="C96">
-        <v>-37303.04395438459</v>
+        <v>-37875.43421206072</v>
       </c>
       <c r="D96">
-        <v>6054.044045615419</v>
+        <v>5991.405787939279</v>
       </c>
       <c r="E96">
-        <v>26975.488</v>
+        <v>27485.24</v>
       </c>
       <c r="F96">
-        <v>47916.688</v>
+        <v>48426.44</v>
       </c>
       <c r="G96">
         <v>4559.6</v>
@@ -9165,37 +9165,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M96">
-        <v>9621.670950400001</v>
+        <v>9724.029152000001</v>
       </c>
       <c r="N96">
-        <v>-5926.346460604082</v>
+        <v>-6028.704662204083</v>
       </c>
       <c r="O96">
-        <v>-1528.997386835853</v>
+        <v>-1555.405802848653</v>
       </c>
       <c r="P96">
-        <v>-4397.34907376823</v>
+        <v>-4473.298859355429</v>
       </c>
       <c r="Q96">
-        <v>-2461.449073768229</v>
+        <v>-2537.398859355429</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4001664327663086</v>
+        <v>0.4710397193195706</v>
       </c>
       <c r="T96">
-        <v>8.183982280977103</v>
+        <v>9.82077873717253</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09908816496449732</v>
+        <v>0.09804513164908156</v>
       </c>
       <c r="W96">
-        <v>0.1809030964751289</v>
+        <v>0.1811125375648644</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3840626549011524</v>
+        <v>0.3800198901127192</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1956088966525997</v>
+        <v>0.1971588966525997</v>
       </c>
       <c r="C97">
-        <v>-37875.43421206072</v>
+        <v>-38446.54156795117</v>
       </c>
       <c r="D97">
-        <v>5991.405787939279</v>
+        <v>5930.050432048829</v>
       </c>
       <c r="E97">
-        <v>27485.24</v>
+        <v>27994.992</v>
       </c>
       <c r="F97">
-        <v>48426.44</v>
+        <v>48936.192</v>
       </c>
       <c r="G97">
         <v>4559.6</v>
@@ -9247,37 +9247,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M97">
-        <v>9724.029152000001</v>
+        <v>9826.387353600001</v>
       </c>
       <c r="N97">
-        <v>-6028.704662204083</v>
+        <v>-6131.062863804083</v>
       </c>
       <c r="O97">
-        <v>-1555.405802848653</v>
+        <v>-1581.814218861453</v>
       </c>
       <c r="P97">
-        <v>-4473.298859355429</v>
+        <v>-4549.248644942629</v>
       </c>
       <c r="Q97">
-        <v>-2537.398859355429</v>
+        <v>-2613.348644942628</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4710397193195706</v>
+        <v>0.5773496491494634</v>
       </c>
       <c r="T97">
-        <v>9.82077873717253</v>
+        <v>12.27597342146567</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09804513164908156</v>
+        <v>0.09702382819440362</v>
       </c>
       <c r="W97">
-        <v>0.1811125375648644</v>
+        <v>0.1813176152985638</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3800198901127192</v>
+        <v>0.3760613495907117</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1971588966525997</v>
+        <v>0.1987088966525997</v>
       </c>
       <c r="C98">
-        <v>-38446.54156795116</v>
+        <v>-39016.40503543863</v>
       </c>
       <c r="D98">
-        <v>5930.050432048829</v>
+        <v>5869.938964561372</v>
       </c>
       <c r="E98">
-        <v>27994.99199999999</v>
+        <v>28504.744</v>
       </c>
       <c r="F98">
-        <v>48936.192</v>
+        <v>49445.944</v>
       </c>
       <c r="G98">
         <v>4559.6</v>
@@ -9329,37 +9329,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M98">
-        <v>9826.387353599999</v>
+        <v>9928.745555199999</v>
       </c>
       <c r="N98">
-        <v>-6131.062863804081</v>
+        <v>-6233.421065404081</v>
       </c>
       <c r="O98">
-        <v>-1581.814218861453</v>
+        <v>-1608.222634874253</v>
       </c>
       <c r="P98">
-        <v>-4549.248644942628</v>
+        <v>-4625.198430529828</v>
       </c>
       <c r="Q98">
-        <v>-2613.348644942627</v>
+        <v>-2689.298430529828</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.577349649149462</v>
+        <v>0.7545328655326159</v>
       </c>
       <c r="T98">
-        <v>12.27597342146563</v>
+        <v>16.36796456195418</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09702382819440365</v>
+        <v>0.09602358254291493</v>
       </c>
       <c r="W98">
-        <v>0.1813176152985637</v>
+        <v>0.1815184646253827</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3760613495907118</v>
+        <v>0.3721844284609106</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1987088966525997</v>
+        <v>0.2002588966525997</v>
       </c>
       <c r="C99">
-        <v>-39016.40503543863</v>
+        <v>-39585.06206190358</v>
       </c>
       <c r="D99">
-        <v>5869.938964561372</v>
+        <v>5811.033938096411</v>
       </c>
       <c r="E99">
-        <v>28504.744</v>
+        <v>29014.496</v>
       </c>
       <c r="F99">
-        <v>49445.944</v>
+        <v>49955.696</v>
       </c>
       <c r="G99">
         <v>4559.6</v>
@@ -9411,37 +9411,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M99">
-        <v>9928.745555199999</v>
+        <v>10031.1037568</v>
       </c>
       <c r="N99">
-        <v>-6233.421065404081</v>
+        <v>-6335.779267004081</v>
       </c>
       <c r="O99">
-        <v>-1608.222634874253</v>
+        <v>-1634.631050887053</v>
       </c>
       <c r="P99">
-        <v>-4625.198430529828</v>
+        <v>-4701.148216117028</v>
       </c>
       <c r="Q99">
-        <v>-2689.298430529828</v>
+        <v>-2765.248216117027</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7545328655326159</v>
+        <v>1.108899298298924</v>
       </c>
       <c r="T99">
-        <v>16.36796456195418</v>
+        <v>24.55194684293127</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09602358254291493</v>
+        <v>0.09504375006798724</v>
       </c>
       <c r="W99">
-        <v>0.1815184646253827</v>
+        <v>0.1817152149863482</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3721844284609106</v>
+        <v>0.3683866281704932</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2002588966525997</v>
+        <v>0.2018088966525997</v>
       </c>
       <c r="C100">
-        <v>-39585.06206190358</v>
+        <v>-40152.54860651809</v>
       </c>
       <c r="D100">
-        <v>5811.033938096411</v>
+        <v>5753.299393481905</v>
       </c>
       <c r="E100">
-        <v>29014.496</v>
+        <v>29524.248</v>
       </c>
       <c r="F100">
-        <v>49955.696</v>
+        <v>50465.448</v>
       </c>
       <c r="G100">
         <v>4559.6</v>
@@ -9493,37 +9493,37 @@
         <v>3695.324489795918</v>
       </c>
       <c r="M100">
-        <v>10031.1037568</v>
+        <v>10133.4619584</v>
       </c>
       <c r="N100">
-        <v>-6335.779267004081</v>
+        <v>-6438.137468604081</v>
       </c>
       <c r="O100">
-        <v>-1634.631050887053</v>
+        <v>-1661.039466899853</v>
       </c>
       <c r="P100">
-        <v>-4701.148216117028</v>
+        <v>-4777.098001704227</v>
       </c>
       <c r="Q100">
-        <v>-2765.248216117027</v>
+        <v>-2841.198001704227</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.108899298298924</v>
+        <v>2.171998596597848</v>
       </c>
       <c r="T100">
-        <v>24.55194684293127</v>
+        <v>49.10389368586254</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09504375006798724</v>
+        <v>0.09408371218851262</v>
       </c>
       <c r="W100">
-        <v>0.1817152149863482</v>
+        <v>0.1819079905925467</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3683866281704932</v>
+        <v>0.3646655511182659</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2018088966525997</v>
-      </c>
-      <c r="C101">
-        <v>-40152.54860651809</v>
-      </c>
-      <c r="D101">
-        <v>5753.299393481905</v>
-      </c>
-      <c r="E101">
-        <v>29524.248</v>
-      </c>
-      <c r="F101">
-        <v>50465.448</v>
-      </c>
-      <c r="G101">
-        <v>4559.6</v>
-      </c>
-      <c r="H101">
-        <v>30034</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5631.224489795919</v>
-      </c>
-      <c r="K101">
-        <v>1935.900000000001</v>
-      </c>
-      <c r="L101">
-        <v>3695.324489795918</v>
-      </c>
-      <c r="M101">
-        <v>10133.4619584</v>
-      </c>
-      <c r="N101">
-        <v>-6438.137468604081</v>
-      </c>
-      <c r="O101">
-        <v>-1661.039466899853</v>
-      </c>
-      <c r="P101">
-        <v>-4777.098001704227</v>
-      </c>
-      <c r="Q101">
-        <v>-2841.198001704227</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.171998596597848</v>
-      </c>
-      <c r="T101">
-        <v>49.10389368586254</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09408371218851262</v>
-      </c>
-      <c r="W101">
-        <v>0.1819079905925467</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3646655511182659</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
